--- a/Portage Canal/Zooplankton_microscopy_counts.xlsx
+++ b/Portage Canal/Zooplankton_microscopy_counts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/khadijahhomolka/Documents/GitHub/PGST-Natural-Resources/Portage Canal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF612220-1108-9042-86D2-C6CF6BFE6223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9AD578-7702-A047-8295-C17B8FCC239B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36580" yWindow="-1560" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68680" yWindow="-3000" windowWidth="36480" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="50">
   <si>
     <t>Project</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Bug</t>
   </si>
   <si>
-    <t>Arrow worm</t>
-  </si>
-  <si>
     <t>Polychaete worm</t>
   </si>
   <si>
@@ -140,13 +137,7 @@
     <t>Worm</t>
   </si>
   <si>
-    <t>Pagarus</t>
-  </si>
-  <si>
     <t>Polychaete</t>
-  </si>
-  <si>
-    <t>Chaetognath</t>
   </si>
   <si>
     <t>Roundworm</t>
@@ -176,16 +167,22 @@
     <t>Sample Number</t>
   </si>
   <si>
-    <t>NC</t>
+    <t>Species Concentration Multiplier (Individuals/L)</t>
   </si>
   <si>
-    <t>SC</t>
+    <t>Pagurus</t>
   </si>
   <si>
-    <t>OAK</t>
+    <t>Arrow Worm</t>
   </si>
   <si>
-    <t>Species Concentration Multiplier (Individuals/L)</t>
+    <t>North Portage Canal</t>
+  </si>
+  <si>
+    <t>South Portage Canal</t>
+  </si>
+  <si>
+    <t>Oak Bay</t>
   </si>
 </sst>
 </file>
@@ -480,7 +477,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -495,7 +492,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -513,10 +510,10 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -554,7 +551,7 @@
         <v>28</v>
       </c>
       <c r="L2">
-        <f>K2/F2</f>
+        <f>(K2/F2)</f>
         <v>0.19337016574585633</v>
       </c>
       <c r="M2">
@@ -588,7 +585,7 @@
         <v>13.26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>12</v>
@@ -597,12 +594,12 @@
         <v>11</v>
       </c>
       <c r="L3">
-        <f>K3/G3</f>
-        <v>5.7291666666666663E-3</v>
+        <f t="shared" ref="L3:L66" si="0">(K3/F3)</f>
+        <v>7.5966850828729282E-2</v>
       </c>
       <c r="M3">
         <f>L3*1000</f>
-        <v>5.7291666666666661</v>
+        <v>75.966850828729278</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -640,12 +637,12 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <f>K4/G4</f>
-        <v>1.5625000000000001E-3</v>
+        <f t="shared" si="0"/>
+        <v>2.0718232044198894E-2</v>
       </c>
       <c r="M4">
         <f>L4*1000</f>
-        <v>1.5625</v>
+        <v>20.718232044198896</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -680,7 +677,7 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5" si="0">K5/F5</f>
+        <f t="shared" si="0"/>
         <v>6.9060773480662981E-3</v>
       </c>
       <c r="M5">
@@ -723,12 +720,12 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L7" si="2">K6/G6</f>
-        <v>5.2083333333333333E-4</v>
+        <f t="shared" si="0"/>
+        <v>6.9060773480662981E-3</v>
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
-        <v>0.52083333333333337</v>
+        <v>6.9060773480662982</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -757,7 +754,7 @@
         <v>13.26</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>17</v>
@@ -766,12 +763,12 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <f t="shared" si="2"/>
-        <v>1.0416666666666667E-3</v>
+        <f t="shared" si="0"/>
+        <v>1.3812154696132596E-2</v>
       </c>
       <c r="M7">
         <f t="shared" si="1"/>
-        <v>1.0416666666666667</v>
+        <v>13.812154696132596</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -806,7 +803,7 @@
         <v>2</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L8" si="3">K8/F8</f>
+        <f t="shared" si="0"/>
         <v>1.3812154696132596E-2</v>
       </c>
       <c r="M8">
@@ -840,7 +837,7 @@
         <v>16.3</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>12</v>
@@ -849,12 +846,12 @@
         <v>13</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L10" si="4">K9/G9</f>
-        <v>6.7708333333333336E-3</v>
+        <f t="shared" si="0"/>
+        <v>8.9779005524861871E-2</v>
       </c>
       <c r="M9">
         <f t="shared" si="1"/>
-        <v>6.7708333333333339</v>
+        <v>89.779005524861873</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -892,12 +889,12 @@
         <v>4</v>
       </c>
       <c r="L10">
-        <f t="shared" si="4"/>
-        <v>2.0833333333333333E-3</v>
+        <f t="shared" si="0"/>
+        <v>2.7624309392265192E-2</v>
       </c>
       <c r="M10">
         <f t="shared" si="1"/>
-        <v>2.0833333333333335</v>
+        <v>27.624309392265193</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -926,7 +923,7 @@
         <v>16.3</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>17</v>
@@ -935,7 +932,7 @@
         <v>4</v>
       </c>
       <c r="L11">
-        <f t="shared" ref="L11" si="5">K11/F11</f>
+        <f t="shared" si="0"/>
         <v>2.7624309392265192E-2</v>
       </c>
       <c r="M11">
@@ -978,12 +975,12 @@
         <v>31</v>
       </c>
       <c r="L12">
-        <f t="shared" ref="L12:L13" si="6">K12/G12</f>
-        <v>1.6145833333333335E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.21408839779005523</v>
       </c>
       <c r="M12">
         <f t="shared" si="1"/>
-        <v>16.145833333333336</v>
+        <v>214.08839779005524</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1021,12 +1018,12 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <f t="shared" si="6"/>
-        <v>5.2083333333333333E-4</v>
+        <f t="shared" si="0"/>
+        <v>6.9060773480662981E-3</v>
       </c>
       <c r="M13">
         <f t="shared" si="1"/>
-        <v>0.52083333333333337</v>
+        <v>6.9060773480662982</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1061,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <f t="shared" ref="L14" si="7">K14/F14</f>
+        <f t="shared" si="0"/>
         <v>6.9060773480662981E-3</v>
       </c>
       <c r="M14">
@@ -1101,12 +1098,12 @@
         <v>3</v>
       </c>
       <c r="L15">
-        <f t="shared" ref="L15:L16" si="8">K15/G15</f>
-        <v>1.5625000000000001E-3</v>
+        <f t="shared" si="0"/>
+        <v>2.0718232044198894E-2</v>
       </c>
       <c r="M15">
         <f t="shared" si="1"/>
-        <v>1.5625</v>
+        <v>20.718232044198896</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1135,7 +1132,7 @@
         <v>16.3</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>21</v>
@@ -1144,12 +1141,12 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <f t="shared" si="8"/>
-        <v>5.2083333333333333E-4</v>
+        <f t="shared" si="0"/>
+        <v>6.9060773480662981E-3</v>
       </c>
       <c r="M16">
         <f t="shared" si="1"/>
-        <v>0.52083333333333337</v>
+        <v>6.9060773480662982</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1187,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <f t="shared" ref="L17" si="9">K17/F17</f>
+        <f t="shared" si="0"/>
         <v>6.9060773480662981E-3</v>
       </c>
       <c r="M17">
@@ -1221,7 +1218,7 @@
         <v>12.7</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>12</v>
@@ -1230,12 +1227,12 @@
         <v>18</v>
       </c>
       <c r="L18">
-        <f t="shared" ref="L18:L19" si="10">K18/G18</f>
-        <v>7.6271186440677969E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.12430939226519336</v>
       </c>
       <c r="M18">
         <f t="shared" si="1"/>
-        <v>7.6271186440677967</v>
+        <v>124.30939226519335</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1273,12 +1270,12 @@
         <v>2</v>
       </c>
       <c r="L19">
-        <f t="shared" si="10"/>
-        <v>8.4745762711864404E-4</v>
+        <f t="shared" si="0"/>
+        <v>1.3812154696132596E-2</v>
       </c>
       <c r="M19">
         <f t="shared" si="1"/>
-        <v>0.84745762711864403</v>
+        <v>13.812154696132596</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1316,7 +1313,7 @@
         <v>18</v>
       </c>
       <c r="L20">
-        <f t="shared" ref="L20" si="11">K20/F20</f>
+        <f t="shared" si="0"/>
         <v>0.12430939226519336</v>
       </c>
       <c r="M20">
@@ -1359,12 +1356,12 @@
         <v>3</v>
       </c>
       <c r="L21">
-        <f t="shared" ref="L21:L22" si="12">K21/G21</f>
-        <v>1.271186440677966E-3</v>
+        <f t="shared" si="0"/>
+        <v>2.0718232044198894E-2</v>
       </c>
       <c r="M21">
         <f t="shared" si="1"/>
-        <v>1.271186440677966</v>
+        <v>20.718232044198896</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1393,7 +1390,7 @@
         <v>12.7</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>17</v>
@@ -1402,12 +1399,12 @@
         <v>3</v>
       </c>
       <c r="L22">
-        <f t="shared" si="12"/>
-        <v>1.271186440677966E-3</v>
+        <f t="shared" si="0"/>
+        <v>2.0718232044198894E-2</v>
       </c>
       <c r="M22">
         <f t="shared" si="1"/>
-        <v>1.271186440677966</v>
+        <v>20.718232044198896</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1445,7 +1442,7 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <f t="shared" ref="L23" si="13">K23/F23</f>
+        <f t="shared" si="0"/>
         <v>6.9060773480662981E-3</v>
       </c>
       <c r="M23">
@@ -1485,12 +1482,12 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <f t="shared" ref="L24:L25" si="14">K24/G24</f>
-        <v>4.2372881355932202E-4</v>
+        <f t="shared" si="0"/>
+        <v>6.9060773480662981E-3</v>
       </c>
       <c r="M24">
         <f t="shared" si="1"/>
-        <v>0.42372881355932202</v>
+        <v>6.9060773480662982</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1525,12 +1522,12 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <f t="shared" si="14"/>
-        <v>2.4456521739130437E-3</v>
+        <f t="shared" si="0"/>
+        <v>7.1621836702212324E-2</v>
       </c>
       <c r="M25">
         <f t="shared" si="1"/>
-        <v>2.4456521739130435</v>
+        <v>71.62183670221232</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1568,7 +1565,7 @@
         <v>2</v>
       </c>
       <c r="L26">
-        <f t="shared" ref="L26" si="15">K26/F26</f>
+        <f t="shared" si="0"/>
         <v>1.5915963711602737E-2</v>
       </c>
       <c r="M26">
@@ -1608,12 +1605,12 @@
         <v>24</v>
       </c>
       <c r="L27">
-        <f t="shared" ref="L27:L28" si="16">K27/G27</f>
-        <v>6.5217391304347823E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.19099156453923286</v>
       </c>
       <c r="M27">
         <f t="shared" si="1"/>
-        <v>6.5217391304347823</v>
+        <v>190.99156453923285</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1642,7 +1639,7 @@
         <v>29.3</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>12</v>
@@ -1651,12 +1648,12 @@
         <v>3</v>
       </c>
       <c r="L28">
-        <f t="shared" si="16"/>
-        <v>8.1521739130434778E-4</v>
+        <f t="shared" si="0"/>
+        <v>2.3873945567404107E-2</v>
       </c>
       <c r="M28">
         <f t="shared" si="1"/>
-        <v>0.81521739130434778</v>
+        <v>23.873945567404107</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1694,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <f t="shared" ref="L29" si="17">K29/F29</f>
+        <f t="shared" si="0"/>
         <v>7.9579818558013684E-3</v>
       </c>
       <c r="M29">
@@ -1728,7 +1725,7 @@
         <v>29.3</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>21</v>
@@ -1737,12 +1734,12 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <f t="shared" ref="L30:L31" si="18">K30/G30</f>
-        <v>1.6304347826086956E-3</v>
+        <f t="shared" si="0"/>
+        <v>4.7747891134808214E-2</v>
       </c>
       <c r="M30">
         <f t="shared" si="1"/>
-        <v>1.6304347826086956</v>
+        <v>47.747891134808214</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1777,12 +1774,12 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <f t="shared" si="18"/>
-        <v>2.7173913043478261E-4</v>
+        <f t="shared" si="0"/>
+        <v>7.9579818558013684E-3</v>
       </c>
       <c r="M31">
         <f t="shared" si="1"/>
-        <v>0.27173913043478259</v>
+        <v>7.9579818558013686</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1811,7 +1808,7 @@
         <v>29.3</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>17</v>
@@ -1820,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <f t="shared" ref="L32" si="19">K32/F32</f>
+        <f t="shared" si="0"/>
         <v>7.9579818558013684E-3</v>
       </c>
       <c r="M32">
@@ -1860,12 +1857,12 @@
         <v>32</v>
       </c>
       <c r="L33">
-        <f t="shared" ref="L33:L34" si="20">K33/G33</f>
-        <v>8.0000000000000002E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.25465541938564379</v>
       </c>
       <c r="M33">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>254.6554193856438</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1900,12 +1897,12 @@
         <v>9</v>
       </c>
       <c r="L34">
-        <f t="shared" si="20"/>
-        <v>2.2499999999999998E-3</v>
+        <f t="shared" si="0"/>
+        <v>7.1621836702212324E-2</v>
       </c>
       <c r="M34">
         <f t="shared" si="1"/>
-        <v>2.25</v>
+        <v>71.62183670221232</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,7 +1931,7 @@
         <v>31.8</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>21</v>
@@ -1943,7 +1940,7 @@
         <v>7</v>
       </c>
       <c r="L35">
-        <f t="shared" ref="L35:L95" si="21">K35/F35</f>
+        <f t="shared" si="0"/>
         <v>5.5705872990609584E-2</v>
       </c>
       <c r="M35">
@@ -1986,12 +1983,12 @@
         <v>2</v>
       </c>
       <c r="L36">
-        <f t="shared" ref="L36:L97" si="22">K36/G36</f>
-        <v>5.0000000000000001E-4</v>
+        <f t="shared" si="0"/>
+        <v>1.5915963711602737E-2</v>
       </c>
       <c r="M36">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>15.915963711602737</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2026,12 +2023,12 @@
         <v>29</v>
       </c>
       <c r="L37">
-        <f t="shared" si="22"/>
-        <v>6.3596491228070174E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.23078147381823971</v>
       </c>
       <c r="M37">
         <f t="shared" si="1"/>
-        <v>6.3596491228070171</v>
+        <v>230.7814738182397</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2066,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="L38">
-        <f t="shared" ref="L38:L98" si="23">K38/F38</f>
+        <f t="shared" si="0"/>
         <v>7.9579818558013687E-2</v>
       </c>
       <c r="M38">
@@ -2100,7 +2097,7 @@
         <v>36.299999999999997</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>21</v>
@@ -2109,12 +2106,12 @@
         <v>5</v>
       </c>
       <c r="L39">
-        <f t="shared" ref="L39:L100" si="24">K39/G39</f>
-        <v>1.0964912280701754E-3</v>
+        <f t="shared" si="0"/>
+        <v>3.9789909279006844E-2</v>
       </c>
       <c r="M39">
         <f t="shared" si="1"/>
-        <v>1.0964912280701753</v>
+        <v>39.789909279006842</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2152,12 +2149,12 @@
         <v>3</v>
       </c>
       <c r="L40">
-        <f t="shared" si="24"/>
-        <v>6.5789473684210525E-4</v>
+        <f t="shared" si="0"/>
+        <v>2.3873945567404107E-2</v>
       </c>
       <c r="M40">
         <f t="shared" si="1"/>
-        <v>0.6578947368421052</v>
+        <v>23.873945567404107</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2195,7 +2192,7 @@
         <v>7</v>
       </c>
       <c r="L41">
-        <f t="shared" ref="L41:L101" si="25">K41/F41</f>
+        <f t="shared" si="0"/>
         <v>5.5705872990609584E-2</v>
       </c>
       <c r="M41">
@@ -2235,12 +2232,12 @@
         <v>1</v>
       </c>
       <c r="L42">
-        <f t="shared" ref="L42:L103" si="26">K42/G42</f>
-        <v>2.1929824561403509E-4</v>
+        <f t="shared" si="0"/>
+        <v>7.9579818558013684E-3</v>
       </c>
       <c r="M42">
         <f t="shared" si="1"/>
-        <v>0.2192982456140351</v>
+        <v>7.9579818558013686</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2275,12 +2272,12 @@
         <v>2</v>
       </c>
       <c r="L43">
-        <f t="shared" si="26"/>
-        <v>4.3859649122807018E-4</v>
+        <f t="shared" si="0"/>
+        <v>1.5915963711602737E-2</v>
       </c>
       <c r="M43">
         <f t="shared" si="1"/>
-        <v>0.43859649122807021</v>
+        <v>15.915963711602737</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2315,7 +2312,7 @@
         <v>17</v>
       </c>
       <c r="L44">
-        <f t="shared" ref="L44:L104" si="27">K44/F44</f>
+        <f t="shared" si="0"/>
         <v>0.1320901320901321</v>
       </c>
       <c r="M44">
@@ -2355,12 +2352,12 @@
         <v>6</v>
       </c>
       <c r="L45">
-        <f t="shared" ref="L45:L106" si="28">K45/G45</f>
-        <v>8.3333333333333339E-4</v>
+        <f t="shared" si="0"/>
+        <v>4.6620046620046623E-2</v>
       </c>
       <c r="M45">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>46.620046620046622</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2386,7 +2383,7 @@
         <v>55.9</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>21</v>
@@ -2395,12 +2392,12 @@
         <v>3</v>
       </c>
       <c r="L46">
-        <f t="shared" si="28"/>
-        <v>4.1666666666666669E-4</v>
+        <f t="shared" si="0"/>
+        <v>2.3310023310023312E-2</v>
       </c>
       <c r="M46">
         <f t="shared" si="1"/>
-        <v>0.41666666666666669</v>
+        <v>23.310023310023311</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2432,7 +2429,7 @@
         <v>25</v>
       </c>
       <c r="L47">
-        <f t="shared" ref="L47:L107" si="29">K47/F47</f>
+        <f t="shared" si="0"/>
         <v>0.19425019425019427</v>
       </c>
       <c r="M47">
@@ -2463,7 +2460,7 @@
         <v>55.9</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>12</v>
@@ -2472,12 +2469,12 @@
         <v>10</v>
       </c>
       <c r="L48">
-        <f t="shared" ref="L48:L109" si="30">K48/G48</f>
-        <v>1.3888888888888889E-3</v>
+        <f t="shared" si="0"/>
+        <v>7.770007770007771E-2</v>
       </c>
       <c r="M48">
         <f t="shared" si="1"/>
-        <v>1.3888888888888888</v>
+        <v>77.700077700077713</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2503,18 +2500,18 @@
         <v>55.9</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K49" s="1">
         <v>4</v>
       </c>
       <c r="L49">
-        <f t="shared" si="30"/>
-        <v>5.5555555555555556E-4</v>
+        <f t="shared" si="0"/>
+        <v>3.1080031080031083E-2</v>
       </c>
       <c r="M49">
         <f t="shared" si="1"/>
-        <v>0.55555555555555558</v>
+        <v>31.080031080031084</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2546,7 +2543,7 @@
         <v>7</v>
       </c>
       <c r="L50">
-        <f t="shared" ref="L50:L110" si="31">K50/F50</f>
+        <f t="shared" si="0"/>
         <v>5.4390054390054392E-2</v>
       </c>
       <c r="M50">
@@ -2577,18 +2574,18 @@
         <v>55.9</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K51" s="1">
         <v>1</v>
       </c>
       <c r="L51">
-        <f t="shared" ref="L51:L112" si="32">K51/G51</f>
-        <v>1.3888888888888889E-4</v>
+        <f t="shared" si="0"/>
+        <v>7.7700077700077709E-3</v>
       </c>
       <c r="M51">
         <f t="shared" si="1"/>
-        <v>0.1388888888888889</v>
+        <v>7.770007770007771</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2620,12 +2617,12 @@
         <v>3</v>
       </c>
       <c r="L52">
-        <f t="shared" si="32"/>
-        <v>4.1666666666666669E-4</v>
+        <f t="shared" si="0"/>
+        <v>2.3310023310023312E-2</v>
       </c>
       <c r="M52">
         <f t="shared" si="1"/>
-        <v>0.41666666666666669</v>
+        <v>23.310023310023311</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2660,7 +2657,7 @@
         <v>1</v>
       </c>
       <c r="L53">
-        <f t="shared" ref="L53:L113" si="33">K53/F53</f>
+        <f t="shared" si="0"/>
         <v>7.7700077700077709E-3</v>
       </c>
       <c r="M53">
@@ -2691,7 +2688,7 @@
         <v>55.9</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>17</v>
@@ -2700,12 +2697,12 @@
         <v>1</v>
       </c>
       <c r="L54">
-        <f t="shared" ref="L54:L115" si="34">K54/G54</f>
-        <v>1.3888888888888889E-4</v>
+        <f t="shared" si="0"/>
+        <v>7.7700077700077709E-3</v>
       </c>
       <c r="M54">
         <f t="shared" si="1"/>
-        <v>0.1388888888888889</v>
+        <v>7.770007770007771</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2731,7 +2728,7 @@
         <v>58.9</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>12</v>
@@ -2740,12 +2737,12 @@
         <v>28</v>
       </c>
       <c r="L55">
-        <f t="shared" si="34"/>
-        <v>3.6914963744232037E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.21756021756021757</v>
       </c>
       <c r="M55">
         <f t="shared" si="1"/>
-        <v>3.6914963744232034</v>
+        <v>217.56021756021758</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2771,7 +2768,7 @@
         <v>58.9</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>21</v>
@@ -2780,7 +2777,7 @@
         <v>4</v>
       </c>
       <c r="L56">
-        <f t="shared" ref="L56:L116" si="35">K56/F56</f>
+        <f t="shared" si="0"/>
         <v>3.1080031080031083E-2</v>
       </c>
       <c r="M56">
@@ -2817,12 +2814,12 @@
         <v>25</v>
       </c>
       <c r="L57">
-        <f t="shared" ref="L57:L118" si="36">K57/G57</f>
-        <v>3.2959789057350032E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.19425019425019427</v>
       </c>
       <c r="M57">
         <f t="shared" si="1"/>
-        <v>3.2959789057350033</v>
+        <v>194.25019425019426</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2857,12 +2854,12 @@
         <v>15</v>
       </c>
       <c r="L58">
-        <f t="shared" si="36"/>
-        <v>1.977587343441002E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.11655011655011656</v>
       </c>
       <c r="M58">
         <f t="shared" si="1"/>
-        <v>1.9775873434410021</v>
+        <v>116.55011655011656</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2888,13 +2885,13 @@
         <v>58.9</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K59" s="1">
         <v>1</v>
       </c>
       <c r="L59">
-        <f t="shared" ref="L59:L119" si="37">K59/F59</f>
+        <f t="shared" si="0"/>
         <v>7.7700077700077709E-3</v>
       </c>
       <c r="M59">
@@ -2931,12 +2928,12 @@
         <v>2</v>
       </c>
       <c r="L60">
-        <f t="shared" ref="L60:L121" si="38">K60/G60</f>
-        <v>2.6367831245880025E-4</v>
+        <f t="shared" si="0"/>
+        <v>1.5540015540015542E-2</v>
       </c>
       <c r="M60">
         <f t="shared" si="1"/>
-        <v>0.26367831245880025</v>
+        <v>15.540015540015542</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2971,12 +2968,12 @@
         <v>1</v>
       </c>
       <c r="L61">
-        <f t="shared" si="38"/>
-        <v>1.3183915622940013E-4</v>
+        <f t="shared" si="0"/>
+        <v>7.7700077700077709E-3</v>
       </c>
       <c r="M61">
         <f t="shared" si="1"/>
-        <v>0.13183915622940012</v>
+        <v>7.770007770007771</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3002,7 +2999,7 @@
         <v>58.9</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>17</v>
@@ -3011,7 +3008,7 @@
         <v>3</v>
       </c>
       <c r="L62">
-        <f t="shared" ref="L62" si="39">K62/F62</f>
+        <f t="shared" si="0"/>
         <v>2.3310023310023312E-2</v>
       </c>
       <c r="M62">
@@ -3042,18 +3039,18 @@
         <v>58.9</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K63" s="1">
         <v>2</v>
       </c>
       <c r="L63">
-        <f t="shared" ref="L63:L64" si="40">K63/G63</f>
-        <v>2.6367831245880025E-4</v>
+        <f t="shared" si="0"/>
+        <v>1.5540015540015542E-2</v>
       </c>
       <c r="M63">
         <f t="shared" si="1"/>
-        <v>0.26367831245880025</v>
+        <v>15.540015540015542</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3088,12 +3085,12 @@
         <v>10</v>
       </c>
       <c r="L64">
-        <f t="shared" si="40"/>
-        <v>1.2370113805047005E-3</v>
+        <f t="shared" si="0"/>
+        <v>7.770007770007771E-2</v>
       </c>
       <c r="M64">
         <f t="shared" si="1"/>
-        <v>1.2370113805047005</v>
+        <v>77.700077700077713</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3119,7 +3116,7 @@
         <v>62.8</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>21</v>
@@ -3128,7 +3125,7 @@
         <v>4</v>
       </c>
       <c r="L65">
-        <f t="shared" si="21"/>
+        <f t="shared" si="0"/>
         <v>3.1080031080031083E-2</v>
       </c>
       <c r="M65">
@@ -3165,12 +3162,12 @@
         <v>29</v>
       </c>
       <c r="L66">
-        <f t="shared" si="22"/>
-        <v>3.587333003463632E-3</v>
+        <f t="shared" si="0"/>
+        <v>0.22533022533022534</v>
       </c>
       <c r="M66">
         <f t="shared" si="1"/>
-        <v>3.5873330034636322</v>
+        <v>225.33022533022535</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3196,7 +3193,7 @@
         <v>62.8</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>17</v>
@@ -3205,12 +3202,12 @@
         <v>4</v>
       </c>
       <c r="L67">
-        <f t="shared" si="22"/>
-        <v>4.9480455220188031E-4</v>
+        <f t="shared" ref="L67:L130" si="2">(K67/F67)</f>
+        <v>3.1080031080031083E-2</v>
       </c>
       <c r="M67">
         <f t="shared" si="1"/>
-        <v>0.4948045522018803</v>
+        <v>31.080031080031084</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3236,7 +3233,7 @@
         <v>62.8</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>12</v>
@@ -3245,7 +3242,7 @@
         <v>24</v>
       </c>
       <c r="L68">
-        <f t="shared" si="23"/>
+        <f t="shared" si="2"/>
         <v>0.18648018648018649</v>
       </c>
       <c r="M68">
@@ -3282,12 +3279,12 @@
         <v>2</v>
       </c>
       <c r="L69">
-        <f t="shared" si="24"/>
-        <v>2.4740227610094015E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.5540015540015542E-2</v>
       </c>
       <c r="M69">
-        <f t="shared" ref="M69:M132" si="41">L69*1000</f>
-        <v>0.24740227610094015</v>
+        <f t="shared" ref="M69:M132" si="3">L69*1000</f>
+        <v>15.540015540015542</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3313,18 +3310,18 @@
         <v>62.8</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K70" s="1">
         <v>4</v>
       </c>
       <c r="L70">
-        <f t="shared" si="24"/>
-        <v>4.9480455220188031E-4</v>
+        <f t="shared" si="2"/>
+        <v>3.1080031080031083E-2</v>
       </c>
       <c r="M70">
-        <f t="shared" si="41"/>
-        <v>0.4948045522018803</v>
+        <f t="shared" si="3"/>
+        <v>31.080031080031084</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3359,11 +3356,11 @@
         <v>1</v>
       </c>
       <c r="L71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="2"/>
         <v>7.7700077700077709E-3</v>
       </c>
       <c r="M71">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>7.770007770007771</v>
       </c>
     </row>
@@ -3396,12 +3393,12 @@
         <v>1</v>
       </c>
       <c r="L72">
-        <f t="shared" si="26"/>
-        <v>1.2370113805047008E-4</v>
+        <f t="shared" si="2"/>
+        <v>7.7700077700077709E-3</v>
       </c>
       <c r="M72">
-        <f t="shared" si="41"/>
-        <v>0.12370113805047007</v>
+        <f t="shared" si="3"/>
+        <v>7.770007770007771</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3427,21 +3424,21 @@
         <v>62.8</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K73" s="1">
         <v>3</v>
       </c>
       <c r="L73">
-        <f t="shared" si="26"/>
-        <v>3.7110341415141018E-4</v>
+        <f t="shared" si="2"/>
+        <v>2.3310023310023312E-2</v>
       </c>
       <c r="M73">
-        <f t="shared" si="41"/>
-        <v>0.37110341415141018</v>
+        <f t="shared" si="3"/>
+        <v>23.310023310023311</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3476,11 +3473,11 @@
         <v>1</v>
       </c>
       <c r="L74">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>7.7700077700077709E-3</v>
       </c>
       <c r="M74">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>7.770007770007771</v>
       </c>
     </row>
@@ -3519,12 +3516,12 @@
         <v>14</v>
       </c>
       <c r="L75">
-        <f t="shared" si="28"/>
-        <v>4.6666666666666671E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.20527859237536655</v>
       </c>
       <c r="M75">
-        <f t="shared" si="41"/>
-        <v>4.666666666666667</v>
+        <f t="shared" si="3"/>
+        <v>205.27859237536654</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3553,7 +3550,7 @@
         <v>44</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>12</v>
@@ -3562,12 +3559,12 @@
         <v>15</v>
       </c>
       <c r="L76">
-        <f t="shared" si="28"/>
-        <v>5.0000000000000001E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.21994134897360704</v>
       </c>
       <c r="M76">
-        <f t="shared" si="41"/>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>219.94134897360703</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3602,11 +3599,11 @@
         <v>5</v>
       </c>
       <c r="L77">
-        <f t="shared" si="29"/>
+        <f t="shared" si="2"/>
         <v>7.3313782991202336E-2</v>
       </c>
       <c r="M77">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>73.313782991202331</v>
       </c>
     </row>
@@ -3642,12 +3639,12 @@
         <v>22</v>
       </c>
       <c r="L78">
-        <f t="shared" si="30"/>
-        <v>7.3333333333333332E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.32258064516129031</v>
       </c>
       <c r="M78">
-        <f t="shared" si="41"/>
-        <v>7.333333333333333</v>
+        <f t="shared" si="3"/>
+        <v>322.58064516129031</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3676,7 +3673,7 @@
         <v>44</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>21</v>
@@ -3685,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="L79">
-        <f t="shared" si="30"/>
-        <v>1E-3</v>
+        <f t="shared" si="2"/>
+        <v>4.3988269794721403E-2</v>
       </c>
       <c r="M79">
-        <f t="shared" si="41"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>43.988269794721404</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3719,17 +3716,17 @@
         <v>44</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K80" s="1">
         <v>8</v>
       </c>
       <c r="L80">
-        <f t="shared" si="31"/>
+        <f t="shared" si="2"/>
         <v>0.11730205278592375</v>
       </c>
       <c r="M80">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>117.30205278592375</v>
       </c>
     </row>
@@ -3759,7 +3756,7 @@
         <v>44</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>17</v>
@@ -3768,12 +3765,12 @@
         <v>2</v>
       </c>
       <c r="L81">
-        <f t="shared" si="32"/>
-        <v>6.6666666666666664E-4</v>
+        <f t="shared" si="2"/>
+        <v>2.9325513196480937E-2</v>
       </c>
       <c r="M81">
-        <f t="shared" si="41"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="3"/>
+        <v>29.325513196480937</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3808,12 +3805,12 @@
         <v>2</v>
       </c>
       <c r="L82">
-        <f t="shared" si="32"/>
-        <v>6.6666666666666664E-4</v>
+        <f t="shared" si="2"/>
+        <v>2.9325513196480937E-2</v>
       </c>
       <c r="M82">
-        <f t="shared" si="41"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="3"/>
+        <v>29.325513196480937</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3851,11 +3848,11 @@
         <v>3</v>
       </c>
       <c r="L83">
-        <f t="shared" si="33"/>
+        <f t="shared" si="2"/>
         <v>4.3988269794721403E-2</v>
       </c>
       <c r="M83">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>43.988269794721404</v>
       </c>
     </row>
@@ -3894,12 +3891,12 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <f t="shared" si="34"/>
-        <v>3.3333333333333332E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.4662756598240468E-2</v>
       </c>
       <c r="M84">
-        <f t="shared" si="41"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="3"/>
+        <v>14.662756598240469</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3934,12 +3931,12 @@
         <v>18</v>
       </c>
       <c r="L85">
-        <f t="shared" si="34"/>
-        <v>7.1428571428571426E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.26392961876832843</v>
       </c>
       <c r="M85">
-        <f t="shared" si="41"/>
-        <v>7.1428571428571423</v>
+        <f t="shared" si="3"/>
+        <v>263.92961876832845</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3977,11 +3974,11 @@
         <v>11</v>
       </c>
       <c r="L86">
-        <f t="shared" si="35"/>
+        <f t="shared" si="2"/>
         <v>0.16129032258064516</v>
       </c>
       <c r="M86">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>161.29032258064515</v>
       </c>
     </row>
@@ -4011,7 +4008,7 @@
         <v>37</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>12</v>
@@ -4020,12 +4017,12 @@
         <v>13</v>
       </c>
       <c r="L87">
-        <f t="shared" si="36"/>
-        <v>5.1587301587301586E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.1906158357771261</v>
       </c>
       <c r="M87">
-        <f t="shared" si="41"/>
-        <v>5.1587301587301591</v>
+        <f t="shared" si="3"/>
+        <v>190.61583577712611</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4054,18 +4051,18 @@
         <v>37</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K88" s="1">
         <v>8</v>
       </c>
       <c r="L88">
-        <f t="shared" si="36"/>
-        <v>3.1746031746031746E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.11730205278592375</v>
       </c>
       <c r="M88">
-        <f t="shared" si="41"/>
-        <v>3.1746031746031744</v>
+        <f t="shared" si="3"/>
+        <v>117.30205278592375</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4100,11 +4097,11 @@
         <v>3</v>
       </c>
       <c r="L89">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>4.3988269794721403E-2</v>
       </c>
       <c r="M89">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>43.988269794721404</v>
       </c>
     </row>
@@ -4134,7 +4131,7 @@
         <v>37</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>17</v>
@@ -4143,12 +4140,12 @@
         <v>4</v>
       </c>
       <c r="L90">
-        <f t="shared" si="38"/>
-        <v>1.5873015873015873E-3</v>
+        <f t="shared" si="2"/>
+        <v>5.8651026392961873E-2</v>
       </c>
       <c r="M90">
-        <f t="shared" si="41"/>
-        <v>1.5873015873015872</v>
+        <f t="shared" si="3"/>
+        <v>58.651026392961874</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4177,7 +4174,7 @@
         <v>37</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>21</v>
@@ -4186,12 +4183,12 @@
         <v>2</v>
       </c>
       <c r="L91">
-        <f t="shared" si="38"/>
-        <v>7.9365079365079365E-4</v>
+        <f t="shared" si="2"/>
+        <v>2.9325513196480937E-2</v>
       </c>
       <c r="M91">
-        <f t="shared" si="41"/>
-        <v>0.79365079365079361</v>
+        <f t="shared" si="3"/>
+        <v>29.325513196480937</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4226,11 +4223,11 @@
         <v>3</v>
       </c>
       <c r="L92">
-        <f t="shared" ref="L92" si="42">K92/F92</f>
+        <f t="shared" si="2"/>
         <v>4.3988269794721403E-2</v>
       </c>
       <c r="M92">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>43.988269794721404</v>
       </c>
     </row>
@@ -4269,12 +4266,12 @@
         <v>1</v>
       </c>
       <c r="L93">
-        <f t="shared" ref="L93:L94" si="43">K93/G93</f>
-        <v>3.9682539682539683E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.4662756598240468E-2</v>
       </c>
       <c r="M93">
-        <f t="shared" si="41"/>
-        <v>0.3968253968253968</v>
+        <f t="shared" si="3"/>
+        <v>14.662756598240469</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4309,12 +4306,12 @@
         <v>18</v>
       </c>
       <c r="L94">
-        <f t="shared" si="43"/>
-        <v>6.2500000000000003E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.26392961876832843</v>
       </c>
       <c r="M94">
-        <f t="shared" si="41"/>
-        <v>6.25</v>
+        <f t="shared" si="3"/>
+        <v>263.92961876832845</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4352,11 +4349,11 @@
         <v>11</v>
       </c>
       <c r="L95">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>0.16129032258064516</v>
       </c>
       <c r="M95">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>161.29032258064515</v>
       </c>
     </row>
@@ -4386,7 +4383,7 @@
         <v>42.2</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>12</v>
@@ -4395,12 +4392,12 @@
         <v>13</v>
       </c>
       <c r="L96">
-        <f t="shared" si="22"/>
-        <v>4.5138888888888885E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.1906158357771261</v>
       </c>
       <c r="M96">
-        <f t="shared" si="41"/>
-        <v>4.5138888888888884</v>
+        <f t="shared" si="3"/>
+        <v>190.61583577712611</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4429,18 +4426,18 @@
         <v>42.2</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K97" s="1">
         <v>8</v>
       </c>
       <c r="L97">
-        <f t="shared" si="22"/>
-        <v>2.7777777777777779E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.11730205278592375</v>
       </c>
       <c r="M97">
-        <f t="shared" si="41"/>
-        <v>2.7777777777777777</v>
+        <f t="shared" si="3"/>
+        <v>117.30205278592375</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4475,11 +4472,11 @@
         <v>3</v>
       </c>
       <c r="L98">
-        <f t="shared" si="23"/>
+        <f t="shared" si="2"/>
         <v>4.3988269794721403E-2</v>
       </c>
       <c r="M98">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>43.988269794721404</v>
       </c>
     </row>
@@ -4509,7 +4506,7 @@
         <v>42.2</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>17</v>
@@ -4518,12 +4515,12 @@
         <v>4</v>
       </c>
       <c r="L99">
-        <f t="shared" si="24"/>
-        <v>1.3888888888888889E-3</v>
+        <f t="shared" si="2"/>
+        <v>5.8651026392961873E-2</v>
       </c>
       <c r="M99">
-        <f t="shared" si="41"/>
-        <v>1.3888888888888888</v>
+        <f t="shared" si="3"/>
+        <v>58.651026392961874</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4552,7 +4549,7 @@
         <v>42.2</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>21</v>
@@ -4561,12 +4558,12 @@
         <v>2</v>
       </c>
       <c r="L100">
-        <f t="shared" si="24"/>
-        <v>6.9444444444444447E-4</v>
+        <f t="shared" si="2"/>
+        <v>2.9325513196480937E-2</v>
       </c>
       <c r="M100">
-        <f t="shared" si="41"/>
-        <v>0.69444444444444442</v>
+        <f t="shared" si="3"/>
+        <v>29.325513196480937</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4601,11 +4598,11 @@
         <v>3</v>
       </c>
       <c r="L101">
-        <f t="shared" si="25"/>
+        <f t="shared" si="2"/>
         <v>4.3988269794721403E-2</v>
       </c>
       <c r="M101">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>43.988269794721404</v>
       </c>
     </row>
@@ -4644,12 +4641,12 @@
         <v>1</v>
       </c>
       <c r="L102">
-        <f t="shared" si="26"/>
-        <v>3.4722222222222224E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.4662756598240468E-2</v>
       </c>
       <c r="M102">
-        <f t="shared" si="41"/>
-        <v>0.34722222222222221</v>
+        <f t="shared" si="3"/>
+        <v>14.662756598240469</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4687,12 +4684,12 @@
         <v>36</v>
       </c>
       <c r="L103">
-        <f t="shared" si="26"/>
-        <v>6.5454545454545453E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.32727272727272727</v>
       </c>
       <c r="M103">
-        <f t="shared" si="41"/>
-        <v>6.545454545454545</v>
+        <f t="shared" si="3"/>
+        <v>327.27272727272725</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4721,7 +4718,7 @@
         <v>43.2</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>21</v>
@@ -4730,11 +4727,11 @@
         <v>15</v>
       </c>
       <c r="L104">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>0.13636363636363635</v>
       </c>
       <c r="M104">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>136.36363636363635</v>
       </c>
     </row>
@@ -4764,7 +4761,7 @@
         <v>43.2</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>12</v>
@@ -4773,12 +4770,12 @@
         <v>28</v>
       </c>
       <c r="L105">
-        <f t="shared" si="28"/>
-        <v>5.0909090909090913E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.25454545454545452</v>
       </c>
       <c r="M105">
-        <f t="shared" si="41"/>
-        <v>5.0909090909090908</v>
+        <f t="shared" si="3"/>
+        <v>254.54545454545453</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4813,12 +4810,12 @@
         <v>5</v>
       </c>
       <c r="L106">
-        <f t="shared" si="28"/>
-        <v>9.0909090909090909E-4</v>
+        <f t="shared" si="2"/>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="M106">
-        <f t="shared" si="41"/>
-        <v>0.90909090909090906</v>
+        <f t="shared" si="3"/>
+        <v>45.454545454545453</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4853,11 +4850,11 @@
         <v>12</v>
       </c>
       <c r="L107">
-        <f t="shared" si="29"/>
+        <f t="shared" si="2"/>
         <v>0.10909090909090909</v>
       </c>
       <c r="M107">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>109.09090909090908</v>
       </c>
     </row>
@@ -4893,12 +4890,12 @@
         <v>1</v>
       </c>
       <c r="L108">
-        <f t="shared" si="30"/>
-        <v>1.8181818181818181E-4</v>
+        <f t="shared" si="2"/>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="M108">
-        <f t="shared" si="41"/>
-        <v>0.1818181818181818</v>
+        <f t="shared" si="3"/>
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4927,18 +4924,18 @@
         <v>43.2</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K109" s="1">
         <v>2</v>
       </c>
       <c r="L109">
-        <f t="shared" si="30"/>
-        <v>3.6363636363636361E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.8181818181818181E-2</v>
       </c>
       <c r="M109">
-        <f t="shared" si="41"/>
-        <v>0.36363636363636359</v>
+        <f t="shared" si="3"/>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4973,11 +4970,11 @@
         <v>3</v>
       </c>
       <c r="L110">
-        <f t="shared" si="31"/>
+        <f t="shared" si="2"/>
         <v>2.7272727272727271E-2</v>
       </c>
       <c r="M110">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>27.27272727272727</v>
       </c>
     </row>
@@ -5016,12 +5013,12 @@
         <v>2</v>
       </c>
       <c r="L111">
-        <f t="shared" si="32"/>
-        <v>3.6363636363636361E-4</v>
+        <f t="shared" si="2"/>
+        <v>1.8181818181818181E-2</v>
       </c>
       <c r="M111">
-        <f t="shared" si="41"/>
-        <v>0.36363636363636359</v>
+        <f t="shared" si="3"/>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="112" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5050,7 +5047,7 @@
         <v>43.2</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>17</v>
@@ -5059,12 +5056,12 @@
         <v>1</v>
       </c>
       <c r="L112">
-        <f t="shared" si="32"/>
-        <v>1.8181818181818181E-4</v>
+        <f t="shared" si="2"/>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="M112">
-        <f t="shared" si="41"/>
-        <v>0.1818181818181818</v>
+        <f t="shared" si="3"/>
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5093,17 +5090,17 @@
         <v>43.2</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K113" s="1">
         <v>4</v>
       </c>
       <c r="L113">
-        <f t="shared" si="33"/>
+        <f t="shared" si="2"/>
         <v>3.6363636363636362E-2</v>
       </c>
       <c r="M113">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>36.36363636363636</v>
       </c>
     </row>
@@ -5139,12 +5136,12 @@
         <v>36</v>
       </c>
       <c r="L114">
-        <f t="shared" si="34"/>
-        <v>4.4444444444444444E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.32727272727272727</v>
       </c>
       <c r="M114">
-        <f t="shared" si="41"/>
-        <v>4.4444444444444446</v>
+        <f t="shared" si="3"/>
+        <v>327.27272727272725</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5182,12 +5179,12 @@
         <v>36</v>
       </c>
       <c r="L115">
-        <f t="shared" si="34"/>
-        <v>4.4444444444444444E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.32727272727272727</v>
       </c>
       <c r="M115">
-        <f t="shared" si="41"/>
-        <v>4.4444444444444446</v>
+        <f t="shared" si="3"/>
+        <v>327.27272727272725</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5216,7 +5213,7 @@
         <v>63.5</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>12</v>
@@ -5225,11 +5222,11 @@
         <v>40</v>
       </c>
       <c r="L116">
-        <f t="shared" si="35"/>
+        <f t="shared" si="2"/>
         <v>0.36363636363636365</v>
       </c>
       <c r="M116">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>363.63636363636363</v>
       </c>
     </row>
@@ -5265,12 +5262,12 @@
         <v>5</v>
       </c>
       <c r="L117">
-        <f t="shared" si="36"/>
-        <v>6.1728395061728394E-4</v>
+        <f t="shared" si="2"/>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="M117">
-        <f t="shared" si="41"/>
-        <v>0.61728395061728392</v>
+        <f t="shared" si="3"/>
+        <v>45.454545454545453</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5305,12 +5302,12 @@
         <v>12</v>
       </c>
       <c r="L118">
-        <f t="shared" si="36"/>
-        <v>1.4814814814814814E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.10909090909090909</v>
       </c>
       <c r="M118">
-        <f t="shared" si="41"/>
-        <v>1.4814814814814814</v>
+        <f t="shared" si="3"/>
+        <v>109.09090909090908</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5348,11 +5345,11 @@
         <v>5</v>
       </c>
       <c r="L119">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>4.5454545454545456E-2</v>
       </c>
       <c r="M119">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>45.454545454545453</v>
       </c>
     </row>
@@ -5382,7 +5379,7 @@
         <v>63.5</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>17</v>
@@ -5391,12 +5388,12 @@
         <v>7</v>
       </c>
       <c r="L120">
-        <f t="shared" si="38"/>
-        <v>8.6419753086419758E-4</v>
+        <f t="shared" si="2"/>
+        <v>6.363636363636363E-2</v>
       </c>
       <c r="M120">
-        <f t="shared" si="41"/>
-        <v>0.86419753086419759</v>
+        <f t="shared" si="3"/>
+        <v>63.636363636363633</v>
       </c>
     </row>
     <row r="121" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5425,18 +5422,18 @@
         <v>63.5</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K121" s="1">
         <v>3</v>
       </c>
       <c r="L121">
-        <f t="shared" si="38"/>
-        <v>3.7037037037037035E-4</v>
+        <f t="shared" si="2"/>
+        <v>2.7272727272727271E-2</v>
       </c>
       <c r="M121">
-        <f t="shared" si="41"/>
-        <v>0.37037037037037035</v>
+        <f t="shared" si="3"/>
+        <v>27.27272727272727</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5474,11 +5471,11 @@
         <v>1</v>
       </c>
       <c r="L122">
-        <f t="shared" ref="L122" si="44">K122/F122</f>
+        <f t="shared" si="2"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="M122">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>9.0909090909090899</v>
       </c>
     </row>
@@ -5508,7 +5505,7 @@
         <v>63.5</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J123" s="1" t="s">
         <v>21</v>
@@ -5517,12 +5514,12 @@
         <v>10</v>
       </c>
       <c r="L123">
-        <f t="shared" ref="L123:L124" si="45">K123/G123</f>
-        <v>1.2345679012345679E-3</v>
+        <f t="shared" si="2"/>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="M123">
-        <f t="shared" si="41"/>
-        <v>1.2345679012345678</v>
+        <f t="shared" si="3"/>
+        <v>90.909090909090907</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5551,18 +5548,18 @@
         <v>63.5</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K124" s="1">
         <v>7</v>
       </c>
       <c r="L124">
-        <f t="shared" si="45"/>
-        <v>8.6419753086419758E-4</v>
+        <f t="shared" si="2"/>
+        <v>6.363636363636363E-2</v>
       </c>
       <c r="M124">
-        <f t="shared" si="41"/>
-        <v>0.86419753086419759</v>
+        <f t="shared" si="3"/>
+        <v>63.636363636363633</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5597,11 +5594,11 @@
         <v>29</v>
       </c>
       <c r="L125">
-        <f t="shared" ref="L125:L185" si="46">K125/F125</f>
+        <f t="shared" si="2"/>
         <v>0.26363636363636361</v>
       </c>
       <c r="M125">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>263.63636363636363</v>
       </c>
     </row>
@@ -5640,12 +5637,12 @@
         <v>40</v>
       </c>
       <c r="L126">
-        <f t="shared" ref="L126:L187" si="47">K126/G126</f>
-        <v>5.4054054054054057E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.36363636363636365</v>
       </c>
       <c r="M126">
-        <f t="shared" si="41"/>
-        <v>5.4054054054054053</v>
+        <f t="shared" si="3"/>
+        <v>363.63636363636363</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5674,7 +5671,7 @@
         <v>58.1</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J127" s="1" t="s">
         <v>21</v>
@@ -5683,12 +5680,12 @@
         <v>14</v>
       </c>
       <c r="L127">
-        <f t="shared" si="47"/>
-        <v>1.8918918918918919E-3</v>
+        <f t="shared" si="2"/>
+        <v>0.12727272727272726</v>
       </c>
       <c r="M127">
-        <f t="shared" si="41"/>
-        <v>1.8918918918918919</v>
+        <f t="shared" si="3"/>
+        <v>127.27272727272727</v>
       </c>
     </row>
     <row r="128" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5717,7 +5714,7 @@
         <v>58.1</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J128" s="1" t="s">
         <v>12</v>
@@ -5726,11 +5723,11 @@
         <v>22</v>
       </c>
       <c r="L128">
-        <f t="shared" ref="L128:L188" si="48">K128/F128</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="M128">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
     </row>
@@ -5766,12 +5763,12 @@
         <v>1</v>
       </c>
       <c r="L129">
-        <f t="shared" ref="L129:L190" si="49">K129/G129</f>
-        <v>1.3513513513513514E-4</v>
+        <f t="shared" si="2"/>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="M129">
-        <f t="shared" si="41"/>
-        <v>0.13513513513513514</v>
+        <f t="shared" si="3"/>
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5800,7 +5797,7 @@
         <v>58.1</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J130" s="1" t="s">
         <v>17</v>
@@ -5809,12 +5806,12 @@
         <v>8</v>
       </c>
       <c r="L130">
-        <f t="shared" si="49"/>
-        <v>1.0810810810810811E-3</v>
+        <f t="shared" si="2"/>
+        <v>7.2727272727272724E-2</v>
       </c>
       <c r="M130">
-        <f t="shared" si="41"/>
-        <v>1.0810810810810811</v>
+        <f t="shared" si="3"/>
+        <v>72.72727272727272</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5849,11 +5846,11 @@
         <v>13</v>
       </c>
       <c r="L131">
-        <f t="shared" ref="L131:L191" si="50">K131/F131</f>
+        <f t="shared" ref="L131:L194" si="4">(K131/F131)</f>
         <v>0.11818181818181818</v>
       </c>
       <c r="M131">
-        <f t="shared" si="41"/>
+        <f t="shared" si="3"/>
         <v>118.18181818181817</v>
       </c>
     </row>
@@ -5883,18 +5880,18 @@
         <v>58.1</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K132" s="1">
         <v>8</v>
       </c>
       <c r="L132">
-        <f t="shared" ref="L132:L193" si="51">K132/G132</f>
-        <v>1.0810810810810811E-3</v>
+        <f t="shared" si="4"/>
+        <v>7.2727272727272724E-2</v>
       </c>
       <c r="M132">
-        <f t="shared" si="41"/>
-        <v>1.0810810810810811</v>
+        <f t="shared" si="3"/>
+        <v>72.72727272727272</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5932,12 +5929,12 @@
         <v>3</v>
       </c>
       <c r="L133">
-        <f t="shared" si="51"/>
-        <v>4.0540540540540538E-4</v>
+        <f t="shared" si="4"/>
+        <v>2.7272727272727271E-2</v>
       </c>
       <c r="M133">
-        <f t="shared" ref="M133:M196" si="52">L133*1000</f>
-        <v>0.40540540540540537</v>
+        <f t="shared" ref="M133:M196" si="5">L133*1000</f>
+        <v>27.27272727272727</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5966,17 +5963,17 @@
         <v>58.1</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K134" s="1">
         <v>1</v>
       </c>
       <c r="L134">
-        <f t="shared" ref="L134:L194" si="53">K134/F134</f>
+        <f t="shared" si="4"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="M134">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>9.0909090909090899</v>
       </c>
     </row>
@@ -6012,12 +6009,12 @@
         <v>1</v>
       </c>
       <c r="L135">
-        <f t="shared" ref="L135:L196" si="54">K135/G135</f>
-        <v>1.3513513513513514E-4</v>
+        <f t="shared" si="4"/>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="M135">
-        <f t="shared" si="52"/>
-        <v>0.13513513513513514</v>
+        <f t="shared" si="5"/>
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6052,12 +6049,12 @@
         <v>2</v>
       </c>
       <c r="L136">
-        <f t="shared" si="54"/>
-        <v>2.7027027027027027E-4</v>
+        <f t="shared" si="4"/>
+        <v>1.8181818181818181E-2</v>
       </c>
       <c r="M136">
-        <f t="shared" si="52"/>
-        <v>0.27027027027027029</v>
+        <f t="shared" si="5"/>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="137" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6095,11 +6092,11 @@
         <v>1</v>
       </c>
       <c r="L137">
-        <f t="shared" ref="L137:L197" si="55">K137/F137</f>
+        <f t="shared" si="4"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="M137">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>9.0909090909090899</v>
       </c>
     </row>
@@ -6132,12 +6129,12 @@
         <v>8</v>
       </c>
       <c r="L138">
-        <f t="shared" ref="L138:L199" si="56">K138/G138</f>
-        <v>5.0793650793650794E-3</v>
+        <f t="shared" si="4"/>
+        <v>5.2253429131286742E-2</v>
       </c>
       <c r="M138">
-        <f t="shared" si="52"/>
-        <v>5.0793650793650791</v>
+        <f t="shared" si="5"/>
+        <v>52.253429131286744</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6169,12 +6166,12 @@
         <v>2</v>
       </c>
       <c r="L139">
-        <f t="shared" si="56"/>
-        <v>1.2698412698412698E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.3063357282821686E-2</v>
       </c>
       <c r="M139">
-        <f t="shared" si="52"/>
-        <v>1.2698412698412698</v>
+        <f t="shared" si="5"/>
+        <v>13.063357282821686</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6200,7 +6197,7 @@
         <v>10.3</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J140" s="1" t="s">
         <v>12</v>
@@ -6209,11 +6206,11 @@
         <v>6</v>
       </c>
       <c r="L140">
-        <f t="shared" ref="L140:L200" si="57">K140/F140</f>
+        <f t="shared" si="4"/>
         <v>3.9190071848465055E-2</v>
       </c>
       <c r="M140">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>39.190071848465053</v>
       </c>
     </row>
@@ -6246,12 +6243,12 @@
         <v>18</v>
       </c>
       <c r="L141">
-        <f t="shared" ref="L141:L202" si="58">K141/G141</f>
-        <v>1.1428571428571429E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.11757021554539517</v>
       </c>
       <c r="M141">
-        <f t="shared" si="52"/>
-        <v>11.428571428571429</v>
+        <f t="shared" si="5"/>
+        <v>117.57021554539517</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6286,12 +6283,12 @@
         <v>1</v>
       </c>
       <c r="L142">
-        <f t="shared" si="58"/>
-        <v>6.3492063492063492E-4</v>
+        <f t="shared" si="4"/>
+        <v>6.5316786414108428E-3</v>
       </c>
       <c r="M142">
-        <f t="shared" si="52"/>
-        <v>0.63492063492063489</v>
+        <f t="shared" si="5"/>
+        <v>6.531678641410843</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6323,11 +6320,11 @@
         <v>3</v>
       </c>
       <c r="L143">
-        <f t="shared" ref="L143:L203" si="59">K143/F143</f>
+        <f t="shared" si="4"/>
         <v>1.9595035924232528E-2</v>
       </c>
       <c r="M143">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>19.595035924232526</v>
       </c>
     </row>
@@ -6363,12 +6360,12 @@
         <v>2</v>
       </c>
       <c r="L144">
-        <f t="shared" ref="L144:L205" si="60">K144/G144</f>
-        <v>1.2698412698412698E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.3063357282821686E-2</v>
       </c>
       <c r="M144">
-        <f t="shared" si="52"/>
-        <v>1.2698412698412698</v>
+        <f t="shared" si="5"/>
+        <v>13.063357282821686</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6394,7 +6391,7 @@
         <v>10.3</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>21</v>
@@ -6403,12 +6400,12 @@
         <v>1</v>
       </c>
       <c r="L145">
-        <f t="shared" si="60"/>
-        <v>6.3492063492063492E-4</v>
+        <f t="shared" si="4"/>
+        <v>6.5316786414108428E-3</v>
       </c>
       <c r="M145">
-        <f t="shared" si="52"/>
-        <v>0.63492063492063489</v>
+        <f t="shared" si="5"/>
+        <v>6.531678641410843</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6443,11 +6440,11 @@
         <v>1</v>
       </c>
       <c r="L146">
-        <f t="shared" ref="L146:L206" si="61">K146/F146</f>
+        <f t="shared" si="4"/>
         <v>6.5316786414108428E-3</v>
       </c>
       <c r="M146">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>6.531678641410843</v>
       </c>
     </row>
@@ -6480,12 +6477,12 @@
         <v>3</v>
       </c>
       <c r="L147">
-        <f t="shared" ref="L147:L208" si="62">K147/G147</f>
-        <v>2.5000000000000001E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.9595035924232528E-2</v>
       </c>
       <c r="M147">
-        <f t="shared" si="52"/>
-        <v>2.5</v>
+        <f t="shared" si="5"/>
+        <v>19.595035924232526</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6517,12 +6514,12 @@
         <v>13</v>
       </c>
       <c r="L148">
-        <f t="shared" si="62"/>
-        <v>1.0833333333333334E-2</v>
+        <f t="shared" si="4"/>
+        <v>8.491182233834095E-2</v>
       </c>
       <c r="M148">
-        <f t="shared" si="52"/>
-        <v>10.833333333333334</v>
+        <f t="shared" si="5"/>
+        <v>84.911822338340954</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6548,17 +6545,17 @@
         <v>7.84</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K149" s="1">
         <v>1</v>
       </c>
       <c r="L149">
-        <f t="shared" ref="L149:L209" si="63">K149/F149</f>
+        <f t="shared" si="4"/>
         <v>6.5316786414108428E-3</v>
       </c>
       <c r="M149">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>6.531678641410843</v>
       </c>
     </row>
@@ -6591,12 +6588,12 @@
         <v>4</v>
       </c>
       <c r="L150">
-        <f t="shared" ref="L150:L211" si="64">K150/G150</f>
-        <v>3.3333333333333335E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.6126714565643371E-2</v>
       </c>
       <c r="M150">
-        <f t="shared" si="52"/>
-        <v>3.3333333333333335</v>
+        <f t="shared" si="5"/>
+        <v>26.126714565643372</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6631,12 +6628,12 @@
         <v>3</v>
       </c>
       <c r="L151">
-        <f t="shared" si="64"/>
-        <v>2.5000000000000001E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.9595035924232528E-2</v>
       </c>
       <c r="M151">
-        <f t="shared" si="52"/>
-        <v>2.5</v>
+        <f t="shared" si="5"/>
+        <v>19.595035924232526</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6662,7 +6659,7 @@
         <v>7.84</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>12</v>
@@ -6671,11 +6668,11 @@
         <v>5</v>
       </c>
       <c r="L152">
-        <f t="shared" ref="L152" si="65">K152/F152</f>
+        <f t="shared" si="4"/>
         <v>3.2658393207054215E-2</v>
       </c>
       <c r="M152">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>32.658393207054218</v>
       </c>
     </row>
@@ -6702,7 +6699,7 @@
         <v>7.84</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>17</v>
@@ -6711,12 +6708,12 @@
         <v>2</v>
       </c>
       <c r="L153">
-        <f t="shared" ref="L153:L154" si="66">K153/G153</f>
-        <v>1.6666666666666668E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.3063357282821686E-2</v>
       </c>
       <c r="M153">
-        <f t="shared" si="52"/>
-        <v>1.6666666666666667</v>
+        <f t="shared" si="5"/>
+        <v>13.063357282821686</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6748,12 +6745,12 @@
         <v>1</v>
       </c>
       <c r="L154">
-        <f t="shared" si="66"/>
-        <v>8.3333333333333339E-4</v>
+        <f t="shared" si="4"/>
+        <v>6.5316786414108428E-3</v>
       </c>
       <c r="M154">
-        <f t="shared" si="52"/>
-        <v>0.83333333333333337</v>
+        <f t="shared" si="5"/>
+        <v>6.531678641410843</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6788,11 +6785,11 @@
         <v>1</v>
       </c>
       <c r="L155">
-        <f t="shared" si="46"/>
+        <f t="shared" si="4"/>
         <v>6.5316786414108428E-3</v>
       </c>
       <c r="M155">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>6.531678641410843</v>
       </c>
     </row>
@@ -6825,12 +6822,12 @@
         <v>9</v>
       </c>
       <c r="L156">
-        <f t="shared" si="47"/>
-        <v>5.8536585365853658E-3</v>
+        <f t="shared" si="4"/>
+        <v>5.8785107772697583E-2</v>
       </c>
       <c r="M156">
-        <f t="shared" si="52"/>
-        <v>5.8536585365853657</v>
+        <f t="shared" si="5"/>
+        <v>58.785107772697586</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6862,12 +6859,12 @@
         <v>16</v>
       </c>
       <c r="L157">
-        <f t="shared" si="47"/>
-        <v>1.040650406504065E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.10450685826257348</v>
       </c>
       <c r="M157">
-        <f t="shared" si="52"/>
-        <v>10.40650406504065</v>
+        <f t="shared" si="5"/>
+        <v>104.50685826257349</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6902,11 +6899,11 @@
         <v>3</v>
       </c>
       <c r="L158">
-        <f t="shared" si="48"/>
+        <f t="shared" si="4"/>
         <v>1.9595035924232528E-2</v>
       </c>
       <c r="M158">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>19.595035924232526</v>
       </c>
     </row>
@@ -6942,12 +6939,12 @@
         <v>1</v>
       </c>
       <c r="L159">
-        <f t="shared" si="49"/>
-        <v>6.5040650406504065E-4</v>
+        <f t="shared" si="4"/>
+        <v>6.5316786414108428E-3</v>
       </c>
       <c r="M159">
-        <f t="shared" si="52"/>
-        <v>0.65040650406504064</v>
+        <f t="shared" si="5"/>
+        <v>6.531678641410843</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6973,7 +6970,7 @@
         <v>10.042999999999999</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>12</v>
@@ -6982,12 +6979,12 @@
         <v>4</v>
       </c>
       <c r="L160">
-        <f t="shared" si="49"/>
-        <v>2.6016260162601626E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.6126714565643371E-2</v>
       </c>
       <c r="M160">
-        <f t="shared" si="52"/>
-        <v>2.6016260162601625</v>
+        <f t="shared" si="5"/>
+        <v>26.126714565643372</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7013,20 +7010,20 @@
         <v>10.042999999999999</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K161" s="1">
         <v>1</v>
       </c>
       <c r="L161">
-        <f t="shared" si="50"/>
+        <f t="shared" si="4"/>
         <v>6.5316786414108428E-3</v>
       </c>
       <c r="M161">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>6.531678641410843</v>
       </c>
     </row>
@@ -7053,7 +7050,7 @@
         <v>10.042999999999999</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>17</v>
@@ -7062,12 +7059,12 @@
         <v>2</v>
       </c>
       <c r="L162">
-        <f t="shared" si="51"/>
-        <v>1.3008130081300813E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.3063357282821686E-2</v>
       </c>
       <c r="M162">
-        <f t="shared" si="52"/>
-        <v>1.3008130081300813</v>
+        <f t="shared" si="5"/>
+        <v>13.063357282821686</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7099,12 +7096,12 @@
         <v>1</v>
       </c>
       <c r="L163">
-        <f t="shared" si="51"/>
-        <v>6.5040650406504065E-4</v>
+        <f t="shared" si="4"/>
+        <v>6.5316786414108428E-3</v>
       </c>
       <c r="M163">
-        <f t="shared" si="52"/>
-        <v>0.65040650406504064</v>
+        <f t="shared" si="5"/>
+        <v>6.531678641410843</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7136,11 +7133,11 @@
         <v>2</v>
       </c>
       <c r="L164">
-        <f t="shared" si="53"/>
+        <f t="shared" si="4"/>
         <v>1.3063357282821686E-2</v>
       </c>
       <c r="M164">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>13.063357282821686</v>
       </c>
     </row>
@@ -7176,12 +7173,12 @@
         <v>2</v>
       </c>
       <c r="L165">
-        <f t="shared" si="54"/>
-        <v>1.3008130081300813E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.3063357282821686E-2</v>
       </c>
       <c r="M165">
-        <f t="shared" si="52"/>
-        <v>1.3008130081300813</v>
+        <f t="shared" si="5"/>
+        <v>13.063357282821686</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7213,12 +7210,12 @@
         <v>13</v>
       </c>
       <c r="L166">
-        <f t="shared" si="54"/>
-        <v>2.7083333333333334E-2</v>
+        <f t="shared" si="4"/>
+        <v>9.814283557300317E-2</v>
       </c>
       <c r="M166">
-        <f t="shared" si="52"/>
-        <v>27.083333333333336</v>
+        <f t="shared" si="5"/>
+        <v>98.142835573003168</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7253,11 +7250,11 @@
         <v>3</v>
       </c>
       <c r="L167">
-        <f t="shared" si="55"/>
+        <f t="shared" si="4"/>
         <v>2.2648346670693039E-2</v>
       </c>
       <c r="M167">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>22.648346670693041</v>
       </c>
     </row>
@@ -7284,21 +7281,21 @@
         <v>3.62</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K168" s="1">
         <v>8</v>
       </c>
       <c r="L168">
-        <f t="shared" si="56"/>
-        <v>1.6666666666666666E-2</v>
+        <f t="shared" si="4"/>
+        <v>6.03955911218481E-2</v>
       </c>
       <c r="M168">
-        <f t="shared" si="52"/>
-        <v>16.666666666666668</v>
+        <f t="shared" si="5"/>
+        <v>60.395591121848099</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7324,7 +7321,7 @@
         <v>3.62</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J169" s="1" t="s">
         <v>12</v>
@@ -7333,12 +7330,12 @@
         <v>8</v>
       </c>
       <c r="L169">
-        <f t="shared" si="56"/>
-        <v>1.6666666666666666E-2</v>
+        <f t="shared" si="4"/>
+        <v>6.03955911218481E-2</v>
       </c>
       <c r="M169">
-        <f t="shared" si="52"/>
-        <v>16.666666666666668</v>
+        <f t="shared" si="5"/>
+        <v>60.395591121848099</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7373,11 +7370,11 @@
         <v>1</v>
       </c>
       <c r="L170">
-        <f t="shared" si="57"/>
+        <f t="shared" si="4"/>
         <v>7.5494488902310124E-3</v>
       </c>
       <c r="M170">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>7.5494488902310124</v>
       </c>
     </row>
@@ -7407,18 +7404,18 @@
         <v>15</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K171" s="1">
         <v>4</v>
       </c>
       <c r="L171">
-        <f t="shared" si="58"/>
-        <v>8.3333333333333332E-3</v>
+        <f t="shared" si="4"/>
+        <v>3.019779556092405E-2</v>
       </c>
       <c r="M171">
-        <f t="shared" si="52"/>
-        <v>8.3333333333333339</v>
+        <f t="shared" si="5"/>
+        <v>30.19779556092405</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7444,18 +7441,18 @@
         <v>3.62</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K172" s="1">
         <v>1</v>
       </c>
       <c r="L172">
-        <f t="shared" si="58"/>
-        <v>2.0833333333333333E-3</v>
+        <f t="shared" si="4"/>
+        <v>7.5494488902310124E-3</v>
       </c>
       <c r="M172">
-        <f t="shared" si="52"/>
-        <v>2.0833333333333335</v>
+        <f t="shared" si="5"/>
+        <v>7.5494488902310124</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7481,7 +7478,7 @@
         <v>3.62</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J173" s="1" t="s">
         <v>17</v>
@@ -7490,11 +7487,11 @@
         <v>1</v>
       </c>
       <c r="L173">
-        <f t="shared" si="59"/>
+        <f t="shared" si="4"/>
         <v>7.5494488902310124E-3</v>
       </c>
       <c r="M173">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>7.5494488902310124</v>
       </c>
     </row>
@@ -7527,12 +7524,12 @@
         <v>1</v>
       </c>
       <c r="L174">
-        <f t="shared" si="60"/>
-        <v>2.0833333333333333E-3</v>
+        <f t="shared" si="4"/>
+        <v>7.5494488902310124E-3</v>
       </c>
       <c r="M174">
-        <f t="shared" si="52"/>
-        <v>2.0833333333333335</v>
+        <f t="shared" si="5"/>
+        <v>7.5494488902310124</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7567,12 +7564,12 @@
         <v>11</v>
       </c>
       <c r="L175">
-        <f t="shared" si="60"/>
-        <v>1.4550264550264549E-2</v>
+        <f t="shared" si="4"/>
+        <v>8.3043937792541142E-2</v>
       </c>
       <c r="M175">
-        <f t="shared" si="52"/>
-        <v>14.550264550264549</v>
+        <f t="shared" si="5"/>
+        <v>83.043937792541143</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7598,20 +7595,20 @@
         <v>5.71</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K176" s="1">
         <v>2</v>
       </c>
       <c r="L176">
-        <f t="shared" si="61"/>
+        <f t="shared" si="4"/>
         <v>1.5098897780462025E-2</v>
       </c>
       <c r="M176">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>15.098897780462025</v>
       </c>
     </row>
@@ -7644,12 +7641,12 @@
         <v>21</v>
       </c>
       <c r="L177">
-        <f t="shared" si="62"/>
-        <v>2.7777777777777776E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.15853842669485127</v>
       </c>
       <c r="M177">
-        <f t="shared" si="52"/>
-        <v>27.777777777777775</v>
+        <f t="shared" si="5"/>
+        <v>158.53842669485127</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7675,7 +7672,7 @@
         <v>5.71</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>17</v>
@@ -7684,12 +7681,12 @@
         <v>6</v>
       </c>
       <c r="L178">
-        <f t="shared" si="62"/>
-        <v>7.9365079365079361E-3</v>
+        <f t="shared" si="4"/>
+        <v>4.5296693341386078E-2</v>
       </c>
       <c r="M178">
-        <f t="shared" si="52"/>
-        <v>7.9365079365079358</v>
+        <f t="shared" si="5"/>
+        <v>45.296693341386081</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7715,7 +7712,7 @@
         <v>5.71</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J179" s="1" t="s">
         <v>12</v>
@@ -7724,11 +7721,11 @@
         <v>9</v>
       </c>
       <c r="L179">
-        <f t="shared" si="63"/>
+        <f t="shared" si="4"/>
         <v>6.7945040012079114E-2</v>
       </c>
       <c r="M179">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>67.945040012079119</v>
       </c>
     </row>
@@ -7761,12 +7758,12 @@
         <v>2</v>
       </c>
       <c r="L180">
-        <f t="shared" si="64"/>
-        <v>2.6455026455026454E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.5098897780462025E-2</v>
       </c>
       <c r="M180">
-        <f t="shared" si="52"/>
-        <v>2.6455026455026456</v>
+        <f t="shared" si="5"/>
+        <v>15.098897780462025</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7795,18 +7792,18 @@
         <v>15</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K181" s="1">
         <v>8</v>
       </c>
       <c r="L181">
-        <f t="shared" si="64"/>
-        <v>1.0582010582010581E-2</v>
+        <f t="shared" si="4"/>
+        <v>6.03955911218481E-2</v>
       </c>
       <c r="M181">
-        <f t="shared" si="52"/>
-        <v>10.582010582010582</v>
+        <f t="shared" si="5"/>
+        <v>60.395591121848099</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7832,17 +7829,17 @@
         <v>5.71</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K182" s="1">
         <v>1</v>
       </c>
       <c r="L182">
-        <f t="shared" ref="L182" si="67">K182/F182</f>
+        <f t="shared" si="4"/>
         <v>7.5494488902310124E-3</v>
       </c>
       <c r="M182">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>7.5494488902310124</v>
       </c>
     </row>
@@ -7875,12 +7872,12 @@
         <v>2</v>
       </c>
       <c r="L183">
-        <f t="shared" ref="L183:L184" si="68">K183/G183</f>
-        <v>2.6455026455026454E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.5098897780462025E-2</v>
       </c>
       <c r="M183">
-        <f t="shared" si="52"/>
-        <v>2.6455026455026456</v>
+        <f t="shared" si="5"/>
+        <v>15.098897780462025</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7906,21 +7903,21 @@
         <v>5.71</v>
       </c>
       <c r="I184" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J184" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J184" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="K184" s="1">
         <v>1</v>
       </c>
       <c r="L184">
-        <f t="shared" si="68"/>
-        <v>1.3227513227513227E-3</v>
+        <f t="shared" si="4"/>
+        <v>7.5494488902310124E-3</v>
       </c>
       <c r="M184">
-        <f t="shared" si="52"/>
-        <v>1.3227513227513228</v>
+        <f t="shared" si="5"/>
+        <v>7.5494488902310124</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7952,11 +7949,11 @@
         <v>1</v>
       </c>
       <c r="L185">
-        <f t="shared" si="46"/>
+        <f t="shared" si="4"/>
         <v>7.5494488902310124E-3</v>
       </c>
       <c r="M185">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>7.5494488902310124</v>
       </c>
     </row>
@@ -7989,12 +7986,12 @@
         <v>12</v>
       </c>
       <c r="L186">
-        <f t="shared" si="47"/>
-        <v>2.0408163265306121E-2</v>
+        <f t="shared" si="4"/>
+        <v>9.0593386682772156E-2</v>
       </c>
       <c r="M186">
-        <f t="shared" si="52"/>
-        <v>20.408163265306122</v>
+        <f t="shared" si="5"/>
+        <v>90.593386682772163</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8020,7 +8017,7 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J187" s="1" t="s">
         <v>12</v>
@@ -8029,12 +8026,12 @@
         <v>12</v>
       </c>
       <c r="L187">
-        <f t="shared" si="47"/>
-        <v>2.0408163265306121E-2</v>
+        <f t="shared" si="4"/>
+        <v>9.0593386682772156E-2</v>
       </c>
       <c r="M187">
-        <f t="shared" si="52"/>
-        <v>20.408163265306122</v>
+        <f t="shared" si="5"/>
+        <v>90.593386682772163</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8069,11 +8066,11 @@
         <v>6</v>
       </c>
       <c r="L188">
-        <f t="shared" si="48"/>
+        <f t="shared" si="4"/>
         <v>4.5296693341386078E-2</v>
       </c>
       <c r="M188">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>45.296693341386081</v>
       </c>
     </row>
@@ -8109,12 +8106,12 @@
         <v>2</v>
       </c>
       <c r="L189">
-        <f t="shared" si="49"/>
-        <v>3.4013605442176869E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.5098897780462025E-2</v>
       </c>
       <c r="M189">
-        <f t="shared" si="52"/>
-        <v>3.4013605442176869</v>
+        <f t="shared" si="5"/>
+        <v>15.098897780462025</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8140,21 +8137,21 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K190" s="1">
         <v>7</v>
       </c>
       <c r="L190">
-        <f t="shared" si="49"/>
-        <v>1.1904761904761904E-2</v>
+        <f t="shared" si="4"/>
+        <v>5.2846142231617085E-2</v>
       </c>
       <c r="M190">
-        <f t="shared" si="52"/>
-        <v>11.904761904761903</v>
+        <f t="shared" si="5"/>
+        <v>52.846142231617087</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8180,17 +8177,17 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K191" s="1">
         <v>1</v>
       </c>
       <c r="L191">
-        <f t="shared" si="50"/>
+        <f t="shared" si="4"/>
         <v>7.5494488902310124E-3</v>
       </c>
       <c r="M191">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>7.5494488902310124</v>
       </c>
     </row>
@@ -8220,18 +8217,18 @@
         <v>15</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K192" s="1">
         <v>1</v>
       </c>
       <c r="L192">
-        <f t="shared" si="51"/>
-        <v>1.7006802721088435E-3</v>
+        <f t="shared" si="4"/>
+        <v>7.5494488902310124E-3</v>
       </c>
       <c r="M192">
-        <f t="shared" si="52"/>
-        <v>1.7006802721088434</v>
+        <f t="shared" si="5"/>
+        <v>7.5494488902310124</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8257,18 +8254,18 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K193" s="1">
         <v>2</v>
       </c>
       <c r="L193">
-        <f t="shared" si="51"/>
-        <v>3.4013605442176869E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.5098897780462025E-2</v>
       </c>
       <c r="M193">
-        <f t="shared" si="52"/>
-        <v>3.4013605442176869</v>
+        <f t="shared" si="5"/>
+        <v>15.098897780462025</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8294,7 +8291,7 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>17</v>
@@ -8303,11 +8300,11 @@
         <v>4</v>
       </c>
       <c r="L194">
-        <f t="shared" si="53"/>
+        <f t="shared" si="4"/>
         <v>3.019779556092405E-2</v>
       </c>
       <c r="M194">
-        <f t="shared" si="52"/>
+        <f t="shared" si="5"/>
         <v>30.19779556092405</v>
       </c>
     </row>
@@ -8340,12 +8337,12 @@
         <v>1</v>
       </c>
       <c r="L195">
-        <f t="shared" si="54"/>
-        <v>1.7006802721088435E-3</v>
+        <f t="shared" ref="L195:L258" si="6">(K195/F195)</f>
+        <v>7.5494488902310124E-3</v>
       </c>
       <c r="M195">
-        <f t="shared" si="52"/>
-        <v>1.7006802721088434</v>
+        <f t="shared" si="5"/>
+        <v>7.5494488902310124</v>
       </c>
     </row>
     <row r="196" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8377,12 +8374,12 @@
         <v>6</v>
       </c>
       <c r="L196">
-        <f t="shared" si="54"/>
-        <v>2.8985507246376812E-3</v>
+        <f t="shared" si="6"/>
+        <v>4.5457989241609209E-2</v>
       </c>
       <c r="M196">
-        <f t="shared" si="52"/>
-        <v>2.8985507246376812</v>
+        <f t="shared" si="5"/>
+        <v>45.457989241609212</v>
       </c>
     </row>
     <row r="197" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8414,11 +8411,11 @@
         <v>25</v>
       </c>
       <c r="L197">
-        <f t="shared" si="55"/>
+        <f t="shared" si="6"/>
         <v>0.18940828850670505</v>
       </c>
       <c r="M197">
-        <f t="shared" ref="M197:M260" si="69">L197*1000</f>
+        <f t="shared" ref="M197:M260" si="7">L197*1000</f>
         <v>189.40828850670505</v>
       </c>
     </row>
@@ -8448,18 +8445,18 @@
         <v>15</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K198" s="1">
         <v>5</v>
       </c>
       <c r="L198">
-        <f t="shared" si="56"/>
-        <v>2.4154589371980675E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.7881657701341005E-2</v>
       </c>
       <c r="M198">
-        <f t="shared" si="69"/>
-        <v>2.4154589371980677</v>
+        <f t="shared" si="7"/>
+        <v>37.881657701341005</v>
       </c>
     </row>
     <row r="199" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8494,12 +8491,12 @@
         <v>4</v>
       </c>
       <c r="L199">
-        <f t="shared" si="56"/>
-        <v>1.9323671497584541E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.0305326161072805E-2</v>
       </c>
       <c r="M199">
-        <f t="shared" si="69"/>
-        <v>1.932367149758454</v>
+        <f t="shared" si="7"/>
+        <v>30.305326161072806</v>
       </c>
     </row>
     <row r="200" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8534,11 +8531,11 @@
         <v>2</v>
       </c>
       <c r="L200">
-        <f t="shared" si="57"/>
+        <f t="shared" si="6"/>
         <v>1.5152663080536402E-2</v>
       </c>
       <c r="M200">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>15.152663080536403</v>
       </c>
     </row>
@@ -8565,21 +8562,21 @@
         <v>15.68</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K201" s="1">
         <v>4</v>
       </c>
       <c r="L201">
-        <f t="shared" si="58"/>
-        <v>1.9323671497584541E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.0305326161072805E-2</v>
       </c>
       <c r="M201">
-        <f t="shared" si="69"/>
-        <v>1.932367149758454</v>
+        <f t="shared" si="7"/>
+        <v>30.305326161072806</v>
       </c>
     </row>
     <row r="202" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8611,12 +8608,12 @@
         <v>3</v>
       </c>
       <c r="L202">
-        <f t="shared" si="58"/>
-        <v>1.4492753623188406E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.2728994620804605E-2</v>
       </c>
       <c r="M202">
-        <f t="shared" si="69"/>
-        <v>1.4492753623188406</v>
+        <f t="shared" si="7"/>
+        <v>22.728994620804606</v>
       </c>
     </row>
     <row r="203" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8642,7 +8639,7 @@
         <v>15.68</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J203" s="1" t="s">
         <v>12</v>
@@ -8651,11 +8648,11 @@
         <v>12</v>
       </c>
       <c r="L203">
-        <f t="shared" si="59"/>
+        <f t="shared" si="6"/>
         <v>9.0915978483218418E-2</v>
       </c>
       <c r="M203">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>90.915978483218424</v>
       </c>
     </row>
@@ -8688,12 +8685,12 @@
         <v>6</v>
       </c>
       <c r="L204">
-        <f t="shared" si="60"/>
-        <v>2.8985507246376812E-3</v>
+        <f t="shared" si="6"/>
+        <v>4.5457989241609209E-2</v>
       </c>
       <c r="M204">
-        <f t="shared" si="69"/>
-        <v>2.8985507246376812</v>
+        <f t="shared" si="7"/>
+        <v>45.457989241609212</v>
       </c>
     </row>
     <row r="205" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8728,12 +8725,12 @@
         <v>1</v>
       </c>
       <c r="L205">
-        <f t="shared" si="60"/>
-        <v>4.8309178743961351E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.5763315402682012E-3</v>
       </c>
       <c r="M205">
-        <f t="shared" si="69"/>
-        <v>0.48309178743961351</v>
+        <f t="shared" si="7"/>
+        <v>7.5763315402682014</v>
       </c>
     </row>
     <row r="206" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8765,11 +8762,11 @@
         <v>1</v>
       </c>
       <c r="L206">
-        <f t="shared" si="61"/>
+        <f t="shared" si="6"/>
         <v>7.5763315402682012E-3</v>
       </c>
       <c r="M206">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.5763315402682014</v>
       </c>
     </row>
@@ -8802,12 +8799,12 @@
         <v>6</v>
       </c>
       <c r="L207">
-        <f t="shared" si="62"/>
-        <v>4.4444444444444444E-3</v>
+        <f t="shared" si="6"/>
+        <v>4.5457989241609209E-2</v>
       </c>
       <c r="M207">
-        <f t="shared" si="69"/>
-        <v>4.4444444444444446</v>
+        <f t="shared" si="7"/>
+        <v>45.457989241609212</v>
       </c>
     </row>
     <row r="208" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8839,12 +8836,12 @@
         <v>18</v>
       </c>
       <c r="L208">
-        <f t="shared" si="62"/>
-        <v>1.3333333333333334E-2</v>
+        <f t="shared" si="6"/>
+        <v>0.13637396772482763</v>
       </c>
       <c r="M208">
-        <f t="shared" si="69"/>
-        <v>13.333333333333334</v>
+        <f t="shared" si="7"/>
+        <v>136.37396772482762</v>
       </c>
     </row>
     <row r="209" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8876,11 +8873,11 @@
         <v>5</v>
       </c>
       <c r="L209">
-        <f t="shared" si="63"/>
+        <f t="shared" si="6"/>
         <v>3.7881657701341005E-2</v>
       </c>
       <c r="M209">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>37.881657701341005</v>
       </c>
     </row>
@@ -8907,7 +8904,7 @@
         <v>10.220000000000001</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>12</v>
@@ -8916,12 +8913,12 @@
         <v>5</v>
       </c>
       <c r="L210">
-        <f t="shared" si="64"/>
-        <v>3.7037037037037038E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.7881657701341005E-2</v>
       </c>
       <c r="M210">
-        <f t="shared" si="69"/>
-        <v>3.7037037037037037</v>
+        <f t="shared" si="7"/>
+        <v>37.881657701341005</v>
       </c>
     </row>
     <row r="211" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8953,12 +8950,12 @@
         <v>3</v>
       </c>
       <c r="L211">
-        <f t="shared" si="64"/>
-        <v>2.2222222222222222E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.2728994620804605E-2</v>
       </c>
       <c r="M211">
-        <f t="shared" si="69"/>
-        <v>2.2222222222222223</v>
+        <f t="shared" si="7"/>
+        <v>22.728994620804606</v>
       </c>
     </row>
     <row r="212" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8993,11 +8990,11 @@
         <v>2</v>
       </c>
       <c r="L212">
-        <f t="shared" ref="L212" si="70">K212/F212</f>
+        <f t="shared" si="6"/>
         <v>1.5152663080536402E-2</v>
       </c>
       <c r="M212">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>15.152663080536403</v>
       </c>
     </row>
@@ -9024,21 +9021,21 @@
         <v>10.220000000000001</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K213" s="1">
         <v>3</v>
       </c>
       <c r="L213">
-        <f t="shared" ref="L213:L214" si="71">K213/G213</f>
-        <v>2.2222222222222222E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.2728994620804605E-2</v>
       </c>
       <c r="M213">
-        <f t="shared" si="69"/>
-        <v>2.2222222222222223</v>
+        <f t="shared" si="7"/>
+        <v>22.728994620804606</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9070,12 +9067,12 @@
         <v>1</v>
       </c>
       <c r="L214">
-        <f t="shared" si="71"/>
-        <v>7.407407407407407E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.5763315402682012E-3</v>
       </c>
       <c r="M214">
-        <f t="shared" si="69"/>
-        <v>0.7407407407407407</v>
+        <f t="shared" si="7"/>
+        <v>7.5763315402682014</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9104,17 +9101,17 @@
         <v>15</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K215" s="1">
         <v>1</v>
       </c>
       <c r="L215">
-        <f t="shared" ref="L215:L275" si="72">K215/F215</f>
+        <f t="shared" si="6"/>
         <v>7.5763315402682012E-3</v>
       </c>
       <c r="M215">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.5763315402682014</v>
       </c>
     </row>
@@ -9150,12 +9147,12 @@
         <v>1</v>
       </c>
       <c r="L216">
-        <f t="shared" ref="L216:L277" si="73">K216/G216</f>
-        <v>7.407407407407407E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.5763315402682012E-3</v>
       </c>
       <c r="M216">
-        <f t="shared" si="69"/>
-        <v>0.7407407407407407</v>
+        <f t="shared" si="7"/>
+        <v>7.5763315402682014</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9187,12 +9184,12 @@
         <v>5</v>
       </c>
       <c r="L217">
-        <f t="shared" si="73"/>
-        <v>2.6881720430107529E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.7881657701341005E-2</v>
       </c>
       <c r="M217">
-        <f t="shared" si="69"/>
-        <v>2.688172043010753</v>
+        <f t="shared" si="7"/>
+        <v>37.881657701341005</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9224,11 +9221,11 @@
         <v>23</v>
       </c>
       <c r="L218">
-        <f t="shared" ref="L218:L278" si="74">K218/F218</f>
+        <f t="shared" si="6"/>
         <v>0.17425562542616863</v>
       </c>
       <c r="M218">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>174.25562542616862</v>
       </c>
     </row>
@@ -9261,12 +9258,12 @@
         <v>12</v>
       </c>
       <c r="L219">
-        <f t="shared" ref="L219:L280" si="75">K219/G219</f>
-        <v>6.4516129032258064E-3</v>
+        <f t="shared" si="6"/>
+        <v>9.0915978483218418E-2</v>
       </c>
       <c r="M219">
-        <f t="shared" si="69"/>
-        <v>6.4516129032258061</v>
+        <f t="shared" si="7"/>
+        <v>90.915978483218424</v>
       </c>
     </row>
     <row r="220" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9298,12 +9295,12 @@
         <v>8</v>
       </c>
       <c r="L220">
-        <f t="shared" si="75"/>
-        <v>4.3010752688172043E-3</v>
+        <f t="shared" si="6"/>
+        <v>6.061065232214561E-2</v>
       </c>
       <c r="M220">
-        <f t="shared" si="69"/>
-        <v>4.301075268817204</v>
+        <f t="shared" si="7"/>
+        <v>60.610652322145611</v>
       </c>
     </row>
     <row r="221" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9329,7 +9326,7 @@
         <v>14.1</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>12</v>
@@ -9338,11 +9335,11 @@
         <v>2</v>
       </c>
       <c r="L221">
-        <f t="shared" ref="L221:L281" si="76">K221/F221</f>
+        <f t="shared" si="6"/>
         <v>1.5152663080536402E-2</v>
       </c>
       <c r="M221">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>15.152663080536403</v>
       </c>
     </row>
@@ -9369,21 +9366,21 @@
         <v>14.1</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K222" s="1">
         <v>3</v>
       </c>
       <c r="L222">
-        <f t="shared" ref="L222:L283" si="77">K222/G222</f>
-        <v>1.6129032258064516E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.2728994620804605E-2</v>
       </c>
       <c r="M222">
-        <f t="shared" si="69"/>
-        <v>1.6129032258064515</v>
+        <f t="shared" si="7"/>
+        <v>22.728994620804606</v>
       </c>
     </row>
     <row r="223" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9412,18 +9409,18 @@
         <v>15</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K223" s="1">
         <v>2</v>
       </c>
       <c r="L223">
-        <f t="shared" si="77"/>
-        <v>1.0752688172043011E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.5152663080536402E-2</v>
       </c>
       <c r="M223">
-        <f t="shared" si="69"/>
-        <v>1.075268817204301</v>
+        <f t="shared" si="7"/>
+        <v>15.152663080536403</v>
       </c>
     </row>
     <row r="224" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9458,11 +9455,11 @@
         <v>5</v>
       </c>
       <c r="L224">
-        <f t="shared" ref="L224:L284" si="78">K224/F224</f>
+        <f t="shared" si="6"/>
         <v>3.7881657701341005E-2</v>
       </c>
       <c r="M224">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>37.881657701341005</v>
       </c>
     </row>
@@ -9498,12 +9495,12 @@
         <v>1</v>
       </c>
       <c r="L225">
-        <f t="shared" ref="L225:L286" si="79">K225/G225</f>
-        <v>5.3763440860215054E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.5763315402682012E-3</v>
       </c>
       <c r="M225">
-        <f t="shared" si="69"/>
-        <v>0.5376344086021505</v>
+        <f t="shared" si="7"/>
+        <v>7.5763315402682014</v>
       </c>
     </row>
     <row r="226" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9535,12 +9532,12 @@
         <v>1</v>
       </c>
       <c r="L226">
-        <f t="shared" si="79"/>
-        <v>5.3763440860215054E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.5763315402682012E-3</v>
       </c>
       <c r="M226">
-        <f t="shared" si="69"/>
-        <v>0.5376344086021505</v>
+        <f t="shared" si="7"/>
+        <v>7.5763315402682014</v>
       </c>
     </row>
     <row r="227" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9569,7 +9566,7 @@
         <v>47.88</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>12</v>
@@ -9578,11 +9575,11 @@
         <v>133</v>
       </c>
       <c r="L227">
-        <f t="shared" ref="L227:L287" si="80">K227/F227</f>
+        <f t="shared" si="6"/>
         <v>0.98730606488011274</v>
       </c>
       <c r="M227">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>987.30606488011279</v>
       </c>
     </row>
@@ -9621,12 +9618,12 @@
         <v>3</v>
       </c>
       <c r="L228">
-        <f t="shared" ref="L228:L289" si="81">K228/G228</f>
-        <v>4.6511627906976747E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.2270061613837131E-2</v>
       </c>
       <c r="M228">
-        <f t="shared" si="69"/>
-        <v>0.46511627906976749</v>
+        <f t="shared" si="7"/>
+        <v>22.270061613837132</v>
       </c>
     </row>
     <row r="229" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9664,12 +9661,12 @@
         <v>52</v>
       </c>
       <c r="L229">
-        <f t="shared" si="81"/>
-        <v>8.0620155038759692E-3</v>
+        <f t="shared" si="6"/>
+        <v>0.38601440130651027</v>
       </c>
       <c r="M229">
-        <f t="shared" si="69"/>
-        <v>8.0620155038759691</v>
+        <f t="shared" si="7"/>
+        <v>386.01440130651025</v>
       </c>
     </row>
     <row r="230" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9707,11 +9704,11 @@
         <v>3</v>
       </c>
       <c r="L230">
-        <f t="shared" ref="L230:L290" si="82">K230/F230</f>
+        <f t="shared" si="6"/>
         <v>2.2270061613837131E-2</v>
       </c>
       <c r="M230">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>22.270061613837132</v>
       </c>
     </row>
@@ -9741,21 +9738,21 @@
         <v>47.88</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K231" s="1">
         <v>2</v>
       </c>
       <c r="L231">
-        <f t="shared" ref="L231:L292" si="83">K231/G231</f>
-        <v>3.1007751937984498E-4</v>
+        <f t="shared" si="6"/>
+        <v>1.4846707742558087E-2</v>
       </c>
       <c r="M231">
-        <f t="shared" si="69"/>
-        <v>0.31007751937984496</v>
+        <f t="shared" si="7"/>
+        <v>14.846707742558086</v>
       </c>
     </row>
     <row r="232" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9790,12 +9787,12 @@
         <v>13</v>
       </c>
       <c r="L232">
-        <f t="shared" si="83"/>
-        <v>2.0155038759689923E-3</v>
+        <f t="shared" si="6"/>
+        <v>9.6503600326627567E-2</v>
       </c>
       <c r="M232">
-        <f t="shared" si="69"/>
-        <v>2.0155038759689923</v>
+        <f t="shared" si="7"/>
+        <v>96.503600326627563</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9824,20 +9821,20 @@
         <v>47.880000000000102</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K233" s="1">
         <v>7</v>
       </c>
       <c r="L233">
-        <f t="shared" ref="L233:L293" si="84">K233/F233</f>
+        <f t="shared" si="6"/>
         <v>5.1963477098953305E-2</v>
       </c>
       <c r="M233">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>51.963477098953305</v>
       </c>
     </row>
@@ -9867,21 +9864,21 @@
         <v>47.880000000000102</v>
       </c>
       <c r="I234" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J234" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J234" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="K234" s="1">
         <v>1</v>
       </c>
       <c r="L234">
-        <f t="shared" ref="L234:L295" si="85">K234/G234</f>
-        <v>1.5503875968992249E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.4233538712790434E-3</v>
       </c>
       <c r="M234">
-        <f t="shared" si="69"/>
-        <v>0.15503875968992248</v>
+        <f t="shared" si="7"/>
+        <v>7.4233538712790432</v>
       </c>
     </row>
     <row r="235" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9910,18 +9907,18 @@
         <v>47.880000000000102</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K235" s="1">
         <v>1</v>
       </c>
       <c r="L235">
-        <f t="shared" si="85"/>
-        <v>1.5503875968992249E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.4233538712790434E-3</v>
       </c>
       <c r="M235">
-        <f t="shared" si="69"/>
-        <v>0.15503875968992248</v>
+        <f t="shared" si="7"/>
+        <v>7.4233538712790432</v>
       </c>
     </row>
     <row r="236" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9959,11 +9956,11 @@
         <v>25</v>
       </c>
       <c r="L236">
-        <f t="shared" ref="L236:L296" si="86">K236/F236</f>
+        <f t="shared" si="6"/>
         <v>0.18558384678197609</v>
       </c>
       <c r="M236">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>185.58384678197609</v>
       </c>
     </row>
@@ -9993,7 +9990,7 @@
         <v>57.16</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>12</v>
@@ -10002,12 +9999,12 @@
         <v>101</v>
       </c>
       <c r="L237">
-        <f t="shared" ref="L237:L298" si="87">K237/G237</f>
-        <v>1.3116883116883117E-2</v>
+        <f t="shared" si="6"/>
+        <v>0.74975874099918338</v>
       </c>
       <c r="M237">
-        <f t="shared" si="69"/>
-        <v>13.116883116883118</v>
+        <f t="shared" si="7"/>
+        <v>749.75874099918337</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10036,7 +10033,7 @@
         <v>57.16</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>17</v>
@@ -10045,12 +10042,12 @@
         <v>3</v>
       </c>
       <c r="L238">
-        <f t="shared" si="87"/>
-        <v>3.8961038961038961E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.2270061613837131E-2</v>
       </c>
       <c r="M238">
-        <f t="shared" si="69"/>
-        <v>0.38961038961038963</v>
+        <f t="shared" si="7"/>
+        <v>22.270061613837132</v>
       </c>
     </row>
     <row r="239" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10088,11 +10085,11 @@
         <v>9</v>
       </c>
       <c r="L239">
-        <f t="shared" ref="L239:L299" si="88">K239/F239</f>
+        <f t="shared" si="6"/>
         <v>6.6810184841511397E-2</v>
       </c>
       <c r="M239">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>66.810184841511401</v>
       </c>
     </row>
@@ -10122,21 +10119,21 @@
         <v>57.16</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K240" s="1">
         <v>4</v>
       </c>
       <c r="L240">
-        <f t="shared" ref="L240:L301" si="89">K240/G240</f>
-        <v>5.1948051948051948E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.9693415485116174E-2</v>
       </c>
       <c r="M240">
-        <f t="shared" si="69"/>
-        <v>0.51948051948051943</v>
+        <f t="shared" si="7"/>
+        <v>29.693415485116173</v>
       </c>
     </row>
     <row r="241" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10174,12 +10171,12 @@
         <v>1</v>
       </c>
       <c r="L241">
-        <f t="shared" si="89"/>
-        <v>1.2987012987012987E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.4233538712790434E-3</v>
       </c>
       <c r="M241">
-        <f t="shared" si="69"/>
-        <v>0.12987012987012986</v>
+        <f t="shared" si="7"/>
+        <v>7.4233538712790432</v>
       </c>
     </row>
     <row r="242" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10208,20 +10205,20 @@
         <v>57.16</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K242" s="1">
         <v>1</v>
       </c>
       <c r="L242">
-        <f t="shared" ref="L242" si="90">K242/F242</f>
+        <f t="shared" si="6"/>
         <v>7.4233538712790434E-3</v>
       </c>
       <c r="M242">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.4233538712790432</v>
       </c>
     </row>
@@ -10257,12 +10254,12 @@
         <v>7</v>
       </c>
       <c r="L243">
-        <f t="shared" ref="L243:L244" si="91">K243/G243</f>
-        <v>9.0909090909090909E-4</v>
+        <f t="shared" si="6"/>
+        <v>5.1963477098953305E-2</v>
       </c>
       <c r="M243">
-        <f t="shared" si="69"/>
-        <v>0.90909090909090906</v>
+        <f t="shared" si="7"/>
+        <v>51.963477098953305</v>
       </c>
     </row>
     <row r="244" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10294,18 +10291,18 @@
         <v>15</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K244" s="1">
         <v>2</v>
       </c>
       <c r="L244">
-        <f t="shared" si="91"/>
-        <v>2.5974025974025974E-4</v>
+        <f t="shared" si="6"/>
+        <v>1.4846707742558087E-2</v>
       </c>
       <c r="M244">
-        <f t="shared" si="69"/>
-        <v>0.25974025974025972</v>
+        <f t="shared" si="7"/>
+        <v>14.846707742558086</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10340,11 +10337,11 @@
         <v>1</v>
       </c>
       <c r="L245">
-        <f t="shared" si="72"/>
+        <f t="shared" si="6"/>
         <v>7.4233538712790434E-3</v>
       </c>
       <c r="M245">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.4233538712790432</v>
       </c>
     </row>
@@ -10374,7 +10371,7 @@
         <v>44.54</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>12</v>
@@ -10383,12 +10380,12 @@
         <v>68</v>
       </c>
       <c r="L246">
-        <f t="shared" si="73"/>
-        <v>1.1333333333333334E-2</v>
+        <f t="shared" si="6"/>
+        <v>0.50478806324697501</v>
       </c>
       <c r="M246">
-        <f t="shared" si="69"/>
-        <v>11.333333333333334</v>
+        <f t="shared" si="7"/>
+        <v>504.78806324697501</v>
       </c>
     </row>
     <row r="247" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10423,12 +10420,12 @@
         <v>13</v>
       </c>
       <c r="L247">
-        <f t="shared" si="73"/>
-        <v>2.1666666666666666E-3</v>
+        <f t="shared" si="6"/>
+        <v>9.6503600326627567E-2</v>
       </c>
       <c r="M247">
-        <f t="shared" si="69"/>
-        <v>2.1666666666666665</v>
+        <f t="shared" si="7"/>
+        <v>96.503600326627563</v>
       </c>
     </row>
     <row r="248" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10466,11 +10463,11 @@
         <v>26</v>
       </c>
       <c r="L248">
-        <f t="shared" si="74"/>
+        <f t="shared" si="6"/>
         <v>0.19300720065325513</v>
       </c>
       <c r="M248">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>193.00720065325513</v>
       </c>
     </row>
@@ -10500,21 +10497,21 @@
         <v>44.54</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K249" s="1">
         <v>4</v>
       </c>
       <c r="L249">
-        <f t="shared" si="75"/>
-        <v>6.6666666666666664E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.9693415485116174E-2</v>
       </c>
       <c r="M249">
-        <f t="shared" si="69"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="7"/>
+        <v>29.693415485116173</v>
       </c>
     </row>
     <row r="250" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10552,12 +10549,12 @@
         <v>3</v>
       </c>
       <c r="L250">
-        <f t="shared" si="75"/>
-        <v>5.0000000000000001E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.2270061613837131E-2</v>
       </c>
       <c r="M250">
-        <f t="shared" si="69"/>
-        <v>0.5</v>
+        <f t="shared" si="7"/>
+        <v>22.270061613837132</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10586,20 +10583,20 @@
         <v>44.54</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K251" s="1">
         <v>1</v>
       </c>
       <c r="L251">
-        <f t="shared" si="76"/>
+        <f t="shared" si="6"/>
         <v>7.4233538712790434E-3</v>
       </c>
       <c r="M251">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.4233538712790432</v>
       </c>
     </row>
@@ -10629,7 +10626,7 @@
         <v>44.54</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>17</v>
@@ -10638,12 +10635,12 @@
         <v>1</v>
       </c>
       <c r="L252">
-        <f t="shared" si="77"/>
-        <v>1.6666666666666666E-4</v>
+        <f t="shared" si="6"/>
+        <v>7.4233538712790434E-3</v>
       </c>
       <c r="M252">
-        <f t="shared" si="69"/>
-        <v>0.16666666666666666</v>
+        <f t="shared" si="7"/>
+        <v>7.4233538712790432</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10672,21 +10669,21 @@
         <v>44.54</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K253" s="1">
         <v>3</v>
       </c>
       <c r="L253">
-        <f t="shared" si="77"/>
-        <v>5.0000000000000001E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.2270061613837131E-2</v>
       </c>
       <c r="M253">
-        <f t="shared" si="69"/>
-        <v>0.5</v>
+        <f t="shared" si="7"/>
+        <v>22.270061613837132</v>
       </c>
     </row>
     <row r="254" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10724,11 +10721,11 @@
         <v>1</v>
       </c>
       <c r="L254">
-        <f t="shared" si="78"/>
+        <f t="shared" si="6"/>
         <v>7.4233538712790434E-3</v>
       </c>
       <c r="M254">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.4233538712790432</v>
       </c>
     </row>
@@ -10761,12 +10758,12 @@
         <v>47</v>
       </c>
       <c r="L255">
-        <f t="shared" si="79"/>
-        <v>8.3555555555555553E-3</v>
+        <f t="shared" si="6"/>
+        <v>0.35600666565671862</v>
       </c>
       <c r="M255">
-        <f t="shared" si="69"/>
-        <v>8.3555555555555561</v>
+        <f t="shared" si="7"/>
+        <v>356.00666565671861</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10792,7 +10789,7 @@
         <v>42.61</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>12</v>
@@ -10801,12 +10798,12 @@
         <v>36</v>
       </c>
       <c r="L256">
-        <f t="shared" si="79"/>
-        <v>6.4000000000000003E-3</v>
+        <f t="shared" si="6"/>
+        <v>0.27268595667323131</v>
       </c>
       <c r="M256">
-        <f t="shared" si="69"/>
-        <v>6.4</v>
+        <f t="shared" si="7"/>
+        <v>272.68595667323132</v>
       </c>
     </row>
     <row r="257" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10838,11 +10835,11 @@
         <v>21</v>
       </c>
       <c r="L257">
-        <f t="shared" si="80"/>
+        <f t="shared" si="6"/>
         <v>0.15906680805938492</v>
       </c>
       <c r="M257">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>159.06680805938493</v>
       </c>
     </row>
@@ -10878,12 +10875,12 @@
         <v>3</v>
       </c>
       <c r="L258">
-        <f t="shared" si="81"/>
-        <v>5.3333333333333336E-4</v>
+        <f t="shared" si="6"/>
+        <v>2.2723829722769276E-2</v>
       </c>
       <c r="M258">
-        <f t="shared" si="69"/>
-        <v>0.53333333333333333</v>
+        <f t="shared" si="7"/>
+        <v>22.723829722769278</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10915,12 +10912,12 @@
         <v>7</v>
       </c>
       <c r="L259">
-        <f t="shared" si="81"/>
-        <v>1.2444444444444445E-3</v>
+        <f t="shared" ref="L259:L322" si="8">(K259/F259)</f>
+        <v>5.3022269353128308E-2</v>
       </c>
       <c r="M259">
-        <f t="shared" si="69"/>
-        <v>1.2444444444444445</v>
+        <f t="shared" si="7"/>
+        <v>53.022269353128308</v>
       </c>
     </row>
     <row r="260" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10946,17 +10943,17 @@
         <v>42.61</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K260" s="1">
         <v>1</v>
       </c>
       <c r="L260">
-        <f t="shared" si="82"/>
+        <f t="shared" si="8"/>
         <v>7.5746099075897589E-3</v>
       </c>
       <c r="M260">
-        <f t="shared" si="69"/>
+        <f t="shared" si="7"/>
         <v>7.5746099075897586</v>
       </c>
     </row>
@@ -10992,12 +10989,12 @@
         <v>6</v>
       </c>
       <c r="L261">
-        <f t="shared" si="83"/>
-        <v>1.0666666666666667E-3</v>
+        <f t="shared" si="8"/>
+        <v>4.5447659445538552E-2</v>
       </c>
       <c r="M261">
-        <f t="shared" ref="M261:M324" si="92">L261*1000</f>
-        <v>1.0666666666666667</v>
+        <f t="shared" ref="M261:M324" si="9">L261*1000</f>
+        <v>45.447659445538555</v>
       </c>
     </row>
     <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11023,18 +11020,18 @@
         <v>42.61</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K262" s="1">
         <v>1</v>
       </c>
       <c r="L262">
-        <f t="shared" si="83"/>
-        <v>1.7777777777777779E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.5746099075897589E-3</v>
       </c>
       <c r="M262">
-        <f t="shared" si="92"/>
-        <v>0.17777777777777778</v>
+        <f t="shared" si="9"/>
+        <v>7.5746099075897586</v>
       </c>
     </row>
     <row r="263" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11060,20 +11057,20 @@
         <v>42.61</v>
       </c>
       <c r="I263" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J263" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J263" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="K263" s="1">
         <v>1</v>
       </c>
       <c r="L263">
-        <f t="shared" si="84"/>
+        <f t="shared" si="8"/>
         <v>7.5746099075897589E-3</v>
       </c>
       <c r="M263">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.5746099075897586</v>
       </c>
     </row>
@@ -11100,21 +11097,21 @@
         <v>42.6099999999999</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K264" s="1">
         <v>1</v>
       </c>
       <c r="L264">
-        <f t="shared" si="85"/>
-        <v>1.7777777777777779E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.5746099075897589E-3</v>
       </c>
       <c r="M264">
-        <f t="shared" si="92"/>
-        <v>0.17777777777777778</v>
+        <f t="shared" si="9"/>
+        <v>7.5746099075897586</v>
       </c>
     </row>
     <row r="265" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11140,7 +11137,7 @@
         <v>33.326999999999998</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>12</v>
@@ -11149,12 +11146,12 @@
         <v>12</v>
       </c>
       <c r="L265">
-        <f t="shared" si="85"/>
-        <v>2.7272727272727275E-3</v>
+        <f t="shared" si="8"/>
+        <v>9.0895318891077104E-2</v>
       </c>
       <c r="M265">
-        <f t="shared" si="92"/>
-        <v>2.7272727272727275</v>
+        <f t="shared" si="9"/>
+        <v>90.89531889107711</v>
       </c>
     </row>
     <row r="266" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11186,11 +11183,11 @@
         <v>5</v>
       </c>
       <c r="L266">
-        <f t="shared" si="86"/>
+        <f t="shared" si="8"/>
         <v>3.7873049537948796E-2</v>
       </c>
       <c r="M266">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>37.873049537948795</v>
       </c>
     </row>
@@ -11223,12 +11220,12 @@
         <v>28</v>
       </c>
       <c r="L267">
-        <f t="shared" si="87"/>
-        <v>6.3636363636363638E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.21208907741251323</v>
       </c>
       <c r="M267">
-        <f t="shared" si="92"/>
-        <v>6.3636363636363642</v>
+        <f t="shared" si="9"/>
+        <v>212.08907741251323</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11263,12 +11260,12 @@
         <v>4</v>
       </c>
       <c r="L268">
-        <f t="shared" si="87"/>
-        <v>9.0909090909090909E-4</v>
+        <f t="shared" si="8"/>
+        <v>3.0298439630359036E-2</v>
       </c>
       <c r="M268">
-        <f t="shared" si="92"/>
-        <v>0.90909090909090906</v>
+        <f t="shared" si="9"/>
+        <v>30.298439630359034</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11294,20 +11291,20 @@
         <v>33.326999999999998</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K269" s="1">
         <v>1</v>
       </c>
       <c r="L269">
-        <f t="shared" si="88"/>
+        <f t="shared" si="8"/>
         <v>7.5746099075897589E-3</v>
       </c>
       <c r="M269">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.5746099075897586</v>
       </c>
     </row>
@@ -11334,18 +11331,18 @@
         <v>33.326999999999998</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K270" s="1">
         <v>3</v>
       </c>
       <c r="L270">
-        <f t="shared" si="89"/>
-        <v>6.8181818181818187E-4</v>
+        <f t="shared" si="8"/>
+        <v>2.2723829722769276E-2</v>
       </c>
       <c r="M270">
-        <f t="shared" si="92"/>
-        <v>0.68181818181818188</v>
+        <f t="shared" si="9"/>
+        <v>22.723829722769278</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11377,12 +11374,12 @@
         <v>1</v>
       </c>
       <c r="L271">
-        <f t="shared" si="89"/>
-        <v>2.2727272727272727E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.5746099075897589E-3</v>
       </c>
       <c r="M271">
-        <f t="shared" si="92"/>
-        <v>0.22727272727272727</v>
+        <f t="shared" si="9"/>
+        <v>7.5746099075897586</v>
       </c>
     </row>
     <row r="272" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11417,11 +11414,11 @@
         <v>2</v>
       </c>
       <c r="L272">
-        <f t="shared" ref="L272" si="93">K272/F272</f>
+        <f t="shared" si="8"/>
         <v>1.5149219815179518E-2</v>
       </c>
       <c r="M272">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>15.149219815179517</v>
       </c>
     </row>
@@ -11454,12 +11451,12 @@
         <v>11</v>
       </c>
       <c r="L273">
-        <f t="shared" ref="L273:L274" si="94">K273/G273</f>
-        <v>2.0370370370370369E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.332070898348734E-2</v>
       </c>
       <c r="M273">
-        <f t="shared" si="92"/>
-        <v>2.0370370370370368</v>
+        <f t="shared" si="9"/>
+        <v>83.320708983487336</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11491,12 +11488,12 @@
         <v>21</v>
       </c>
       <c r="L274">
-        <f t="shared" si="94"/>
-        <v>3.8888888888888888E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.15906680805938492</v>
       </c>
       <c r="M274">
-        <f t="shared" si="92"/>
-        <v>3.8888888888888888</v>
+        <f t="shared" si="9"/>
+        <v>159.06680805938493</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11522,20 +11519,20 @@
         <v>40.9</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K275" s="1">
         <v>3</v>
       </c>
       <c r="L275">
-        <f t="shared" si="72"/>
+        <f t="shared" si="8"/>
         <v>2.2723829722769276E-2</v>
       </c>
       <c r="M275">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>22.723829722769278</v>
       </c>
     </row>
@@ -11562,7 +11559,7 @@
         <v>40.9</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>12</v>
@@ -11571,12 +11568,12 @@
         <v>20</v>
       </c>
       <c r="L276">
-        <f t="shared" si="73"/>
-        <v>3.7037037037037038E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.15149219815179518</v>
       </c>
       <c r="M276">
-        <f t="shared" si="92"/>
-        <v>3.7037037037037037</v>
+        <f t="shared" si="9"/>
+        <v>151.49219815179518</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11608,12 +11605,12 @@
         <v>2</v>
       </c>
       <c r="L277">
-        <f t="shared" si="73"/>
-        <v>3.7037037037037035E-4</v>
+        <f t="shared" si="8"/>
+        <v>1.5149219815179518E-2</v>
       </c>
       <c r="M277">
-        <f t="shared" si="92"/>
-        <v>0.37037037037037035</v>
+        <f t="shared" si="9"/>
+        <v>15.149219815179517</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11639,7 +11636,7 @@
         <v>40.9</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J278" s="1" t="s">
         <v>17</v>
@@ -11648,11 +11645,11 @@
         <v>1</v>
       </c>
       <c r="L278">
-        <f t="shared" si="74"/>
+        <f t="shared" si="8"/>
         <v>7.5746099075897589E-3</v>
       </c>
       <c r="M278">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.5746099075897586</v>
       </c>
     </row>
@@ -11691,12 +11688,12 @@
         <v>14</v>
       </c>
       <c r="L279">
-        <f t="shared" si="75"/>
-        <v>6.4814814814814813E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.10702545676936014</v>
       </c>
       <c r="M279">
-        <f t="shared" si="92"/>
-        <v>6.481481481481481</v>
+        <f t="shared" si="9"/>
+        <v>107.02545676936013</v>
       </c>
     </row>
     <row r="280" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11731,12 +11728,12 @@
         <v>2</v>
       </c>
       <c r="L280">
-        <f t="shared" si="75"/>
-        <v>9.2592592592592596E-4</v>
+        <f t="shared" si="8"/>
+        <v>1.5289350967051448E-2</v>
       </c>
       <c r="M280">
-        <f t="shared" si="92"/>
-        <v>0.92592592592592593</v>
+        <f t="shared" si="9"/>
+        <v>15.289350967051448</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11765,20 +11762,20 @@
         <v>16.510000000000002</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K281" s="1">
         <v>3</v>
       </c>
       <c r="L281">
-        <f t="shared" si="76"/>
+        <f t="shared" si="8"/>
         <v>2.2934026450577173E-2</v>
       </c>
       <c r="M281">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>22.934026450577171</v>
       </c>
     </row>
@@ -11817,12 +11814,12 @@
         <v>4</v>
       </c>
       <c r="L282">
-        <f t="shared" si="77"/>
-        <v>1.8518518518518519E-3</v>
+        <f t="shared" si="8"/>
+        <v>3.0578701934102896E-2</v>
       </c>
       <c r="M282">
-        <f t="shared" si="92"/>
-        <v>1.8518518518518519</v>
+        <f t="shared" si="9"/>
+        <v>30.578701934102895</v>
       </c>
     </row>
     <row r="283" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11851,7 +11848,7 @@
         <v>16.510000000000002</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>12</v>
@@ -11860,12 +11857,12 @@
         <v>3</v>
       </c>
       <c r="L283">
-        <f t="shared" si="77"/>
-        <v>1.3888888888888889E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.2934026450577173E-2</v>
       </c>
       <c r="M283">
-        <f t="shared" si="92"/>
-        <v>1.3888888888888888</v>
+        <f t="shared" si="9"/>
+        <v>22.934026450577171</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11900,11 +11897,11 @@
         <v>1</v>
       </c>
       <c r="L284">
-        <f t="shared" si="78"/>
+        <f t="shared" si="8"/>
         <v>7.6446754835257239E-3</v>
       </c>
       <c r="M284">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.6446754835257238</v>
       </c>
     </row>
@@ -11943,12 +11940,12 @@
         <v>5</v>
       </c>
       <c r="L285">
-        <f t="shared" si="79"/>
-        <v>3.1250000000000002E-3</v>
+        <f t="shared" si="8"/>
+        <v>3.8223377417628622E-2</v>
       </c>
       <c r="M285">
-        <f t="shared" si="92"/>
-        <v>3.125</v>
+        <f t="shared" si="9"/>
+        <v>38.223377417628619</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11977,7 +11974,7 @@
         <v>12.23</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>12</v>
@@ -11986,12 +11983,12 @@
         <v>3</v>
       </c>
       <c r="L286">
-        <f t="shared" si="79"/>
-        <v>1.8749999999999999E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.2934026450577173E-2</v>
       </c>
       <c r="M286">
-        <f t="shared" si="92"/>
-        <v>1.875</v>
+        <f t="shared" si="9"/>
+        <v>22.934026450577171</v>
       </c>
     </row>
     <row r="287" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12023,17 +12020,17 @@
         <v>15</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K287" s="1">
         <v>1</v>
       </c>
       <c r="L287">
-        <f t="shared" si="80"/>
+        <f t="shared" si="8"/>
         <v>7.6446754835257239E-3</v>
       </c>
       <c r="M287">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.6446754835257238</v>
       </c>
     </row>
@@ -12069,12 +12066,12 @@
         <v>6</v>
       </c>
       <c r="L288">
-        <f t="shared" si="81"/>
-        <v>3.7499999999999999E-3</v>
+        <f t="shared" si="8"/>
+        <v>4.5868052901154345E-2</v>
       </c>
       <c r="M288">
-        <f t="shared" si="92"/>
-        <v>3.75</v>
+        <f t="shared" si="9"/>
+        <v>45.868052901154343</v>
       </c>
     </row>
     <row r="289" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12112,12 +12109,12 @@
         <v>2</v>
       </c>
       <c r="L289">
-        <f t="shared" si="81"/>
-        <v>1.25E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.5289350967051448E-2</v>
       </c>
       <c r="M289">
-        <f t="shared" si="92"/>
-        <v>1.25</v>
+        <f t="shared" si="9"/>
+        <v>15.289350967051448</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12155,11 +12152,11 @@
         <v>3</v>
       </c>
       <c r="L290">
-        <f t="shared" si="82"/>
+        <f t="shared" si="8"/>
         <v>2.2934026450577173E-2</v>
       </c>
       <c r="M290">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>22.934026450577171</v>
       </c>
     </row>
@@ -12198,12 +12195,12 @@
         <v>11</v>
       </c>
       <c r="L291">
-        <f t="shared" si="83"/>
-        <v>5.4999999999999997E-3</v>
+        <f t="shared" si="8"/>
+        <v>8.4091430318782967E-2</v>
       </c>
       <c r="M291">
-        <f t="shared" si="92"/>
-        <v>5.5</v>
+        <f t="shared" si="9"/>
+        <v>84.091430318782969</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12238,12 +12235,12 @@
         <v>1</v>
       </c>
       <c r="L292">
-        <f t="shared" si="83"/>
-        <v>5.0000000000000001E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.6446754835257239E-3</v>
       </c>
       <c r="M292">
-        <f t="shared" si="92"/>
-        <v>0.5</v>
+        <f t="shared" si="9"/>
+        <v>7.6446754835257238</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12281,11 +12278,11 @@
         <v>1</v>
       </c>
       <c r="L293">
-        <f t="shared" si="84"/>
+        <f t="shared" si="8"/>
         <v>7.6446754835257239E-3</v>
       </c>
       <c r="M293">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.6446754835257238</v>
       </c>
     </row>
@@ -12321,12 +12318,12 @@
         <v>3</v>
       </c>
       <c r="L294">
-        <f t="shared" si="85"/>
-        <v>1.5E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.2934026450577173E-2</v>
       </c>
       <c r="M294">
-        <f t="shared" si="92"/>
-        <v>1.5</v>
+        <f t="shared" si="9"/>
+        <v>22.934026450577171</v>
       </c>
     </row>
     <row r="295" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12364,12 +12361,12 @@
         <v>2</v>
       </c>
       <c r="L295">
-        <f t="shared" si="85"/>
-        <v>1E-3</v>
+        <f t="shared" si="8"/>
+        <v>1.5289350967051448E-2</v>
       </c>
       <c r="M295">
-        <f t="shared" si="92"/>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>15.289350967051448</v>
       </c>
     </row>
     <row r="296" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12398,7 +12395,7 @@
         <v>15.29</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J296" s="1" t="s">
         <v>12</v>
@@ -12407,11 +12404,11 @@
         <v>4</v>
       </c>
       <c r="L296">
-        <f t="shared" si="86"/>
+        <f t="shared" si="8"/>
         <v>3.0578701934102896E-2</v>
       </c>
       <c r="M296">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>30.578701934102895</v>
       </c>
     </row>
@@ -12441,7 +12438,7 @@
         <v>15.29</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>17</v>
@@ -12450,12 +12447,12 @@
         <v>1</v>
       </c>
       <c r="L297">
-        <f t="shared" si="87"/>
-        <v>5.0000000000000001E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.6446754835257239E-3</v>
       </c>
       <c r="M297">
-        <f t="shared" si="92"/>
-        <v>0.5</v>
+        <f t="shared" si="9"/>
+        <v>7.6446754835257238</v>
       </c>
     </row>
     <row r="298" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12484,18 +12481,18 @@
         <v>15.29</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K298" s="1">
         <v>1</v>
       </c>
       <c r="L298">
-        <f t="shared" si="87"/>
-        <v>5.0000000000000001E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.6446754835257239E-3</v>
       </c>
       <c r="M298">
-        <f t="shared" si="92"/>
-        <v>0.5</v>
+        <f t="shared" si="9"/>
+        <v>7.6446754835257238</v>
       </c>
     </row>
     <row r="299" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12530,11 +12527,11 @@
         <v>1</v>
       </c>
       <c r="L299">
-        <f t="shared" si="88"/>
+        <f t="shared" si="8"/>
         <v>7.6446754835257239E-3</v>
       </c>
       <c r="M299">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.6446754835257238</v>
       </c>
     </row>
@@ -12564,21 +12561,21 @@
         <v>28.42</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J300" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K300" s="1">
         <v>22</v>
       </c>
       <c r="L300">
-        <f t="shared" si="89"/>
-        <v>5.6410256410256415E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.16032648301996794</v>
       </c>
       <c r="M300">
-        <f t="shared" si="92"/>
-        <v>5.6410256410256414</v>
+        <f t="shared" si="9"/>
+        <v>160.32648301996792</v>
       </c>
     </row>
     <row r="301" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12607,7 +12604,7 @@
         <v>28.42</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>12</v>
@@ -12616,12 +12613,12 @@
         <v>49</v>
       </c>
       <c r="L301">
-        <f t="shared" si="89"/>
-        <v>1.2564102564102564E-2</v>
+        <f t="shared" si="8"/>
+        <v>0.35709080308992858</v>
       </c>
       <c r="M301">
-        <f t="shared" si="92"/>
-        <v>12.564102564102564</v>
+        <f t="shared" si="9"/>
+        <v>357.09080308992856</v>
       </c>
     </row>
     <row r="302" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12656,11 +12653,11 @@
         <v>2</v>
       </c>
       <c r="L302">
-        <f t="shared" ref="L302" si="95">K302/F302</f>
+        <f t="shared" si="8"/>
         <v>1.4575134819997086E-2</v>
       </c>
       <c r="M302">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>14.575134819997086</v>
       </c>
     </row>
@@ -12690,7 +12687,7 @@
         <v>28.42</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>17</v>
@@ -12699,12 +12696,12 @@
         <v>1</v>
       </c>
       <c r="L303">
-        <f t="shared" ref="L303:L304" si="96">K303/G303</f>
-        <v>2.5641025641025641E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M303">
-        <f t="shared" si="92"/>
-        <v>0.25641025641025639</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12742,12 +12739,12 @@
         <v>1</v>
       </c>
       <c r="L304">
-        <f t="shared" si="96"/>
-        <v>2.5641025641025641E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M304">
-        <f t="shared" si="92"/>
-        <v>0.25641025641025639</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="305" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12779,17 +12776,17 @@
         <v>18</v>
       </c>
       <c r="J305" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K305" s="1">
         <v>2</v>
       </c>
       <c r="L305">
-        <f t="shared" ref="L305:L365" si="97">K305/F305</f>
+        <f t="shared" si="8"/>
         <v>1.4575134819997086E-2</v>
       </c>
       <c r="M305">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>14.575134819997086</v>
       </c>
     </row>
@@ -12819,21 +12816,21 @@
         <v>28.42</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J306" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K306" s="1">
         <v>1</v>
       </c>
       <c r="L306">
-        <f t="shared" ref="L306:L367" si="98">K306/G306</f>
-        <v>2.5641025641025641E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M306">
-        <f t="shared" si="92"/>
-        <v>0.25641025641025639</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="307" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12865,18 +12862,18 @@
         <v>18</v>
       </c>
       <c r="J307" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K307" s="1">
         <v>1</v>
       </c>
       <c r="L307">
-        <f t="shared" si="98"/>
-        <v>2.2727272727272727E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M307">
-        <f t="shared" si="92"/>
-        <v>0.22727272727272727</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="308" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12905,7 +12902,7 @@
         <v>32.06</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>12</v>
@@ -12914,11 +12911,11 @@
         <v>47</v>
       </c>
       <c r="L308">
-        <f t="shared" ref="L308:L368" si="99">K308/F308</f>
+        <f t="shared" si="8"/>
         <v>0.34251566826993152</v>
       </c>
       <c r="M308">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>342.5156682699315</v>
       </c>
     </row>
@@ -12957,12 +12954,12 @@
         <v>1</v>
       </c>
       <c r="L309">
-        <f t="shared" ref="L309:L370" si="100">K309/G309</f>
-        <v>2.2727272727272727E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M309">
-        <f t="shared" si="92"/>
-        <v>0.22727272727272727</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="310" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12991,21 +12988,21 @@
         <v>32.06</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J310" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K310" s="1">
         <v>32</v>
       </c>
       <c r="L310">
-        <f t="shared" si="100"/>
-        <v>7.2727272727272727E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.23320215711995337</v>
       </c>
       <c r="M310">
-        <f t="shared" si="92"/>
-        <v>7.2727272727272725</v>
+        <f t="shared" si="9"/>
+        <v>233.20215711995337</v>
       </c>
     </row>
     <row r="311" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13043,11 +13040,11 @@
         <v>1</v>
       </c>
       <c r="L311">
-        <f t="shared" ref="L311:L371" si="101">K311/F311</f>
+        <f t="shared" si="8"/>
         <v>7.2875674099985429E-3</v>
       </c>
       <c r="M311">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.2875674099985428</v>
       </c>
     </row>
@@ -13077,7 +13074,7 @@
         <v>32.06</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>17</v>
@@ -13086,12 +13083,12 @@
         <v>2</v>
       </c>
       <c r="L312">
-        <f t="shared" ref="L312:L373" si="102">K312/G312</f>
-        <v>4.5454545454545455E-4</v>
+        <f t="shared" si="8"/>
+        <v>1.4575134819997086E-2</v>
       </c>
       <c r="M312">
-        <f t="shared" si="92"/>
-        <v>0.45454545454545453</v>
+        <f t="shared" si="9"/>
+        <v>14.575134819997086</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13120,7 +13117,7 @@
         <v>32.06</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>17</v>
@@ -13129,12 +13126,12 @@
         <v>1</v>
       </c>
       <c r="L313">
-        <f t="shared" si="102"/>
-        <v>2.2727272727272727E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M313">
-        <f t="shared" si="92"/>
-        <v>0.22727272727272727</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13163,20 +13160,20 @@
         <v>32.06</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J314" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K314" s="1">
         <v>1</v>
       </c>
       <c r="L314">
-        <f t="shared" ref="L314:L374" si="103">K314/F314</f>
+        <f t="shared" si="8"/>
         <v>7.2875674099985429E-3</v>
       </c>
       <c r="M314">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.2875674099985428</v>
       </c>
     </row>
@@ -13206,7 +13203,7 @@
         <v>32.06</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>12</v>
@@ -13215,12 +13212,12 @@
         <v>2</v>
       </c>
       <c r="L315">
-        <f t="shared" ref="L315:L376" si="104">K315/G315</f>
-        <v>4.5454545454545455E-4</v>
+        <f t="shared" si="8"/>
+        <v>1.4575134819997086E-2</v>
       </c>
       <c r="M315">
-        <f t="shared" si="92"/>
-        <v>0.45454545454545453</v>
+        <f t="shared" si="9"/>
+        <v>14.575134819997086</v>
       </c>
     </row>
     <row r="316" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13249,7 +13246,7 @@
         <v>32.43</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>12</v>
@@ -13258,12 +13255,12 @@
         <v>52</v>
       </c>
       <c r="L316">
-        <f t="shared" si="104"/>
-        <v>1.1685393258426966E-2</v>
+        <f t="shared" si="8"/>
+        <v>0.37895350531992422</v>
       </c>
       <c r="M316">
-        <f t="shared" si="92"/>
-        <v>11.685393258426966</v>
+        <f t="shared" si="9"/>
+        <v>378.9535053199242</v>
       </c>
     </row>
     <row r="317" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13301,11 +13298,11 @@
         <v>2</v>
       </c>
       <c r="L317">
-        <f t="shared" ref="L317:L377" si="105">K317/F317</f>
+        <f t="shared" si="8"/>
         <v>1.4575134819997086E-2</v>
       </c>
       <c r="M317">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>14.575134819997086</v>
       </c>
     </row>
@@ -13335,21 +13332,21 @@
         <v>32.43</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J318" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K318" s="1">
         <v>20</v>
       </c>
       <c r="L318">
-        <f t="shared" ref="L318:L379" si="106">K318/G318</f>
-        <v>4.4943820224719105E-3</v>
+        <f t="shared" si="8"/>
+        <v>0.14575134819997085</v>
       </c>
       <c r="M318">
-        <f t="shared" si="92"/>
-        <v>4.4943820224719104</v>
+        <f t="shared" si="9"/>
+        <v>145.75134819997083</v>
       </c>
     </row>
     <row r="319" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13384,12 +13381,12 @@
         <v>2</v>
       </c>
       <c r="L319">
-        <f t="shared" si="106"/>
-        <v>4.4943820224719103E-4</v>
+        <f t="shared" si="8"/>
+        <v>1.4575134819997086E-2</v>
       </c>
       <c r="M319">
-        <f t="shared" si="92"/>
-        <v>0.44943820224719105</v>
+        <f t="shared" si="9"/>
+        <v>14.575134819997086</v>
       </c>
     </row>
     <row r="320" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13418,7 +13415,7 @@
         <v>32.43</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J320" s="1" t="s">
         <v>17</v>
@@ -13427,11 +13424,11 @@
         <v>6</v>
       </c>
       <c r="L320">
-        <f t="shared" ref="L320:L350" si="107">K320/F320</f>
+        <f t="shared" si="8"/>
         <v>4.3725404459991256E-2</v>
       </c>
       <c r="M320">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>43.725404459991253</v>
       </c>
     </row>
@@ -13464,18 +13461,18 @@
         <v>18</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K321" s="1">
         <v>1</v>
       </c>
       <c r="L321">
-        <f t="shared" ref="L321:L352" si="108">K321/G321</f>
-        <v>2.2471910112359551E-4</v>
+        <f t="shared" si="8"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M321">
-        <f t="shared" si="92"/>
-        <v>0.22471910112359553</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="322" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13513,12 +13510,12 @@
         <v>3</v>
       </c>
       <c r="L322">
-        <f t="shared" si="108"/>
-        <v>6.7415730337078649E-4</v>
+        <f t="shared" si="8"/>
+        <v>2.1862702229995628E-2</v>
       </c>
       <c r="M322">
-        <f t="shared" si="92"/>
-        <v>0.6741573033707865</v>
+        <f t="shared" si="9"/>
+        <v>21.862702229995627</v>
       </c>
     </row>
     <row r="323" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13547,17 +13544,17 @@
         <v>32.43</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K323" s="1">
         <v>1</v>
       </c>
       <c r="L323">
-        <f t="shared" ref="L323:L353" si="109">K323/F323</f>
+        <f t="shared" ref="L323:L379" si="10">(K323/F323)</f>
         <v>7.2875674099985429E-3</v>
       </c>
       <c r="M323">
-        <f t="shared" si="92"/>
+        <f t="shared" si="9"/>
         <v>7.2875674099985428</v>
       </c>
     </row>
@@ -13587,21 +13584,21 @@
         <v>32.43</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J324" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K324" s="1">
         <v>1</v>
       </c>
       <c r="L324">
-        <f t="shared" ref="L324:L355" si="110">K324/G324</f>
-        <v>2.2471910112359551E-4</v>
+        <f t="shared" si="10"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M324">
-        <f t="shared" si="92"/>
-        <v>0.22471910112359553</v>
+        <f t="shared" si="9"/>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13636,12 +13633,12 @@
         <v>1</v>
       </c>
       <c r="L325">
-        <f t="shared" si="110"/>
-        <v>2.2471910112359551E-4</v>
+        <f t="shared" si="10"/>
+        <v>7.2875674099985429E-3</v>
       </c>
       <c r="M325">
-        <f t="shared" ref="M325:M379" si="111">L325*1000</f>
-        <v>0.22471910112359553</v>
+        <f t="shared" ref="M325:M379" si="11">L325*1000</f>
+        <v>7.2875674099985428</v>
       </c>
     </row>
     <row r="326" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13676,11 +13673,11 @@
         <v>13</v>
       </c>
       <c r="L326">
-        <f t="shared" ref="L326:L356" si="112">K326/F326</f>
+        <f t="shared" si="10"/>
         <v>0.18648687419308566</v>
       </c>
       <c r="M326">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>186.48687419308567</v>
       </c>
     </row>
@@ -13716,12 +13713,12 @@
         <v>29</v>
       </c>
       <c r="L327">
-        <f t="shared" ref="L327:L358" si="113">K327/G327</f>
-        <v>5.7999999999999996E-3</v>
+        <f t="shared" si="10"/>
+        <v>0.41600918089226802</v>
       </c>
       <c r="M327">
-        <f t="shared" si="111"/>
-        <v>5.8</v>
+        <f t="shared" si="11"/>
+        <v>416.00918089226803</v>
       </c>
     </row>
     <row r="328" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13756,12 +13753,12 @@
         <v>4</v>
       </c>
       <c r="L328">
-        <f t="shared" si="113"/>
-        <v>8.0000000000000004E-4</v>
+        <f t="shared" si="10"/>
+        <v>5.738057667479559E-2</v>
       </c>
       <c r="M328">
-        <f t="shared" si="111"/>
-        <v>0.8</v>
+        <f t="shared" si="11"/>
+        <v>57.380576674795591</v>
       </c>
     </row>
     <row r="329" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13793,11 +13790,11 @@
         <v>8</v>
       </c>
       <c r="L329">
-        <f t="shared" ref="L329:L359" si="114">K329/F329</f>
+        <f t="shared" si="10"/>
         <v>0.11476115334959118</v>
       </c>
       <c r="M329">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>114.76115334959118</v>
       </c>
     </row>
@@ -13824,7 +13821,7 @@
         <v>71.73</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>12</v>
@@ -13833,12 +13830,12 @@
         <v>24</v>
       </c>
       <c r="L330">
-        <f t="shared" ref="L330:L361" si="115">K330/G330</f>
-        <v>4.7999999999999996E-3</v>
+        <f t="shared" si="10"/>
+        <v>0.34428346004877353</v>
       </c>
       <c r="M330">
-        <f t="shared" si="111"/>
-        <v>4.8</v>
+        <f t="shared" si="11"/>
+        <v>344.28346004877352</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13870,12 +13867,12 @@
         <v>8</v>
       </c>
       <c r="L331">
-        <f t="shared" si="115"/>
-        <v>1.6000000000000001E-3</v>
+        <f t="shared" si="10"/>
+        <v>0.11476115334959118</v>
       </c>
       <c r="M331">
-        <f t="shared" si="111"/>
-        <v>1.6</v>
+        <f t="shared" si="11"/>
+        <v>114.76115334959118</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13901,20 +13898,20 @@
         <v>71.73</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J332" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K332" s="1">
         <v>2</v>
       </c>
       <c r="L332">
-        <f t="shared" ref="L332" si="116">K332/F332</f>
+        <f t="shared" si="10"/>
         <v>2.8690288337397795E-2</v>
       </c>
       <c r="M332">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>28.690288337397796</v>
       </c>
     </row>
@@ -13941,21 +13938,21 @@
         <v>71.73</v>
       </c>
       <c r="I333" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J333" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J333" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="K333" s="1">
         <v>2</v>
       </c>
       <c r="L333">
-        <f t="shared" ref="L333:L334" si="117">K333/G333</f>
-        <v>4.0000000000000002E-4</v>
+        <f t="shared" si="10"/>
+        <v>2.8690288337397795E-2</v>
       </c>
       <c r="M333">
-        <f t="shared" si="111"/>
-        <v>0.4</v>
+        <f t="shared" si="11"/>
+        <v>28.690288337397796</v>
       </c>
     </row>
     <row r="334" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13984,18 +13981,18 @@
         <v>10</v>
       </c>
       <c r="J334" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K334" s="1">
         <v>1</v>
       </c>
       <c r="L334">
-        <f t="shared" si="117"/>
-        <v>2.0000000000000001E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.4345144168698898E-2</v>
       </c>
       <c r="M334">
-        <f t="shared" si="111"/>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>14.345144168698898</v>
       </c>
     </row>
     <row r="335" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14021,7 +14018,7 @@
         <v>71.73</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>17</v>
@@ -14030,11 +14027,11 @@
         <v>2</v>
       </c>
       <c r="L335">
-        <f t="shared" si="97"/>
+        <f t="shared" si="10"/>
         <v>2.8690288337397795E-2</v>
       </c>
       <c r="M335">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>28.690288337397796</v>
       </c>
     </row>
@@ -14067,12 +14064,12 @@
         <v>1</v>
       </c>
       <c r="L336">
-        <f t="shared" si="98"/>
-        <v>2.0000000000000001E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.4345144168698898E-2</v>
       </c>
       <c r="M336">
-        <f t="shared" si="111"/>
-        <v>0.2</v>
+        <f t="shared" si="11"/>
+        <v>14.345144168698898</v>
       </c>
     </row>
     <row r="337" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14104,12 +14101,12 @@
         <v>6</v>
       </c>
       <c r="L337">
-        <f t="shared" si="98"/>
-        <v>1.1999999999999999E-3</v>
+        <f t="shared" si="10"/>
+        <v>8.6070865012193382E-2</v>
       </c>
       <c r="M337">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="11"/>
+        <v>86.07086501219338</v>
       </c>
     </row>
     <row r="338" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14144,11 +14141,11 @@
         <v>34</v>
       </c>
       <c r="L338">
-        <f t="shared" si="99"/>
+        <f t="shared" si="10"/>
         <v>0.4877349017357625</v>
       </c>
       <c r="M338">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>487.73490173576249</v>
       </c>
     </row>
@@ -14184,12 +14181,12 @@
         <v>22</v>
       </c>
       <c r="L339">
-        <f t="shared" si="100"/>
-        <v>3.6666666666666666E-3</v>
+        <f t="shared" si="10"/>
+        <v>0.31559317171137574</v>
       </c>
       <c r="M339">
-        <f t="shared" si="111"/>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="11"/>
+        <v>315.59317171137576</v>
       </c>
     </row>
     <row r="340" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14224,12 +14221,12 @@
         <v>2</v>
       </c>
       <c r="L340">
-        <f t="shared" si="100"/>
-        <v>3.3333333333333332E-4</v>
+        <f t="shared" si="10"/>
+        <v>2.8690288337397795E-2</v>
       </c>
       <c r="M340">
-        <f t="shared" si="111"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="11"/>
+        <v>28.690288337397796</v>
       </c>
     </row>
     <row r="341" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14255,7 +14252,7 @@
         <v>86.07</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J341" s="1" t="s">
         <v>12</v>
@@ -14264,11 +14261,11 @@
         <v>22</v>
       </c>
       <c r="L341">
-        <f t="shared" si="101"/>
+        <f t="shared" si="10"/>
         <v>0.31559317171137574</v>
       </c>
       <c r="M341">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>315.59317171137576</v>
       </c>
     </row>
@@ -14295,7 +14292,7 @@
         <v>86.07</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J342" s="1" t="s">
         <v>17</v>
@@ -14304,12 +14301,12 @@
         <v>2</v>
       </c>
       <c r="L342">
-        <f t="shared" si="102"/>
-        <v>3.3333333333333332E-4</v>
+        <f t="shared" si="10"/>
+        <v>2.8690288337397795E-2</v>
       </c>
       <c r="M342">
-        <f t="shared" si="111"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="11"/>
+        <v>28.690288337397796</v>
       </c>
     </row>
     <row r="343" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14335,18 +14332,18 @@
         <v>86.07</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K343" s="1">
         <v>1</v>
       </c>
       <c r="L343">
-        <f t="shared" si="102"/>
-        <v>1.6666666666666666E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.4345144168698898E-2</v>
       </c>
       <c r="M343">
-        <f t="shared" si="111"/>
-        <v>0.16666666666666666</v>
+        <f t="shared" si="11"/>
+        <v>14.345144168698898</v>
       </c>
     </row>
     <row r="344" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14378,11 +14375,11 @@
         <v>9</v>
       </c>
       <c r="L344">
-        <f t="shared" si="103"/>
+        <f t="shared" si="10"/>
         <v>0.12910629751829006</v>
       </c>
       <c r="M344">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>129.10629751829006</v>
       </c>
     </row>
@@ -14409,7 +14406,7 @@
         <v>86.07</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J345" s="1" t="s">
         <v>17</v>
@@ -14418,12 +14415,12 @@
         <v>2</v>
       </c>
       <c r="L345">
-        <f t="shared" si="104"/>
-        <v>3.3333333333333332E-4</v>
+        <f t="shared" si="10"/>
+        <v>2.8690288337397795E-2</v>
       </c>
       <c r="M345">
-        <f t="shared" si="111"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="11"/>
+        <v>28.690288337397796</v>
       </c>
     </row>
     <row r="346" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14455,12 +14452,12 @@
         <v>2</v>
       </c>
       <c r="L346">
-        <f t="shared" si="104"/>
-        <v>3.3333333333333332E-4</v>
+        <f t="shared" si="10"/>
+        <v>2.8690288337397795E-2</v>
       </c>
       <c r="M346">
-        <f t="shared" si="111"/>
-        <v>0.33333333333333331</v>
+        <f t="shared" si="11"/>
+        <v>28.690288337397796</v>
       </c>
     </row>
     <row r="347" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14492,11 +14489,11 @@
         <v>4</v>
       </c>
       <c r="L347">
-        <f t="shared" si="105"/>
+        <f t="shared" si="10"/>
         <v>5.738057667479559E-2</v>
       </c>
       <c r="M347">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>57.380576674795591</v>
       </c>
     </row>
@@ -14529,12 +14526,12 @@
         <v>4</v>
       </c>
       <c r="L348">
-        <f t="shared" si="106"/>
-        <v>7.5757575757575758E-4</v>
+        <f t="shared" si="10"/>
+        <v>5.738057667479559E-2</v>
       </c>
       <c r="M348">
-        <f t="shared" si="111"/>
-        <v>0.75757575757575757</v>
+        <f t="shared" si="11"/>
+        <v>57.380576674795591</v>
       </c>
     </row>
     <row r="349" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14569,12 +14566,12 @@
         <v>22</v>
       </c>
       <c r="L349">
-        <f t="shared" si="106"/>
-        <v>4.1666666666666666E-3</v>
+        <f t="shared" si="10"/>
+        <v>0.31559317171137574</v>
       </c>
       <c r="M349">
-        <f t="shared" si="111"/>
-        <v>4.166666666666667</v>
+        <f t="shared" si="11"/>
+        <v>315.59317171137576</v>
       </c>
     </row>
     <row r="350" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14609,11 +14606,11 @@
         <v>16</v>
       </c>
       <c r="L350">
-        <f t="shared" si="107"/>
+        <f t="shared" si="10"/>
         <v>0.22952230669918236</v>
       </c>
       <c r="M350">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>229.52230669918237</v>
       </c>
     </row>
@@ -14640,7 +14637,7 @@
         <v>75.75</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J351" s="1" t="s">
         <v>17</v>
@@ -14649,12 +14646,12 @@
         <v>4</v>
       </c>
       <c r="L351">
-        <f t="shared" si="108"/>
-        <v>7.5757575757575758E-4</v>
+        <f t="shared" si="10"/>
+        <v>5.738057667479559E-2</v>
       </c>
       <c r="M351">
-        <f t="shared" si="111"/>
-        <v>0.75757575757575757</v>
+        <f t="shared" si="11"/>
+        <v>57.380576674795591</v>
       </c>
     </row>
     <row r="352" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14680,18 +14677,18 @@
         <v>75.75</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K352" s="1">
         <v>3</v>
       </c>
       <c r="L352">
-        <f t="shared" si="108"/>
-        <v>5.6818181818181815E-4</v>
+        <f t="shared" si="10"/>
+        <v>4.3035432506096691E-2</v>
       </c>
       <c r="M352">
-        <f t="shared" si="111"/>
-        <v>0.56818181818181812</v>
+        <f t="shared" si="11"/>
+        <v>43.03543250609669</v>
       </c>
     </row>
     <row r="353" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14717,7 +14714,7 @@
         <v>75.75</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J353" s="1" t="s">
         <v>12</v>
@@ -14726,11 +14723,11 @@
         <v>26</v>
       </c>
       <c r="L353">
-        <f t="shared" si="109"/>
+        <f t="shared" si="10"/>
         <v>0.37297374838617131</v>
       </c>
       <c r="M353">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>372.97374838617134</v>
       </c>
     </row>
@@ -14763,12 +14760,12 @@
         <v>7</v>
       </c>
       <c r="L354">
-        <f t="shared" si="110"/>
-        <v>1.3257575757575758E-3</v>
+        <f t="shared" si="10"/>
+        <v>0.10041600918089227</v>
       </c>
       <c r="M354">
-        <f t="shared" si="111"/>
-        <v>1.3257575757575759</v>
+        <f t="shared" si="11"/>
+        <v>100.41600918089227</v>
       </c>
     </row>
     <row r="355" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14794,21 +14791,21 @@
         <v>75.75</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J355" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K355" s="1">
         <v>1</v>
       </c>
       <c r="L355">
-        <f t="shared" si="110"/>
-        <v>1.8939393939393939E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.4345144168698898E-2</v>
       </c>
       <c r="M355">
-        <f t="shared" si="111"/>
-        <v>0.18939393939393939</v>
+        <f t="shared" si="11"/>
+        <v>14.345144168698898</v>
       </c>
     </row>
     <row r="356" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14840,11 +14837,11 @@
         <v>1</v>
       </c>
       <c r="L356">
-        <f t="shared" si="112"/>
+        <f t="shared" si="10"/>
         <v>1.4345144168698898E-2</v>
       </c>
       <c r="M356">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>14.345144168698898</v>
       </c>
     </row>
@@ -14880,12 +14877,12 @@
         <v>2</v>
       </c>
       <c r="L357">
-        <f t="shared" si="113"/>
-        <v>3.7878787878787879E-4</v>
+        <f t="shared" si="10"/>
+        <v>2.8690288337397795E-2</v>
       </c>
       <c r="M357">
-        <f t="shared" si="111"/>
-        <v>0.37878787878787878</v>
+        <f t="shared" si="11"/>
+        <v>28.690288337397796</v>
       </c>
     </row>
     <row r="358" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14917,12 +14914,12 @@
         <v>1</v>
       </c>
       <c r="L358">
-        <f t="shared" si="113"/>
-        <v>1.8939393939393939E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.4345144168698898E-2</v>
       </c>
       <c r="M358">
-        <f t="shared" si="111"/>
-        <v>0.18939393939393939</v>
+        <f t="shared" si="11"/>
+        <v>14.345144168698898</v>
       </c>
     </row>
     <row r="359" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14948,20 +14945,20 @@
         <v>75.75</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J359" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K359" s="1">
         <v>1</v>
       </c>
       <c r="L359">
-        <f t="shared" si="114"/>
+        <f t="shared" si="10"/>
         <v>1.4345144168698898E-2</v>
       </c>
       <c r="M359">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>14.345144168698898</v>
       </c>
     </row>
@@ -14997,12 +14994,12 @@
         <v>10</v>
       </c>
       <c r="L360">
-        <f t="shared" si="115"/>
-        <v>4.608294930875576E-3</v>
+        <f t="shared" si="10"/>
+        <v>8.8051422030465801E-2</v>
       </c>
       <c r="M360">
-        <f t="shared" si="111"/>
-        <v>4.6082949308755756</v>
+        <f t="shared" si="11"/>
+        <v>88.051422030465801</v>
       </c>
     </row>
     <row r="361" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15034,12 +15031,12 @@
         <v>3</v>
       </c>
       <c r="L361">
-        <f t="shared" si="115"/>
-        <v>1.3824884792626728E-3</v>
+        <f t="shared" si="10"/>
+        <v>2.6415426609139741E-2</v>
       </c>
       <c r="M361">
-        <f t="shared" si="111"/>
-        <v>1.3824884792626728</v>
+        <f t="shared" si="11"/>
+        <v>26.41542660913974</v>
       </c>
     </row>
     <row r="362" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15065,7 +15062,7 @@
         <v>19.11</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J362" s="1" t="s">
         <v>12</v>
@@ -15074,11 +15071,11 @@
         <v>6</v>
       </c>
       <c r="L362">
-        <f t="shared" ref="L362" si="118">K362/F362</f>
+        <f t="shared" si="10"/>
         <v>5.2830853218279482E-2</v>
       </c>
       <c r="M362">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>52.830853218279479</v>
       </c>
     </row>
@@ -15114,12 +15111,12 @@
         <v>7</v>
       </c>
       <c r="L363">
-        <f t="shared" ref="L363:L364" si="119">K363/G363</f>
-        <v>3.2258064516129032E-3</v>
+        <f t="shared" si="10"/>
+        <v>6.1635995421326056E-2</v>
       </c>
       <c r="M363">
-        <f t="shared" si="111"/>
-        <v>3.225806451612903</v>
+        <f t="shared" si="11"/>
+        <v>61.635995421326058</v>
       </c>
     </row>
     <row r="364" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15151,12 +15148,12 @@
         <v>2</v>
       </c>
       <c r="L364">
-        <f t="shared" si="119"/>
-        <v>9.2165898617511521E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.7610284406093159E-2</v>
       </c>
       <c r="M364">
-        <f t="shared" si="111"/>
-        <v>0.92165898617511521</v>
+        <f t="shared" si="11"/>
+        <v>17.610284406093161</v>
       </c>
     </row>
     <row r="365" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15188,11 +15185,11 @@
         <v>2</v>
       </c>
       <c r="L365">
-        <f t="shared" si="97"/>
+        <f t="shared" si="10"/>
         <v>1.7610284406093159E-2</v>
       </c>
       <c r="M365">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>17.610284406093161</v>
       </c>
     </row>
@@ -15219,18 +15216,18 @@
         <v>19.11</v>
       </c>
       <c r="I366" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K366" s="1">
         <v>1</v>
       </c>
       <c r="L366">
-        <f t="shared" si="98"/>
-        <v>4.608294930875576E-4</v>
+        <f t="shared" si="10"/>
+        <v>8.8051422030465797E-3</v>
       </c>
       <c r="M366">
-        <f t="shared" si="111"/>
-        <v>0.46082949308755761</v>
+        <f t="shared" si="11"/>
+        <v>8.8051422030465805</v>
       </c>
     </row>
     <row r="367" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15265,12 +15262,12 @@
         <v>9</v>
       </c>
       <c r="L367">
-        <f t="shared" si="98"/>
-        <v>4.1474654377880189E-3</v>
+        <f t="shared" si="10"/>
+        <v>7.9246279827419219E-2</v>
       </c>
       <c r="M367">
-        <f t="shared" si="111"/>
-        <v>4.1474654377880187</v>
+        <f t="shared" si="11"/>
+        <v>79.246279827419215</v>
       </c>
     </row>
     <row r="368" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15305,11 +15302,11 @@
         <v>7</v>
       </c>
       <c r="L368">
-        <f t="shared" si="99"/>
+        <f t="shared" si="10"/>
         <v>6.1635995421326056E-2</v>
       </c>
       <c r="M368">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>61.635995421326058</v>
       </c>
     </row>
@@ -15342,12 +15339,12 @@
         <v>5</v>
       </c>
       <c r="L369">
-        <f t="shared" si="100"/>
-        <v>2.304147465437788E-3</v>
+        <f t="shared" si="10"/>
+        <v>4.40257110152329E-2</v>
       </c>
       <c r="M369">
-        <f t="shared" si="111"/>
-        <v>2.3041474654377878</v>
+        <f t="shared" si="11"/>
+        <v>44.025711015232901</v>
       </c>
     </row>
     <row r="370" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15373,7 +15370,7 @@
         <v>19.11</v>
       </c>
       <c r="I370" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J370" s="1" t="s">
         <v>12</v>
@@ -15382,12 +15379,12 @@
         <v>6</v>
       </c>
       <c r="L370">
-        <f t="shared" si="100"/>
-        <v>2.7649769585253456E-3</v>
+        <f t="shared" si="10"/>
+        <v>5.2830853218279482E-2</v>
       </c>
       <c r="M370">
-        <f t="shared" si="111"/>
-        <v>2.7649769585253456</v>
+        <f t="shared" si="11"/>
+        <v>52.830853218279479</v>
       </c>
     </row>
     <row r="371" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15419,11 +15416,11 @@
         <v>1</v>
       </c>
       <c r="L371">
-        <f t="shared" si="101"/>
+        <f t="shared" si="10"/>
         <v>8.8051422030465797E-3</v>
       </c>
       <c r="M371">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>8.8051422030465805</v>
       </c>
     </row>
@@ -15459,12 +15456,12 @@
         <v>1</v>
       </c>
       <c r="L372">
-        <f t="shared" si="102"/>
-        <v>4.608294930875576E-4</v>
+        <f t="shared" si="10"/>
+        <v>8.8051422030465797E-3</v>
       </c>
       <c r="M372">
-        <f t="shared" si="111"/>
-        <v>0.46082949308755761</v>
+        <f t="shared" si="11"/>
+        <v>8.8051422030465805</v>
       </c>
     </row>
     <row r="373" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15496,12 +15493,12 @@
         <v>2</v>
       </c>
       <c r="L373">
-        <f t="shared" si="102"/>
-        <v>9.2165898617511521E-4</v>
+        <f t="shared" si="10"/>
+        <v>1.7610284406093159E-2</v>
       </c>
       <c r="M373">
-        <f t="shared" si="111"/>
-        <v>0.92165898617511521</v>
+        <f t="shared" si="11"/>
+        <v>17.610284406093161</v>
       </c>
     </row>
     <row r="374" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15533,11 +15530,11 @@
         <v>6</v>
       </c>
       <c r="L374">
-        <f t="shared" si="103"/>
+        <f t="shared" si="10"/>
         <v>5.2830853218279482E-2</v>
       </c>
       <c r="M374">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>52.830853218279479</v>
       </c>
     </row>
@@ -15573,12 +15570,12 @@
         <v>9</v>
       </c>
       <c r="L375">
-        <f t="shared" si="104"/>
-        <v>3.8961038961038961E-3</v>
+        <f t="shared" si="10"/>
+        <v>7.9246279827419219E-2</v>
       </c>
       <c r="M375">
-        <f t="shared" si="111"/>
-        <v>3.8961038961038961</v>
+        <f t="shared" si="11"/>
+        <v>79.246279827419215</v>
       </c>
     </row>
     <row r="376" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15610,12 +15607,12 @@
         <v>1</v>
       </c>
       <c r="L376">
-        <f t="shared" si="104"/>
-        <v>4.329004329004329E-4</v>
+        <f t="shared" si="10"/>
+        <v>8.8051422030465797E-3</v>
       </c>
       <c r="M376">
-        <f t="shared" si="111"/>
-        <v>0.4329004329004329</v>
+        <f t="shared" si="11"/>
+        <v>8.8051422030465805</v>
       </c>
     </row>
     <row r="377" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15641,7 +15638,7 @@
         <v>20.34</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J377" s="1" t="s">
         <v>12</v>
@@ -15650,11 +15647,11 @@
         <v>9</v>
       </c>
       <c r="L377">
-        <f t="shared" si="105"/>
+        <f t="shared" si="10"/>
         <v>7.9246279827419219E-2</v>
       </c>
       <c r="M377">
-        <f t="shared" si="111"/>
+        <f t="shared" si="11"/>
         <v>79.246279827419215</v>
       </c>
     </row>
@@ -15687,12 +15684,12 @@
         <v>1</v>
       </c>
       <c r="L378">
-        <f t="shared" si="106"/>
-        <v>4.329004329004329E-4</v>
+        <f t="shared" si="10"/>
+        <v>8.8051422030465797E-3</v>
       </c>
       <c r="M378">
-        <f t="shared" si="111"/>
-        <v>0.4329004329004329</v>
+        <f t="shared" si="11"/>
+        <v>8.8051422030465805</v>
       </c>
     </row>
     <row r="379" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15727,12 +15724,12 @@
         <v>7</v>
       </c>
       <c r="L379">
-        <f t="shared" si="106"/>
-        <v>3.0303030303030303E-3</v>
+        <f t="shared" si="10"/>
+        <v>6.1635995421326056E-2</v>
       </c>
       <c r="M379">
-        <f t="shared" si="111"/>
-        <v>3.0303030303030303</v>
+        <f t="shared" si="11"/>
+        <v>61.635995421326058</v>
       </c>
     </row>
     <row r="380" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/Portage Canal/Zooplankton_microscopy_counts.xlsx
+++ b/Portage Canal/Zooplankton_microscopy_counts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/khadijahhomolka/Documents/GitHub/PGST-Natural-Resources/Portage Canal/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\NR-Research\GitHub\PGST-Natural-Resources\Portage Canal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9AD578-7702-A047-8295-C17B8FCC239B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADE69B5-0F27-4E5B-AE68-3091E1AC8926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68680" yWindow="-3000" windowWidth="36480" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -189,9 +189,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -233,14 +230,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,25 +455,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="5.5" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="8.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="33" customWidth="1"/>
-    <col min="9" max="9" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" customWidth="1"/>
-    <col min="12" max="12" width="40.5" customWidth="1"/>
-    <col min="13" max="13" width="39.5" customWidth="1"/>
-    <col min="14" max="26" width="8.6640625" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="40.42578125" customWidth="1"/>
+    <col min="13" max="13" width="39.42578125" customWidth="1"/>
+    <col min="14" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -516,7 +514,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -559,7 +557,7 @@
         <v>193.37016574585633</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -602,7 +600,7 @@
         <v>75.966850828729278</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -645,7 +643,7 @@
         <v>20.718232044198896</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -685,7 +683,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -728,7 +726,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -771,7 +769,7 @@
         <v>13.812154696132596</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -811,7 +809,7 @@
         <v>13.812154696132596</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -854,7 +852,7 @@
         <v>89.779005524861873</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -897,7 +895,7 @@
         <v>27.624309392265193</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -940,7 +938,7 @@
         <v>27.624309392265193</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -983,7 +981,7 @@
         <v>214.08839779005524</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -1026,7 +1024,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -1066,7 +1064,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -1106,7 +1104,7 @@
         <v>20.718232044198896</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -1149,7 +1147,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -1192,7 +1190,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -1235,7 +1233,7 @@
         <v>124.30939226519335</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -1278,7 +1276,7 @@
         <v>13.812154696132596</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>3</v>
       </c>
@@ -1321,7 +1319,7 @@
         <v>124.30939226519335</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -1364,7 +1362,7 @@
         <v>20.718232044198896</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -1407,7 +1405,7 @@
         <v>20.718232044198896</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -1450,7 +1448,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -1490,7 +1488,7 @@
         <v>6.9060773480662982</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -1530,7 +1528,7 @@
         <v>71.62183670221232</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -1573,7 +1571,7 @@
         <v>15.915963711602737</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -1613,7 +1611,7 @@
         <v>190.99156453923285</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -1656,7 +1654,7 @@
         <v>23.873945567404107</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1699,7 +1697,7 @@
         <v>7.9579818558013686</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -1742,7 +1740,7 @@
         <v>47.747891134808214</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -1782,7 +1780,7 @@
         <v>7.9579818558013686</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1825,7 +1823,7 @@
         <v>7.9579818558013686</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -1865,7 +1863,7 @@
         <v>254.6554193856438</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>2</v>
       </c>
@@ -1905,7 +1903,7 @@
         <v>71.62183670221232</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2</v>
       </c>
@@ -1948,7 +1946,7 @@
         <v>55.705872990609585</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>2</v>
       </c>
@@ -1991,7 +1989,7 @@
         <v>15.915963711602737</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>3</v>
       </c>
@@ -2031,7 +2029,7 @@
         <v>230.7814738182397</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>3</v>
       </c>
@@ -2071,7 +2069,7 @@
         <v>79.579818558013685</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>3</v>
       </c>
@@ -2114,7 +2112,7 @@
         <v>39.789909279006842</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>3</v>
       </c>
@@ -2157,7 +2155,7 @@
         <v>23.873945567404107</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>3</v>
       </c>
@@ -2200,7 +2198,7 @@
         <v>55.705872990609585</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>3</v>
       </c>
@@ -2240,7 +2238,7 @@
         <v>7.9579818558013686</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>3</v>
       </c>
@@ -2280,7 +2278,7 @@
         <v>15.915963711602737</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -2292,6 +2290,9 @@
       </c>
       <c r="D44" s="3">
         <v>45498</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.52013888888888893</v>
       </c>
       <c r="F44" s="1">
         <v>128.69999999999999</v>
@@ -2320,7 +2321,7 @@
         <v>132.0901320901321</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>1</v>
       </c>
@@ -2332,6 +2333,9 @@
       </c>
       <c r="D45" s="3">
         <v>45498</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.52013888888888893</v>
       </c>
       <c r="F45" s="1">
         <v>128.69999999999999</v>
@@ -2360,7 +2364,7 @@
         <v>46.620046620046622</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -2372,6 +2376,9 @@
       </c>
       <c r="D46" s="3">
         <v>45498</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.52013888888888893</v>
       </c>
       <c r="F46" s="1">
         <v>128.69999999999999</v>
@@ -2400,7 +2407,7 @@
         <v>23.310023310023311</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -2412,6 +2419,9 @@
       </c>
       <c r="D47" s="3">
         <v>45498</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.52013888888888893</v>
       </c>
       <c r="F47" s="1">
         <v>128.69999999999999</v>
@@ -2437,7 +2447,7 @@
         <v>194.25019425019426</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>1</v>
       </c>
@@ -2449,6 +2459,9 @@
       </c>
       <c r="D48" s="3">
         <v>45498</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F48" s="1">
         <v>128.69999999999999</v>
@@ -2477,7 +2490,7 @@
         <v>77.700077700077713</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -2489,6 +2502,9 @@
       </c>
       <c r="D49" s="3">
         <v>45498</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F49" s="1">
         <v>128.69999999999999</v>
@@ -2514,7 +2530,7 @@
         <v>31.080031080031084</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -2526,6 +2542,9 @@
       </c>
       <c r="D50" s="3">
         <v>45498</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F50" s="1">
         <v>128.69999999999999</v>
@@ -2551,7 +2570,7 @@
         <v>54.390054390054395</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -2563,6 +2582,9 @@
       </c>
       <c r="D51" s="3">
         <v>45498</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F51" s="1">
         <v>128.69999999999999</v>
@@ -2588,7 +2610,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -2600,6 +2622,9 @@
       </c>
       <c r="D52" s="3">
         <v>45498</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F52" s="1">
         <v>128.69999999999999</v>
@@ -2625,7 +2650,7 @@
         <v>23.310023310023311</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>1</v>
       </c>
@@ -2637,6 +2662,9 @@
       </c>
       <c r="D53" s="3">
         <v>45498</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F53" s="1">
         <v>128.69999999999999</v>
@@ -2665,7 +2693,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>1</v>
       </c>
@@ -2677,6 +2705,9 @@
       </c>
       <c r="D54" s="3">
         <v>45498</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F54" s="1">
         <v>128.69999999999999</v>
@@ -2705,7 +2736,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -2717,6 +2748,9 @@
       </c>
       <c r="D55" s="3">
         <v>45498</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F55" s="1">
         <v>128.69999999999999</v>
@@ -2745,7 +2779,7 @@
         <v>217.56021756021758</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>2</v>
       </c>
@@ -2757,6 +2791,9 @@
       </c>
       <c r="D56" s="3">
         <v>45498</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F56" s="1">
         <v>128.69999999999999</v>
@@ -2785,7 +2822,7 @@
         <v>31.080031080031084</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>2</v>
       </c>
@@ -2797,6 +2834,9 @@
       </c>
       <c r="D57" s="3">
         <v>45498</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F57" s="1">
         <v>128.69999999999999</v>
@@ -2822,7 +2862,7 @@
         <v>194.25019425019426</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>2</v>
       </c>
@@ -2834,6 +2874,9 @@
       </c>
       <c r="D58" s="3">
         <v>45498</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F58" s="1">
         <v>128.69999999999999</v>
@@ -2862,7 +2905,7 @@
         <v>116.55011655011656</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -2874,6 +2917,9 @@
       </c>
       <c r="D59" s="3">
         <v>45498</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F59" s="1">
         <v>128.69999999999999</v>
@@ -2899,7 +2945,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>2</v>
       </c>
@@ -2911,6 +2957,9 @@
       </c>
       <c r="D60" s="3">
         <v>45498</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F60" s="1">
         <v>128.69999999999999</v>
@@ -2936,7 +2985,7 @@
         <v>15.540015540015542</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>2</v>
       </c>
@@ -2948,6 +2997,9 @@
       </c>
       <c r="D61" s="3">
         <v>45498</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F61" s="1">
         <v>128.69999999999999</v>
@@ -2976,7 +3028,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>2</v>
       </c>
@@ -2988,6 +3040,9 @@
       </c>
       <c r="D62" s="3">
         <v>45498</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F62" s="1">
         <v>128.69999999999999</v>
@@ -3016,7 +3071,7 @@
         <v>23.310023310023311</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>2</v>
       </c>
@@ -3028,6 +3083,9 @@
       </c>
       <c r="D63" s="3">
         <v>45498</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F63" s="1">
         <v>128.69999999999999</v>
@@ -3053,7 +3111,7 @@
         <v>15.540015540015542</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>3</v>
       </c>
@@ -3065,6 +3123,9 @@
       </c>
       <c r="D64" s="3">
         <v>45498</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F64" s="1">
         <v>128.69999999999999</v>
@@ -3093,7 +3154,7 @@
         <v>77.700077700077713</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>3</v>
       </c>
@@ -3105,6 +3166,9 @@
       </c>
       <c r="D65" s="3">
         <v>45498</v>
+      </c>
+      <c r="E65" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F65" s="1">
         <v>128.69999999999999</v>
@@ -3133,7 +3197,7 @@
         <v>31.080031080031084</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>3</v>
       </c>
@@ -3145,6 +3209,9 @@
       </c>
       <c r="D66" s="3">
         <v>45498</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F66" s="1">
         <v>128.69999999999999</v>
@@ -3170,7 +3237,7 @@
         <v>225.33022533022535</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>3</v>
       </c>
@@ -3182,6 +3249,9 @@
       </c>
       <c r="D67" s="3">
         <v>45498</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F67" s="1">
         <v>128.69999999999999</v>
@@ -3210,7 +3280,7 @@
         <v>31.080031080031084</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>3</v>
       </c>
@@ -3222,6 +3292,9 @@
       </c>
       <c r="D68" s="3">
         <v>45498</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F68" s="1">
         <v>128.69999999999999</v>
@@ -3250,7 +3323,7 @@
         <v>186.48018648018649</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>3</v>
       </c>
@@ -3262,6 +3335,9 @@
       </c>
       <c r="D69" s="3">
         <v>45498</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F69" s="1">
         <v>128.69999999999999</v>
@@ -3287,7 +3363,7 @@
         <v>15.540015540015542</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>3</v>
       </c>
@@ -3299,6 +3375,9 @@
       </c>
       <c r="D70" s="3">
         <v>45498</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F70" s="1">
         <v>128.69999999999999</v>
@@ -3324,7 +3403,7 @@
         <v>31.080031080031084</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>3</v>
       </c>
@@ -3336,6 +3415,9 @@
       </c>
       <c r="D71" s="3">
         <v>45498</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F71" s="1">
         <v>128.69999999999999</v>
@@ -3364,7 +3446,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>3</v>
       </c>
@@ -3376,6 +3458,9 @@
       </c>
       <c r="D72" s="3">
         <v>45498</v>
+      </c>
+      <c r="E72" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F72" s="1">
         <v>128.69999999999999</v>
@@ -3401,7 +3486,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>3</v>
       </c>
@@ -3413,6 +3498,9 @@
       </c>
       <c r="D73" s="3">
         <v>45498</v>
+      </c>
+      <c r="E73" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F73" s="1">
         <v>128.69999999999999</v>
@@ -3441,7 +3529,7 @@
         <v>23.310023310023311</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>3</v>
       </c>
@@ -3453,6 +3541,9 @@
       </c>
       <c r="D74" s="3">
         <v>45498</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0.52013888888888904</v>
       </c>
       <c r="F74" s="1">
         <v>128.69999999999999</v>
@@ -3481,7 +3572,7 @@
         <v>7.770007770007771</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>1</v>
       </c>
@@ -3524,7 +3615,7 @@
         <v>205.27859237536654</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>1</v>
       </c>
@@ -3567,7 +3658,7 @@
         <v>219.94134897360703</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -3607,7 +3698,7 @@
         <v>73.313782991202331</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1</v>
       </c>
@@ -3647,7 +3738,7 @@
         <v>322.58064516129031</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>1</v>
       </c>
@@ -3690,7 +3781,7 @@
         <v>43.988269794721404</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>1</v>
       </c>
@@ -3730,7 +3821,7 @@
         <v>117.30205278592375</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>1</v>
       </c>
@@ -3773,7 +3864,7 @@
         <v>29.325513196480937</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>1</v>
       </c>
@@ -3813,7 +3904,7 @@
         <v>29.325513196480937</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>1</v>
       </c>
@@ -3856,7 +3947,7 @@
         <v>43.988269794721404</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>1</v>
       </c>
@@ -3899,7 +3990,7 @@
         <v>14.662756598240469</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>2</v>
       </c>
@@ -3939,7 +4030,7 @@
         <v>263.92961876832845</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>2</v>
       </c>
@@ -3982,7 +4073,7 @@
         <v>161.29032258064515</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>2</v>
       </c>
@@ -4025,7 +4116,7 @@
         <v>190.61583577712611</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>2</v>
       </c>
@@ -4065,7 +4156,7 @@
         <v>117.30205278592375</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>2</v>
       </c>
@@ -4105,7 +4196,7 @@
         <v>43.988269794721404</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>2</v>
       </c>
@@ -4148,7 +4239,7 @@
         <v>58.651026392961874</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>2</v>
       </c>
@@ -4191,7 +4282,7 @@
         <v>29.325513196480937</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>2</v>
       </c>
@@ -4231,7 +4322,7 @@
         <v>43.988269794721404</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>2</v>
       </c>
@@ -4274,7 +4365,7 @@
         <v>14.662756598240469</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>3</v>
       </c>
@@ -4314,7 +4405,7 @@
         <v>263.92961876832845</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>3</v>
       </c>
@@ -4357,7 +4448,7 @@
         <v>161.29032258064515</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>3</v>
       </c>
@@ -4400,7 +4491,7 @@
         <v>190.61583577712611</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>3</v>
       </c>
@@ -4440,7 +4531,7 @@
         <v>117.30205278592375</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>3</v>
       </c>
@@ -4480,7 +4571,7 @@
         <v>43.988269794721404</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>3</v>
       </c>
@@ -4523,7 +4614,7 @@
         <v>58.651026392961874</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>3</v>
       </c>
@@ -4566,7 +4657,7 @@
         <v>29.325513196480937</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>3</v>
       </c>
@@ -4606,7 +4697,7 @@
         <v>43.988269794721404</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>3</v>
       </c>
@@ -4649,7 +4740,7 @@
         <v>14.662756598240469</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>1</v>
       </c>
@@ -4692,7 +4783,7 @@
         <v>327.27272727272725</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>1</v>
       </c>
@@ -4735,7 +4826,7 @@
         <v>136.36363636363635</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>1</v>
       </c>
@@ -4778,7 +4869,7 @@
         <v>254.54545454545453</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>1</v>
       </c>
@@ -4818,7 +4909,7 @@
         <v>45.454545454545453</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>1</v>
       </c>
@@ -4858,7 +4949,7 @@
         <v>109.09090909090908</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>1</v>
       </c>
@@ -4898,7 +4989,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>1</v>
       </c>
@@ -4938,7 +5029,7 @@
         <v>18.18181818181818</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>1</v>
       </c>
@@ -4978,7 +5069,7 @@
         <v>27.27272727272727</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>1</v>
       </c>
@@ -5021,7 +5112,7 @@
         <v>18.18181818181818</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>1</v>
       </c>
@@ -5064,7 +5155,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>1</v>
       </c>
@@ -5104,7 +5195,7 @@
         <v>36.36363636363636</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>2</v>
       </c>
@@ -5144,7 +5235,7 @@
         <v>327.27272727272725</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>2</v>
       </c>
@@ -5187,7 +5278,7 @@
         <v>327.27272727272725</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>2</v>
       </c>
@@ -5230,7 +5321,7 @@
         <v>363.63636363636363</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>2</v>
       </c>
@@ -5270,7 +5361,7 @@
         <v>45.454545454545453</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>2</v>
       </c>
@@ -5310,7 +5401,7 @@
         <v>109.09090909090908</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>2</v>
       </c>
@@ -5353,7 +5444,7 @@
         <v>45.454545454545453</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>2</v>
       </c>
@@ -5396,7 +5487,7 @@
         <v>63.636363636363633</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>2</v>
       </c>
@@ -5436,7 +5527,7 @@
         <v>27.27272727272727</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>2</v>
       </c>
@@ -5479,7 +5570,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>2</v>
       </c>
@@ -5522,7 +5613,7 @@
         <v>90.909090909090907</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>2</v>
       </c>
@@ -5562,7 +5653,7 @@
         <v>63.636363636363633</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>3</v>
       </c>
@@ -5602,7 +5693,7 @@
         <v>263.63636363636363</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>3</v>
       </c>
@@ -5645,7 +5736,7 @@
         <v>363.63636363636363</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>3</v>
       </c>
@@ -5688,7 +5779,7 @@
         <v>127.27272727272727</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>3</v>
       </c>
@@ -5731,7 +5822,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>3</v>
       </c>
@@ -5771,7 +5862,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>3</v>
       </c>
@@ -5814,7 +5905,7 @@
         <v>72.72727272727272</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>3</v>
       </c>
@@ -5854,7 +5945,7 @@
         <v>118.18181818181817</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>3</v>
       </c>
@@ -5894,7 +5985,7 @@
         <v>72.72727272727272</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>3</v>
       </c>
@@ -5937,7 +6028,7 @@
         <v>27.27272727272727</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>3</v>
       </c>
@@ -5977,7 +6068,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>3</v>
       </c>
@@ -6017,7 +6108,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>3</v>
       </c>
@@ -6057,7 +6148,7 @@
         <v>18.18181818181818</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>3</v>
       </c>
@@ -6100,7 +6191,7 @@
         <v>9.0909090909090899</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1</v>
       </c>
@@ -6112,6 +6203,9 @@
       </c>
       <c r="D138" s="3">
         <v>45561</v>
+      </c>
+      <c r="E138" s="7">
+        <v>0.52361111111111114</v>
       </c>
       <c r="F138" s="1">
         <v>153.1</v>
@@ -6137,7 +6231,7 @@
         <v>52.253429131286744</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>1</v>
       </c>
@@ -6149,6 +6243,9 @@
       </c>
       <c r="D139" s="3">
         <v>45561</v>
+      </c>
+      <c r="E139" s="7">
+        <v>0.52361111111111114</v>
       </c>
       <c r="F139" s="1">
         <v>153.1</v>
@@ -6174,7 +6271,7 @@
         <v>13.063357282821686</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>1</v>
       </c>
@@ -6186,6 +6283,9 @@
       </c>
       <c r="D140" s="3">
         <v>45561</v>
+      </c>
+      <c r="E140" s="7">
+        <v>0.52361111111111114</v>
       </c>
       <c r="F140" s="1">
         <v>153.1</v>
@@ -6214,7 +6314,7 @@
         <v>39.190071848465053</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>1</v>
       </c>
@@ -6226,6 +6326,9 @@
       </c>
       <c r="D141" s="3">
         <v>45561</v>
+      </c>
+      <c r="E141" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F141" s="1">
         <v>153.1</v>
@@ -6251,7 +6354,7 @@
         <v>117.57021554539517</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1</v>
       </c>
@@ -6263,6 +6366,9 @@
       </c>
       <c r="D142" s="3">
         <v>45561</v>
+      </c>
+      <c r="E142" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F142" s="1">
         <v>153.1</v>
@@ -6291,7 +6397,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>1</v>
       </c>
@@ -6303,6 +6409,9 @@
       </c>
       <c r="D143" s="3">
         <v>45561</v>
+      </c>
+      <c r="E143" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F143" s="1">
         <v>153.1</v>
@@ -6328,7 +6437,7 @@
         <v>19.595035924232526</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>1</v>
       </c>
@@ -6340,6 +6449,9 @@
       </c>
       <c r="D144" s="3">
         <v>45561</v>
+      </c>
+      <c r="E144" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F144" s="1">
         <v>153.1</v>
@@ -6368,7 +6480,7 @@
         <v>13.063357282821686</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>1</v>
       </c>
@@ -6380,6 +6492,9 @@
       </c>
       <c r="D145" s="3">
         <v>45561</v>
+      </c>
+      <c r="E145" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F145" s="1">
         <v>153.1</v>
@@ -6408,7 +6523,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>1</v>
       </c>
@@ -6420,6 +6535,9 @@
       </c>
       <c r="D146" s="3">
         <v>45561</v>
+      </c>
+      <c r="E146" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F146" s="1">
         <v>153.1</v>
@@ -6448,7 +6566,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>2</v>
       </c>
@@ -6460,6 +6578,9 @@
       </c>
       <c r="D147" s="3">
         <v>45561</v>
+      </c>
+      <c r="E147" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F147" s="1">
         <v>153.1</v>
@@ -6485,7 +6606,7 @@
         <v>19.595035924232526</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>2</v>
       </c>
@@ -6497,6 +6618,9 @@
       </c>
       <c r="D148" s="3">
         <v>45561</v>
+      </c>
+      <c r="E148" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F148" s="1">
         <v>153.1</v>
@@ -6522,7 +6646,7 @@
         <v>84.911822338340954</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>2</v>
       </c>
@@ -6534,6 +6658,9 @@
       </c>
       <c r="D149" s="3">
         <v>45561</v>
+      </c>
+      <c r="E149" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F149" s="1">
         <v>153.1</v>
@@ -6559,7 +6686,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>2</v>
       </c>
@@ -6571,6 +6698,9 @@
       </c>
       <c r="D150" s="3">
         <v>45561</v>
+      </c>
+      <c r="E150" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F150" s="1">
         <v>153.1</v>
@@ -6596,7 +6726,7 @@
         <v>26.126714565643372</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>2</v>
       </c>
@@ -6608,6 +6738,9 @@
       </c>
       <c r="D151" s="3">
         <v>45561</v>
+      </c>
+      <c r="E151" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F151" s="1">
         <v>153.1</v>
@@ -6636,7 +6769,7 @@
         <v>19.595035924232526</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>2</v>
       </c>
@@ -6648,6 +6781,9 @@
       </c>
       <c r="D152" s="3">
         <v>45561</v>
+      </c>
+      <c r="E152" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F152" s="1">
         <v>153.1</v>
@@ -6676,7 +6812,7 @@
         <v>32.658393207054218</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>2</v>
       </c>
@@ -6688,6 +6824,9 @@
       </c>
       <c r="D153" s="3">
         <v>45561</v>
+      </c>
+      <c r="E153" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F153" s="1">
         <v>153.1</v>
@@ -6716,7 +6855,7 @@
         <v>13.063357282821686</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>2</v>
       </c>
@@ -6728,6 +6867,9 @@
       </c>
       <c r="D154" s="3">
         <v>45561</v>
+      </c>
+      <c r="E154" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F154" s="1">
         <v>153.1</v>
@@ -6753,7 +6895,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>2</v>
       </c>
@@ -6765,6 +6907,9 @@
       </c>
       <c r="D155" s="3">
         <v>45561</v>
+      </c>
+      <c r="E155" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F155" s="1">
         <v>153.1</v>
@@ -6793,7 +6938,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>3</v>
       </c>
@@ -6805,6 +6950,9 @@
       </c>
       <c r="D156" s="3">
         <v>45561</v>
+      </c>
+      <c r="E156" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F156" s="1">
         <v>153.1</v>
@@ -6830,7 +6978,7 @@
         <v>58.785107772697586</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>3</v>
       </c>
@@ -6842,6 +6990,9 @@
       </c>
       <c r="D157" s="3">
         <v>45561</v>
+      </c>
+      <c r="E157" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F157" s="1">
         <v>153.1</v>
@@ -6867,7 +7018,7 @@
         <v>104.50685826257349</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>3</v>
       </c>
@@ -6879,6 +7030,9 @@
       </c>
       <c r="D158" s="3">
         <v>45561</v>
+      </c>
+      <c r="E158" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F158" s="1">
         <v>153.1</v>
@@ -6907,7 +7061,7 @@
         <v>19.595035924232526</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>3</v>
       </c>
@@ -6919,6 +7073,9 @@
       </c>
       <c r="D159" s="3">
         <v>45561</v>
+      </c>
+      <c r="E159" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F159" s="1">
         <v>153.1</v>
@@ -6947,7 +7104,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>3</v>
       </c>
@@ -6959,6 +7116,9 @@
       </c>
       <c r="D160" s="3">
         <v>45561</v>
+      </c>
+      <c r="E160" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F160" s="1">
         <v>153.1</v>
@@ -6987,7 +7147,7 @@
         <v>26.126714565643372</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>3</v>
       </c>
@@ -6999,6 +7159,9 @@
       </c>
       <c r="D161" s="3">
         <v>45561</v>
+      </c>
+      <c r="E161" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F161" s="1">
         <v>153.1</v>
@@ -7027,7 +7190,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>3</v>
       </c>
@@ -7039,6 +7202,9 @@
       </c>
       <c r="D162" s="3">
         <v>45561</v>
+      </c>
+      <c r="E162" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F162" s="1">
         <v>153.1</v>
@@ -7067,7 +7233,7 @@
         <v>13.063357282821686</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>3</v>
       </c>
@@ -7079,6 +7245,9 @@
       </c>
       <c r="D163" s="3">
         <v>45561</v>
+      </c>
+      <c r="E163" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F163" s="1">
         <v>153.1</v>
@@ -7104,7 +7273,7 @@
         <v>6.531678641410843</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>3</v>
       </c>
@@ -7116,6 +7285,9 @@
       </c>
       <c r="D164" s="3">
         <v>45561</v>
+      </c>
+      <c r="E164" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F164" s="1">
         <v>153.1</v>
@@ -7141,7 +7313,7 @@
         <v>13.063357282821686</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>3</v>
       </c>
@@ -7153,6 +7325,9 @@
       </c>
       <c r="D165" s="3">
         <v>45561</v>
+      </c>
+      <c r="E165" s="7">
+        <v>0.52361111111111103</v>
       </c>
       <c r="F165" s="1">
         <v>153.1</v>
@@ -7181,7 +7356,7 @@
         <v>13.063357282821686</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>1</v>
       </c>
@@ -7193,6 +7368,9 @@
       </c>
       <c r="D166" s="5">
         <v>45546</v>
+      </c>
+      <c r="E166" s="7">
+        <v>0.6430555555555556</v>
       </c>
       <c r="F166" s="1">
         <v>132.46</v>
@@ -7218,7 +7396,7 @@
         <v>98.142835573003168</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>1</v>
       </c>
@@ -7230,6 +7408,9 @@
       </c>
       <c r="D167" s="5">
         <v>45546</v>
+      </c>
+      <c r="E167" s="7">
+        <v>0.6430555555555556</v>
       </c>
       <c r="F167" s="1">
         <v>132.46</v>
@@ -7258,7 +7439,7 @@
         <v>22.648346670693041</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>1</v>
       </c>
@@ -7270,6 +7451,9 @@
       </c>
       <c r="D168" s="5">
         <v>45546</v>
+      </c>
+      <c r="E168" s="7">
+        <v>0.6430555555555556</v>
       </c>
       <c r="F168" s="1">
         <v>132.46</v>
@@ -7298,7 +7482,7 @@
         <v>60.395591121848099</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>1</v>
       </c>
@@ -7310,6 +7494,9 @@
       </c>
       <c r="D169" s="5">
         <v>45546</v>
+      </c>
+      <c r="E169" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F169" s="1">
         <v>132.46</v>
@@ -7338,7 +7525,7 @@
         <v>60.395591121848099</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>1</v>
       </c>
@@ -7350,6 +7537,9 @@
       </c>
       <c r="D170" s="5">
         <v>45546</v>
+      </c>
+      <c r="E170" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F170" s="1">
         <v>132.46</v>
@@ -7378,7 +7568,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>1</v>
       </c>
@@ -7390,6 +7580,9 @@
       </c>
       <c r="D171" s="5">
         <v>45546</v>
+      </c>
+      <c r="E171" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F171" s="1">
         <v>132.46</v>
@@ -7418,7 +7611,7 @@
         <v>30.19779556092405</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>1</v>
       </c>
@@ -7430,6 +7623,9 @@
       </c>
       <c r="D172" s="5">
         <v>45546</v>
+      </c>
+      <c r="E172" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F172" s="1">
         <v>132.46</v>
@@ -7455,7 +7651,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>1</v>
       </c>
@@ -7467,6 +7663,9 @@
       </c>
       <c r="D173" s="5">
         <v>45546</v>
+      </c>
+      <c r="E173" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F173" s="1">
         <v>132.46</v>
@@ -7495,7 +7694,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>1</v>
       </c>
@@ -7507,6 +7706,9 @@
       </c>
       <c r="D174" s="5">
         <v>45546</v>
+      </c>
+      <c r="E174" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F174" s="1">
         <v>132.46</v>
@@ -7532,7 +7734,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>2</v>
       </c>
@@ -7544,6 +7746,9 @@
       </c>
       <c r="D175" s="5">
         <v>45546</v>
+      </c>
+      <c r="E175" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F175" s="1">
         <v>132.46</v>
@@ -7572,7 +7777,7 @@
         <v>83.043937792541143</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>2</v>
       </c>
@@ -7584,6 +7789,9 @@
       </c>
       <c r="D176" s="5">
         <v>45546</v>
+      </c>
+      <c r="E176" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F176" s="1">
         <v>132.46</v>
@@ -7612,7 +7820,7 @@
         <v>15.098897780462025</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>2</v>
       </c>
@@ -7624,6 +7832,9 @@
       </c>
       <c r="D177" s="5">
         <v>45546</v>
+      </c>
+      <c r="E177" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F177" s="1">
         <v>132.46</v>
@@ -7649,7 +7860,7 @@
         <v>158.53842669485127</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>2</v>
       </c>
@@ -7661,6 +7872,9 @@
       </c>
       <c r="D178" s="5">
         <v>45546</v>
+      </c>
+      <c r="E178" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F178" s="1">
         <v>132.46</v>
@@ -7689,7 +7903,7 @@
         <v>45.296693341386081</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>2</v>
       </c>
@@ -7701,6 +7915,9 @@
       </c>
       <c r="D179" s="5">
         <v>45546</v>
+      </c>
+      <c r="E179" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F179" s="1">
         <v>132.46</v>
@@ -7729,7 +7946,7 @@
         <v>67.945040012079119</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>2</v>
       </c>
@@ -7741,6 +7958,9 @@
       </c>
       <c r="D180" s="5">
         <v>45546</v>
+      </c>
+      <c r="E180" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F180" s="1">
         <v>132.46</v>
@@ -7766,7 +7986,7 @@
         <v>15.098897780462025</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>2</v>
       </c>
@@ -7778,6 +7998,9 @@
       </c>
       <c r="D181" s="5">
         <v>45546</v>
+      </c>
+      <c r="E181" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F181" s="1">
         <v>132.46</v>
@@ -7806,7 +8029,7 @@
         <v>60.395591121848099</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>2</v>
       </c>
@@ -7818,6 +8041,9 @@
       </c>
       <c r="D182" s="5">
         <v>45546</v>
+      </c>
+      <c r="E182" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F182" s="1">
         <v>132.46</v>
@@ -7843,7 +8069,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>2</v>
       </c>
@@ -7855,6 +8081,9 @@
       </c>
       <c r="D183" s="5">
         <v>45546</v>
+      </c>
+      <c r="E183" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F183" s="1">
         <v>132.46</v>
@@ -7880,7 +8109,7 @@
         <v>15.098897780462025</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>2</v>
       </c>
@@ -7892,6 +8121,9 @@
       </c>
       <c r="D184" s="5">
         <v>45546</v>
+      </c>
+      <c r="E184" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F184" s="1">
         <v>132.46</v>
@@ -7920,7 +8152,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>3</v>
       </c>
@@ -7932,6 +8164,9 @@
       </c>
       <c r="D185" s="5">
         <v>45546</v>
+      </c>
+      <c r="E185" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F185" s="1">
         <v>132.46</v>
@@ -7957,7 +8192,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>3</v>
       </c>
@@ -7969,6 +8204,9 @@
       </c>
       <c r="D186" s="5">
         <v>45546</v>
+      </c>
+      <c r="E186" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F186" s="1">
         <v>132.46</v>
@@ -7994,7 +8232,7 @@
         <v>90.593386682772163</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>3</v>
       </c>
@@ -8006,6 +8244,9 @@
       </c>
       <c r="D187" s="5">
         <v>45546</v>
+      </c>
+      <c r="E187" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F187" s="1">
         <v>132.46</v>
@@ -8034,7 +8275,7 @@
         <v>90.593386682772163</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>3</v>
       </c>
@@ -8046,6 +8287,9 @@
       </c>
       <c r="D188" s="5">
         <v>45546</v>
+      </c>
+      <c r="E188" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F188" s="1">
         <v>132.46</v>
@@ -8074,7 +8318,7 @@
         <v>45.296693341386081</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>3</v>
       </c>
@@ -8086,6 +8330,9 @@
       </c>
       <c r="D189" s="5">
         <v>45546</v>
+      </c>
+      <c r="E189" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F189" s="1">
         <v>132.46</v>
@@ -8114,7 +8361,7 @@
         <v>15.098897780462025</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>3</v>
       </c>
@@ -8126,6 +8373,9 @@
       </c>
       <c r="D190" s="5">
         <v>45546</v>
+      </c>
+      <c r="E190" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F190" s="1">
         <v>132.46</v>
@@ -8154,7 +8404,7 @@
         <v>52.846142231617087</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>3</v>
       </c>
@@ -8166,6 +8416,9 @@
       </c>
       <c r="D191" s="5">
         <v>45546</v>
+      </c>
+      <c r="E191" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F191" s="1">
         <v>132.46</v>
@@ -8191,7 +8444,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>3</v>
       </c>
@@ -8203,6 +8456,9 @@
       </c>
       <c r="D192" s="5">
         <v>45546</v>
+      </c>
+      <c r="E192" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F192" s="1">
         <v>132.46</v>
@@ -8231,7 +8487,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>3</v>
       </c>
@@ -8243,6 +8499,9 @@
       </c>
       <c r="D193" s="5">
         <v>45546</v>
+      </c>
+      <c r="E193" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F193" s="1">
         <v>132.46</v>
@@ -8268,7 +8527,7 @@
         <v>15.098897780462025</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>3</v>
       </c>
@@ -8280,6 +8539,9 @@
       </c>
       <c r="D194" s="5">
         <v>45546</v>
+      </c>
+      <c r="E194" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F194" s="1">
         <v>132.46</v>
@@ -8308,7 +8570,7 @@
         <v>30.19779556092405</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>3</v>
       </c>
@@ -8320,6 +8582,9 @@
       </c>
       <c r="D195" s="5">
         <v>45546</v>
+      </c>
+      <c r="E195" s="7">
+        <v>0.64305555555555605</v>
       </c>
       <c r="F195" s="1">
         <v>132.46</v>
@@ -8345,7 +8610,7 @@
         <v>7.5494488902310124</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>1</v>
       </c>
@@ -8357,6 +8622,9 @@
       </c>
       <c r="D196" s="5">
         <v>45574</v>
+      </c>
+      <c r="E196" s="7">
+        <v>0.5</v>
       </c>
       <c r="F196" s="1">
         <v>131.99</v>
@@ -8382,7 +8650,7 @@
         <v>45.457989241609212</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>1</v>
       </c>
@@ -8394,6 +8662,9 @@
       </c>
       <c r="D197" s="5">
         <v>45574</v>
+      </c>
+      <c r="E197" s="7">
+        <v>0.5</v>
       </c>
       <c r="F197" s="1">
         <v>131.99</v>
@@ -8419,7 +8690,7 @@
         <v>189.40828850670505</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>1</v>
       </c>
@@ -8431,6 +8702,9 @@
       </c>
       <c r="D198" s="5">
         <v>45574</v>
+      </c>
+      <c r="E198" s="7">
+        <v>0.5</v>
       </c>
       <c r="F198" s="1">
         <v>131.99</v>
@@ -8459,7 +8733,7 @@
         <v>37.881657701341005</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>1</v>
       </c>
@@ -8471,6 +8745,9 @@
       </c>
       <c r="D199" s="5">
         <v>45574</v>
+      </c>
+      <c r="E199" s="7">
+        <v>0.5</v>
       </c>
       <c r="F199" s="1">
         <v>131.99</v>
@@ -8499,7 +8776,7 @@
         <v>30.305326161072806</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>1</v>
       </c>
@@ -8511,6 +8788,9 @@
       </c>
       <c r="D200" s="5">
         <v>45574</v>
+      </c>
+      <c r="E200" s="7">
+        <v>0.5</v>
       </c>
       <c r="F200" s="1">
         <v>131.99</v>
@@ -8539,7 +8819,7 @@
         <v>15.152663080536403</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>1</v>
       </c>
@@ -8551,6 +8831,9 @@
       </c>
       <c r="D201" s="5">
         <v>45574</v>
+      </c>
+      <c r="E201" s="7">
+        <v>0.5</v>
       </c>
       <c r="F201" s="1">
         <v>131.99</v>
@@ -8579,7 +8862,7 @@
         <v>30.305326161072806</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>1</v>
       </c>
@@ -8591,6 +8874,9 @@
       </c>
       <c r="D202" s="5">
         <v>45574</v>
+      </c>
+      <c r="E202" s="7">
+        <v>0.5</v>
       </c>
       <c r="F202" s="1">
         <v>131.99</v>
@@ -8616,7 +8902,7 @@
         <v>22.728994620804606</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>1</v>
       </c>
@@ -8628,6 +8914,9 @@
       </c>
       <c r="D203" s="5">
         <v>45574</v>
+      </c>
+      <c r="E203" s="7">
+        <v>0.5</v>
       </c>
       <c r="F203" s="1">
         <v>131.99</v>
@@ -8656,7 +8945,7 @@
         <v>90.915978483218424</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>1</v>
       </c>
@@ -8668,6 +8957,9 @@
       </c>
       <c r="D204" s="5">
         <v>45574</v>
+      </c>
+      <c r="E204" s="7">
+        <v>0.5</v>
       </c>
       <c r="F204" s="1">
         <v>131.99</v>
@@ -8693,7 +8985,7 @@
         <v>45.457989241609212</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>1</v>
       </c>
@@ -8705,6 +8997,9 @@
       </c>
       <c r="D205" s="5">
         <v>45574</v>
+      </c>
+      <c r="E205" s="7">
+        <v>0.5</v>
       </c>
       <c r="F205" s="1">
         <v>131.99</v>
@@ -8733,7 +9028,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>1</v>
       </c>
@@ -8745,6 +9040,9 @@
       </c>
       <c r="D206" s="5">
         <v>45574</v>
+      </c>
+      <c r="E206" s="7">
+        <v>0.5</v>
       </c>
       <c r="F206" s="1">
         <v>131.99</v>
@@ -8770,7 +9068,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>2</v>
       </c>
@@ -8782,6 +9080,9 @@
       </c>
       <c r="D207" s="5">
         <v>45574</v>
+      </c>
+      <c r="E207" s="7">
+        <v>0.5</v>
       </c>
       <c r="F207" s="1">
         <v>131.99</v>
@@ -8807,7 +9108,7 @@
         <v>45.457989241609212</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>2</v>
       </c>
@@ -8819,6 +9120,9 @@
       </c>
       <c r="D208" s="5">
         <v>45574</v>
+      </c>
+      <c r="E208" s="7">
+        <v>0.5</v>
       </c>
       <c r="F208" s="1">
         <v>131.99</v>
@@ -8844,7 +9148,7 @@
         <v>136.37396772482762</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>2</v>
       </c>
@@ -8856,6 +9160,9 @@
       </c>
       <c r="D209" s="5">
         <v>45574</v>
+      </c>
+      <c r="E209" s="7">
+        <v>0.5</v>
       </c>
       <c r="F209" s="1">
         <v>131.99</v>
@@ -8881,7 +9188,7 @@
         <v>37.881657701341005</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>2</v>
       </c>
@@ -8893,6 +9200,9 @@
       </c>
       <c r="D210" s="5">
         <v>45574</v>
+      </c>
+      <c r="E210" s="7">
+        <v>0.5</v>
       </c>
       <c r="F210" s="1">
         <v>131.99</v>
@@ -8921,7 +9231,7 @@
         <v>37.881657701341005</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>2</v>
       </c>
@@ -8933,6 +9243,9 @@
       </c>
       <c r="D211" s="5">
         <v>45574</v>
+      </c>
+      <c r="E211" s="7">
+        <v>0.5</v>
       </c>
       <c r="F211" s="1">
         <v>131.99</v>
@@ -8958,7 +9271,7 @@
         <v>22.728994620804606</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>2</v>
       </c>
@@ -8970,6 +9283,9 @@
       </c>
       <c r="D212" s="5">
         <v>45574</v>
+      </c>
+      <c r="E212" s="7">
+        <v>0.5</v>
       </c>
       <c r="F212" s="1">
         <v>131.99</v>
@@ -8998,7 +9314,7 @@
         <v>15.152663080536403</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -9010,6 +9326,9 @@
       </c>
       <c r="D213" s="5">
         <v>45574</v>
+      </c>
+      <c r="E213" s="7">
+        <v>0.5</v>
       </c>
       <c r="F213" s="1">
         <v>131.99</v>
@@ -9038,7 +9357,7 @@
         <v>22.728994620804606</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>2</v>
       </c>
@@ -9050,6 +9369,9 @@
       </c>
       <c r="D214" s="5">
         <v>45574</v>
+      </c>
+      <c r="E214" s="7">
+        <v>0.5</v>
       </c>
       <c r="F214" s="1">
         <v>131.99</v>
@@ -9075,7 +9397,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>2</v>
       </c>
@@ -9087,6 +9409,9 @@
       </c>
       <c r="D215" s="5">
         <v>45574</v>
+      </c>
+      <c r="E215" s="7">
+        <v>0.5</v>
       </c>
       <c r="F215" s="1">
         <v>131.99</v>
@@ -9115,7 +9440,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>2</v>
       </c>
@@ -9127,6 +9452,9 @@
       </c>
       <c r="D216" s="5">
         <v>45574</v>
+      </c>
+      <c r="E216" s="7">
+        <v>0.5</v>
       </c>
       <c r="F216" s="1">
         <v>131.99</v>
@@ -9155,7 +9483,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>3</v>
       </c>
@@ -9167,6 +9495,9 @@
       </c>
       <c r="D217" s="5">
         <v>45574</v>
+      </c>
+      <c r="E217" s="7">
+        <v>0.5</v>
       </c>
       <c r="F217" s="1">
         <v>131.99</v>
@@ -9192,7 +9523,7 @@
         <v>37.881657701341005</v>
       </c>
     </row>
-    <row r="218" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>3</v>
       </c>
@@ -9204,6 +9535,9 @@
       </c>
       <c r="D218" s="5">
         <v>45574</v>
+      </c>
+      <c r="E218" s="7">
+        <v>0.5</v>
       </c>
       <c r="F218" s="1">
         <v>131.99</v>
@@ -9229,7 +9563,7 @@
         <v>174.25562542616862</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>3</v>
       </c>
@@ -9241,6 +9575,9 @@
       </c>
       <c r="D219" s="5">
         <v>45574</v>
+      </c>
+      <c r="E219" s="7">
+        <v>0.5</v>
       </c>
       <c r="F219" s="1">
         <v>131.99</v>
@@ -9266,7 +9603,7 @@
         <v>90.915978483218424</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>3</v>
       </c>
@@ -9278,6 +9615,9 @@
       </c>
       <c r="D220" s="5">
         <v>45574</v>
+      </c>
+      <c r="E220" s="7">
+        <v>0.5</v>
       </c>
       <c r="F220" s="1">
         <v>131.99</v>
@@ -9303,7 +9643,7 @@
         <v>60.610652322145611</v>
       </c>
     </row>
-    <row r="221" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>3</v>
       </c>
@@ -9315,6 +9655,9 @@
       </c>
       <c r="D221" s="5">
         <v>45574</v>
+      </c>
+      <c r="E221" s="7">
+        <v>0.5</v>
       </c>
       <c r="F221" s="1">
         <v>131.99</v>
@@ -9343,7 +9686,7 @@
         <v>15.152663080536403</v>
       </c>
     </row>
-    <row r="222" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>3</v>
       </c>
@@ -9355,6 +9698,9 @@
       </c>
       <c r="D222" s="5">
         <v>45574</v>
+      </c>
+      <c r="E222" s="7">
+        <v>0.5</v>
       </c>
       <c r="F222" s="1">
         <v>131.99</v>
@@ -9383,7 +9729,7 @@
         <v>22.728994620804606</v>
       </c>
     </row>
-    <row r="223" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>3</v>
       </c>
@@ -9395,6 +9741,9 @@
       </c>
       <c r="D223" s="5">
         <v>45574</v>
+      </c>
+      <c r="E223" s="7">
+        <v>0.5</v>
       </c>
       <c r="F223" s="1">
         <v>131.99</v>
@@ -9423,7 +9772,7 @@
         <v>15.152663080536403</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>3</v>
       </c>
@@ -9435,6 +9784,9 @@
       </c>
       <c r="D224" s="5">
         <v>45574</v>
+      </c>
+      <c r="E224" s="7">
+        <v>0.5</v>
       </c>
       <c r="F224" s="1">
         <v>131.99</v>
@@ -9463,7 +9815,7 @@
         <v>37.881657701341005</v>
       </c>
     </row>
-    <row r="225" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>3</v>
       </c>
@@ -9475,6 +9827,9 @@
       </c>
       <c r="D225" s="5">
         <v>45574</v>
+      </c>
+      <c r="E225" s="7">
+        <v>0.5</v>
       </c>
       <c r="F225" s="1">
         <v>131.99</v>
@@ -9503,7 +9858,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="226" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>3</v>
       </c>
@@ -9515,6 +9870,9 @@
       </c>
       <c r="D226" s="5">
         <v>45574</v>
+      </c>
+      <c r="E226" s="7">
+        <v>0.5</v>
       </c>
       <c r="F226" s="1">
         <v>131.99</v>
@@ -9540,7 +9898,7 @@
         <v>7.5763315402682014</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>1</v>
       </c>
@@ -9583,7 +9941,7 @@
         <v>987.30606488011279</v>
       </c>
     </row>
-    <row r="228" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>1</v>
       </c>
@@ -9626,7 +9984,7 @@
         <v>22.270061613837132</v>
       </c>
     </row>
-    <row r="229" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>1</v>
       </c>
@@ -9669,7 +10027,7 @@
         <v>386.01440130651025</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>1</v>
       </c>
@@ -9712,7 +10070,7 @@
         <v>22.270061613837132</v>
       </c>
     </row>
-    <row r="231" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>1</v>
       </c>
@@ -9755,7 +10113,7 @@
         <v>14.846707742558086</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>1</v>
       </c>
@@ -9795,7 +10153,7 @@
         <v>96.503600326627563</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>1</v>
       </c>
@@ -9838,7 +10196,7 @@
         <v>51.963477098953305</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>1</v>
       </c>
@@ -9881,7 +10239,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>1</v>
       </c>
@@ -9921,7 +10279,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="236" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>2</v>
       </c>
@@ -9964,7 +10322,7 @@
         <v>185.58384678197609</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>2</v>
       </c>
@@ -10007,7 +10365,7 @@
         <v>749.75874099918337</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>2</v>
       </c>
@@ -10050,7 +10408,7 @@
         <v>22.270061613837132</v>
       </c>
     </row>
-    <row r="239" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>2</v>
       </c>
@@ -10093,7 +10451,7 @@
         <v>66.810184841511401</v>
       </c>
     </row>
-    <row r="240" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>2</v>
       </c>
@@ -10136,7 +10494,7 @@
         <v>29.693415485116173</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>2</v>
       </c>
@@ -10179,7 +10537,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="242" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>2</v>
       </c>
@@ -10222,7 +10580,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="243" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>2</v>
       </c>
@@ -10262,7 +10620,7 @@
         <v>51.963477098953305</v>
       </c>
     </row>
-    <row r="244" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>2</v>
       </c>
@@ -10305,7 +10663,7 @@
         <v>14.846707742558086</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>2</v>
       </c>
@@ -10345,7 +10703,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="246" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>3</v>
       </c>
@@ -10388,7 +10746,7 @@
         <v>504.78806324697501</v>
       </c>
     </row>
-    <row r="247" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>3</v>
       </c>
@@ -10428,7 +10786,7 @@
         <v>96.503600326627563</v>
       </c>
     </row>
-    <row r="248" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>3</v>
       </c>
@@ -10471,7 +10829,7 @@
         <v>193.00720065325513</v>
       </c>
     </row>
-    <row r="249" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>3</v>
       </c>
@@ -10514,7 +10872,7 @@
         <v>29.693415485116173</v>
       </c>
     </row>
-    <row r="250" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>3</v>
       </c>
@@ -10557,7 +10915,7 @@
         <v>22.270061613837132</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>3</v>
       </c>
@@ -10600,7 +10958,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="252" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>3</v>
       </c>
@@ -10643,7 +11001,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="253" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>3</v>
       </c>
@@ -10686,7 +11044,7 @@
         <v>22.270061613837132</v>
       </c>
     </row>
-    <row r="254" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>3</v>
       </c>
@@ -10729,7 +11087,7 @@
         <v>7.4233538712790432</v>
       </c>
     </row>
-    <row r="255" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>1</v>
       </c>
@@ -10741,6 +11099,9 @@
       </c>
       <c r="D255" s="5">
         <v>45498</v>
+      </c>
+      <c r="E255" s="7">
+        <v>0.48819444444444443</v>
       </c>
       <c r="F255" s="1">
         <v>132.02000000000001</v>
@@ -10766,7 +11127,7 @@
         <v>356.00666565671861</v>
       </c>
     </row>
-    <row r="256" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>1</v>
       </c>
@@ -10778,6 +11139,9 @@
       </c>
       <c r="D256" s="5">
         <v>45498</v>
+      </c>
+      <c r="E256" s="7">
+        <v>0.48819444444444443</v>
       </c>
       <c r="F256" s="1">
         <v>132.02000000000001</v>
@@ -10806,7 +11170,7 @@
         <v>272.68595667323132</v>
       </c>
     </row>
-    <row r="257" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>1</v>
       </c>
@@ -10818,6 +11182,9 @@
       </c>
       <c r="D257" s="5">
         <v>45498</v>
+      </c>
+      <c r="E257" s="7">
+        <v>0.48819444444444443</v>
       </c>
       <c r="F257" s="1">
         <v>132.02000000000001</v>
@@ -10843,7 +11210,7 @@
         <v>159.06680805938493</v>
       </c>
     </row>
-    <row r="258" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>1</v>
       </c>
@@ -10855,6 +11222,9 @@
       </c>
       <c r="D258" s="5">
         <v>45498</v>
+      </c>
+      <c r="E258" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F258" s="1">
         <v>132.02000000000001</v>
@@ -10883,7 +11253,7 @@
         <v>22.723829722769278</v>
       </c>
     </row>
-    <row r="259" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>1</v>
       </c>
@@ -10895,6 +11265,9 @@
       </c>
       <c r="D259" s="5">
         <v>45498</v>
+      </c>
+      <c r="E259" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F259" s="1">
         <v>132.02000000000001</v>
@@ -10920,7 +11293,7 @@
         <v>53.022269353128308</v>
       </c>
     </row>
-    <row r="260" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>1</v>
       </c>
@@ -10932,6 +11305,9 @@
       </c>
       <c r="D260" s="5">
         <v>45498</v>
+      </c>
+      <c r="E260" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F260" s="1">
         <v>132.02000000000001</v>
@@ -10957,7 +11333,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>1</v>
       </c>
@@ -10969,6 +11345,9 @@
       </c>
       <c r="D261" s="5">
         <v>45498</v>
+      </c>
+      <c r="E261" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F261" s="1">
         <v>132.02000000000001</v>
@@ -10997,7 +11376,7 @@
         <v>45.447659445538555</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>1</v>
       </c>
@@ -11009,6 +11388,9 @@
       </c>
       <c r="D262" s="5">
         <v>45498</v>
+      </c>
+      <c r="E262" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F262" s="1">
         <v>132.02000000000001</v>
@@ -11034,7 +11416,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="263" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>1</v>
       </c>
@@ -11046,6 +11428,9 @@
       </c>
       <c r="D263" s="5">
         <v>45498</v>
+      </c>
+      <c r="E263" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F263" s="1">
         <v>132.02000000000001</v>
@@ -11074,7 +11459,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>1</v>
       </c>
@@ -11086,6 +11471,9 @@
       </c>
       <c r="D264" s="5">
         <v>45498</v>
+      </c>
+      <c r="E264" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F264" s="1">
         <v>132.02000000000001</v>
@@ -11114,7 +11502,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="265" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>2</v>
       </c>
@@ -11126,6 +11514,9 @@
       </c>
       <c r="D265" s="5">
         <v>45498</v>
+      </c>
+      <c r="E265" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F265" s="1">
         <v>132.02000000000001</v>
@@ -11154,7 +11545,7 @@
         <v>90.89531889107711</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>2</v>
       </c>
@@ -11166,6 +11557,9 @@
       </c>
       <c r="D266" s="5">
         <v>45498</v>
+      </c>
+      <c r="E266" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F266" s="1">
         <v>132.02000000000001</v>
@@ -11191,7 +11585,7 @@
         <v>37.873049537948795</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>2</v>
       </c>
@@ -11203,6 +11597,9 @@
       </c>
       <c r="D267" s="5">
         <v>45498</v>
+      </c>
+      <c r="E267" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F267" s="1">
         <v>132.02000000000001</v>
@@ -11228,7 +11625,7 @@
         <v>212.08907741251323</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>2</v>
       </c>
@@ -11240,6 +11637,9 @@
       </c>
       <c r="D268" s="5">
         <v>45498</v>
+      </c>
+      <c r="E268" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F268" s="1">
         <v>132.02000000000001</v>
@@ -11268,7 +11668,7 @@
         <v>30.298439630359034</v>
       </c>
     </row>
-    <row r="269" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>2</v>
       </c>
@@ -11280,6 +11680,9 @@
       </c>
       <c r="D269" s="5">
         <v>45498</v>
+      </c>
+      <c r="E269" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F269" s="1">
         <v>132.02000000000001</v>
@@ -11308,7 +11711,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>2</v>
       </c>
@@ -11320,6 +11723,9 @@
       </c>
       <c r="D270" s="5">
         <v>45498</v>
+      </c>
+      <c r="E270" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F270" s="1">
         <v>132.02000000000001</v>
@@ -11345,7 +11751,7 @@
         <v>22.723829722769278</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>2</v>
       </c>
@@ -11357,6 +11763,9 @@
       </c>
       <c r="D271" s="5">
         <v>45498</v>
+      </c>
+      <c r="E271" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F271" s="1">
         <v>132.02000000000001</v>
@@ -11382,7 +11791,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>3</v>
       </c>
@@ -11394,6 +11803,9 @@
       </c>
       <c r="D272" s="5">
         <v>45498</v>
+      </c>
+      <c r="E272" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F272" s="1">
         <v>132.02000000000001</v>
@@ -11422,7 +11834,7 @@
         <v>15.149219815179517</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>3</v>
       </c>
@@ -11434,6 +11846,9 @@
       </c>
       <c r="D273" s="5">
         <v>45498</v>
+      </c>
+      <c r="E273" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F273" s="1">
         <v>132.02000000000001</v>
@@ -11459,7 +11874,7 @@
         <v>83.320708983487336</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>3</v>
       </c>
@@ -11471,6 +11886,9 @@
       </c>
       <c r="D274" s="5">
         <v>45498</v>
+      </c>
+      <c r="E274" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F274" s="1">
         <v>132.02000000000001</v>
@@ -11496,7 +11914,7 @@
         <v>159.06680805938493</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>3</v>
       </c>
@@ -11508,6 +11926,9 @@
       </c>
       <c r="D275" s="5">
         <v>45498</v>
+      </c>
+      <c r="E275" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F275" s="1">
         <v>132.02000000000001</v>
@@ -11536,7 +11957,7 @@
         <v>22.723829722769278</v>
       </c>
     </row>
-    <row r="276" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>3</v>
       </c>
@@ -11548,6 +11969,9 @@
       </c>
       <c r="D276" s="5">
         <v>45498</v>
+      </c>
+      <c r="E276" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F276" s="1">
         <v>132.02000000000001</v>
@@ -11576,7 +12000,7 @@
         <v>151.49219815179518</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>3</v>
       </c>
@@ -11588,6 +12012,9 @@
       </c>
       <c r="D277" s="5">
         <v>45498</v>
+      </c>
+      <c r="E277" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F277" s="1">
         <v>132.02000000000001</v>
@@ -11613,7 +12040,7 @@
         <v>15.149219815179517</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>3</v>
       </c>
@@ -11625,6 +12052,9 @@
       </c>
       <c r="D278" s="5">
         <v>45498</v>
+      </c>
+      <c r="E278" s="7">
+        <v>0.48819444444444399</v>
       </c>
       <c r="F278" s="1">
         <v>132.02000000000001</v>
@@ -11653,7 +12083,7 @@
         <v>7.5746099075897586</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>1</v>
       </c>
@@ -11664,7 +12094,7 @@
         <v>47</v>
       </c>
       <c r="D279" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E279" s="6">
         <v>0.55138888888888893</v>
@@ -11696,7 +12126,7 @@
         <v>107.02545676936013</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>1</v>
       </c>
@@ -11707,7 +12137,7 @@
         <v>47</v>
       </c>
       <c r="D280" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E280" s="6">
         <v>0.55138888888888893</v>
@@ -11736,7 +12166,7 @@
         <v>15.289350967051448</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>1</v>
       </c>
@@ -11747,7 +12177,7 @@
         <v>47</v>
       </c>
       <c r="D281" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E281" s="6">
         <v>0.55138888888888893</v>
@@ -11779,7 +12209,7 @@
         <v>22.934026450577171</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>1</v>
       </c>
@@ -11790,7 +12220,7 @@
         <v>47</v>
       </c>
       <c r="D282" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E282" s="6">
         <v>0.55138888888888893</v>
@@ -11822,7 +12252,7 @@
         <v>30.578701934102895</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>1</v>
       </c>
@@ -11833,7 +12263,7 @@
         <v>47</v>
       </c>
       <c r="D283" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E283" s="6">
         <v>0.55138888888888893</v>
@@ -11865,7 +12295,7 @@
         <v>22.934026450577171</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>1</v>
       </c>
@@ -11876,7 +12306,7 @@
         <v>47</v>
       </c>
       <c r="D284" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E284" s="6">
         <v>0.55138888888888893</v>
@@ -11905,7 +12335,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>2</v>
       </c>
@@ -11916,7 +12346,7 @@
         <v>47</v>
       </c>
       <c r="D285" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E285" s="6">
         <v>0.55138888888888893</v>
@@ -11948,7 +12378,7 @@
         <v>38.223377417628619</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>2</v>
       </c>
@@ -11959,7 +12389,7 @@
         <v>47</v>
       </c>
       <c r="D286" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E286" s="6">
         <v>0.55138888888888893</v>
@@ -11991,7 +12421,7 @@
         <v>22.934026450577171</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>2</v>
       </c>
@@ -12002,7 +12432,7 @@
         <v>47</v>
       </c>
       <c r="D287" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E287" s="6">
         <v>0.55138888888888893</v>
@@ -12034,7 +12464,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>2</v>
       </c>
@@ -12045,7 +12475,7 @@
         <v>47</v>
       </c>
       <c r="D288" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E288" s="6">
         <v>0.55138888888888893</v>
@@ -12074,7 +12504,7 @@
         <v>45.868052901154343</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>2</v>
       </c>
@@ -12085,7 +12515,7 @@
         <v>47</v>
       </c>
       <c r="D289" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E289" s="6">
         <v>0.55138888888888893</v>
@@ -12117,7 +12547,7 @@
         <v>15.289350967051448</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>2</v>
       </c>
@@ -12128,7 +12558,7 @@
         <v>47</v>
       </c>
       <c r="D290" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E290" s="6">
         <v>0.55138888888888893</v>
@@ -12160,7 +12590,7 @@
         <v>22.934026450577171</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>3</v>
       </c>
@@ -12171,7 +12601,7 @@
         <v>47</v>
       </c>
       <c r="D291" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E291" s="6">
         <v>0.55138888888888893</v>
@@ -12203,7 +12633,7 @@
         <v>84.091430318782969</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>3</v>
       </c>
@@ -12214,7 +12644,7 @@
         <v>47</v>
       </c>
       <c r="D292" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E292" s="6">
         <v>0.55138888888888893</v>
@@ -12243,7 +12673,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>3</v>
       </c>
@@ -12254,7 +12684,7 @@
         <v>47</v>
       </c>
       <c r="D293" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E293" s="6">
         <v>0.55138888888888893</v>
@@ -12286,7 +12716,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>3</v>
       </c>
@@ -12297,7 +12727,7 @@
         <v>47</v>
       </c>
       <c r="D294" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E294" s="6">
         <v>0.55138888888888893</v>
@@ -12326,7 +12756,7 @@
         <v>22.934026450577171</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>3</v>
       </c>
@@ -12337,7 +12767,7 @@
         <v>47</v>
       </c>
       <c r="D295" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E295" s="6">
         <v>0.55138888888888893</v>
@@ -12369,7 +12799,7 @@
         <v>15.289350967051448</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>3</v>
       </c>
@@ -12380,7 +12810,7 @@
         <v>47</v>
       </c>
       <c r="D296" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E296" s="6">
         <v>0.55138888888888893</v>
@@ -12412,7 +12842,7 @@
         <v>30.578701934102895</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>3</v>
       </c>
@@ -12423,7 +12853,7 @@
         <v>47</v>
       </c>
       <c r="D297" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E297" s="6">
         <v>0.55138888888888893</v>
@@ -12455,7 +12885,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>3</v>
       </c>
@@ -12466,7 +12896,7 @@
         <v>47</v>
       </c>
       <c r="D298" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E298" s="6">
         <v>0.55138888888888893</v>
@@ -12495,7 +12925,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>3</v>
       </c>
@@ -12506,7 +12936,7 @@
         <v>47</v>
       </c>
       <c r="D299" s="5">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="E299" s="6">
         <v>0.55138888888888893</v>
@@ -12535,7 +12965,7 @@
         <v>7.6446754835257238</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>1</v>
       </c>
@@ -12578,7 +13008,7 @@
         <v>160.32648301996792</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>1</v>
       </c>
@@ -12621,7 +13051,7 @@
         <v>357.09080308992856</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>1</v>
       </c>
@@ -12661,7 +13091,7 @@
         <v>14.575134819997086</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>1</v>
       </c>
@@ -12704,7 +13134,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>1</v>
       </c>
@@ -12747,7 +13177,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>1</v>
       </c>
@@ -12790,7 +13220,7 @@
         <v>14.575134819997086</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>1</v>
       </c>
@@ -12833,7 +13263,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>2</v>
       </c>
@@ -12876,7 +13306,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>2</v>
       </c>
@@ -12919,7 +13349,7 @@
         <v>342.5156682699315</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>2</v>
       </c>
@@ -12962,7 +13392,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>2</v>
       </c>
@@ -13005,7 +13435,7 @@
         <v>233.20215711995337</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>2</v>
       </c>
@@ -13048,7 +13478,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>2</v>
       </c>
@@ -13091,7 +13521,7 @@
         <v>14.575134819997086</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>2</v>
       </c>
@@ -13134,7 +13564,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>2</v>
       </c>
@@ -13177,7 +13607,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>2</v>
       </c>
@@ -13220,7 +13650,7 @@
         <v>14.575134819997086</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>3</v>
       </c>
@@ -13263,7 +13693,7 @@
         <v>378.9535053199242</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>3</v>
       </c>
@@ -13306,7 +13736,7 @@
         <v>14.575134819997086</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>3</v>
       </c>
@@ -13349,7 +13779,7 @@
         <v>145.75134819997083</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>3</v>
       </c>
@@ -13389,7 +13819,7 @@
         <v>14.575134819997086</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>3</v>
       </c>
@@ -13432,7 +13862,7 @@
         <v>43.725404459991253</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>3</v>
       </c>
@@ -13475,7 +13905,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>3</v>
       </c>
@@ -13518,7 +13948,7 @@
         <v>21.862702229995627</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>3</v>
       </c>
@@ -13558,7 +13988,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>3</v>
       </c>
@@ -13601,7 +14031,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>3</v>
       </c>
@@ -13641,7 +14071,7 @@
         <v>7.2875674099985428</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>1</v>
       </c>
@@ -13653,6 +14083,9 @@
       </c>
       <c r="D326" s="5">
         <v>45491</v>
+      </c>
+      <c r="E326" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F326" s="1">
         <v>69.709999999999994</v>
@@ -13681,7 +14114,7 @@
         <v>186.48687419308567</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>1</v>
       </c>
@@ -13693,6 +14126,9 @@
       </c>
       <c r="D327" s="5">
         <v>45491</v>
+      </c>
+      <c r="E327" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F327" s="1">
         <v>69.709999999999994</v>
@@ -13721,7 +14157,7 @@
         <v>416.00918089226803</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>1</v>
       </c>
@@ -13733,6 +14169,9 @@
       </c>
       <c r="D328" s="5">
         <v>45491</v>
+      </c>
+      <c r="E328" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F328" s="1">
         <v>69.709999999999994</v>
@@ -13761,7 +14200,7 @@
         <v>57.380576674795591</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>1</v>
       </c>
@@ -13773,6 +14212,9 @@
       </c>
       <c r="D329" s="5">
         <v>45491</v>
+      </c>
+      <c r="E329" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F329" s="1">
         <v>69.709999999999994</v>
@@ -13798,7 +14240,7 @@
         <v>114.76115334959118</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>1</v>
       </c>
@@ -13810,6 +14252,9 @@
       </c>
       <c r="D330" s="5">
         <v>45491</v>
+      </c>
+      <c r="E330" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F330" s="1">
         <v>69.709999999999994</v>
@@ -13838,7 +14283,7 @@
         <v>344.28346004877352</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>1</v>
       </c>
@@ -13850,6 +14295,9 @@
       </c>
       <c r="D331" s="5">
         <v>45491</v>
+      </c>
+      <c r="E331" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F331" s="1">
         <v>69.709999999999994</v>
@@ -13875,7 +14323,7 @@
         <v>114.76115334959118</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>1</v>
       </c>
@@ -13887,6 +14335,9 @@
       </c>
       <c r="D332" s="5">
         <v>45491</v>
+      </c>
+      <c r="E332" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F332" s="1">
         <v>69.709999999999994</v>
@@ -13915,7 +14366,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>1</v>
       </c>
@@ -13927,6 +14378,9 @@
       </c>
       <c r="D333" s="5">
         <v>45491</v>
+      </c>
+      <c r="E333" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F333" s="1">
         <v>69.709999999999994</v>
@@ -13955,7 +14409,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>1</v>
       </c>
@@ -13967,6 +14421,9 @@
       </c>
       <c r="D334" s="5">
         <v>45491</v>
+      </c>
+      <c r="E334" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F334" s="1">
         <v>69.709999999999994</v>
@@ -13995,7 +14452,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>1</v>
       </c>
@@ -14007,6 +14464,9 @@
       </c>
       <c r="D335" s="5">
         <v>45491</v>
+      </c>
+      <c r="E335" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F335" s="1">
         <v>69.709999999999994</v>
@@ -14035,7 +14495,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>1</v>
       </c>
@@ -14047,6 +14507,9 @@
       </c>
       <c r="D336" s="5">
         <v>45491</v>
+      </c>
+      <c r="E336" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F336" s="1">
         <v>69.709999999999994</v>
@@ -14072,7 +14535,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>1</v>
       </c>
@@ -14084,6 +14547,9 @@
       </c>
       <c r="D337" s="5">
         <v>45491</v>
+      </c>
+      <c r="E337" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F337" s="1">
         <v>69.709999999999994</v>
@@ -14109,7 +14575,7 @@
         <v>86.07086501219338</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>2</v>
       </c>
@@ -14121,6 +14587,9 @@
       </c>
       <c r="D338" s="5">
         <v>45491</v>
+      </c>
+      <c r="E338" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F338" s="1">
         <v>69.709999999999994</v>
@@ -14149,7 +14618,7 @@
         <v>487.73490173576249</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>2</v>
       </c>
@@ -14161,6 +14630,9 @@
       </c>
       <c r="D339" s="5">
         <v>45491</v>
+      </c>
+      <c r="E339" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F339" s="1">
         <v>69.709999999999994</v>
@@ -14189,7 +14661,7 @@
         <v>315.59317171137576</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>2</v>
       </c>
@@ -14201,6 +14673,9 @@
       </c>
       <c r="D340" s="5">
         <v>45491</v>
+      </c>
+      <c r="E340" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F340" s="1">
         <v>69.709999999999994</v>
@@ -14229,7 +14704,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>2</v>
       </c>
@@ -14241,6 +14716,9 @@
       </c>
       <c r="D341" s="5">
         <v>45491</v>
+      </c>
+      <c r="E341" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F341" s="1">
         <v>69.709999999999994</v>
@@ -14269,7 +14747,7 @@
         <v>315.59317171137576</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>2</v>
       </c>
@@ -14281,6 +14759,9 @@
       </c>
       <c r="D342" s="5">
         <v>45491</v>
+      </c>
+      <c r="E342" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F342" s="1">
         <v>69.709999999999994</v>
@@ -14309,7 +14790,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="343" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>2</v>
       </c>
@@ -14321,6 +14802,9 @@
       </c>
       <c r="D343" s="5">
         <v>45491</v>
+      </c>
+      <c r="E343" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F343" s="1">
         <v>69.709999999999994</v>
@@ -14346,7 +14830,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="344" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>2</v>
       </c>
@@ -14358,6 +14842,9 @@
       </c>
       <c r="D344" s="5">
         <v>45491</v>
+      </c>
+      <c r="E344" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F344" s="1">
         <v>69.709999999999994</v>
@@ -14383,7 +14870,7 @@
         <v>129.10629751829006</v>
       </c>
     </row>
-    <row r="345" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>2</v>
       </c>
@@ -14395,6 +14882,9 @@
       </c>
       <c r="D345" s="5">
         <v>45491</v>
+      </c>
+      <c r="E345" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F345" s="1">
         <v>69.709999999999994</v>
@@ -14423,7 +14913,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="346" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>2</v>
       </c>
@@ -14435,6 +14925,9 @@
       </c>
       <c r="D346" s="5">
         <v>45491</v>
+      </c>
+      <c r="E346" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F346" s="1">
         <v>69.709999999999994</v>
@@ -14460,7 +14953,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="347" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>2</v>
       </c>
@@ -14472,6 +14965,9 @@
       </c>
       <c r="D347" s="5">
         <v>45491</v>
+      </c>
+      <c r="E347" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F347" s="1">
         <v>69.709999999999994</v>
@@ -14497,7 +14993,7 @@
         <v>57.380576674795591</v>
       </c>
     </row>
-    <row r="348" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>3</v>
       </c>
@@ -14509,6 +15005,9 @@
       </c>
       <c r="D348" s="5">
         <v>45491</v>
+      </c>
+      <c r="E348" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F348" s="1">
         <v>69.709999999999994</v>
@@ -14534,7 +15033,7 @@
         <v>57.380576674795591</v>
       </c>
     </row>
-    <row r="349" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>3</v>
       </c>
@@ -14546,6 +15045,9 @@
       </c>
       <c r="D349" s="5">
         <v>45491</v>
+      </c>
+      <c r="E349" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F349" s="1">
         <v>69.709999999999994</v>
@@ -14574,7 +15076,7 @@
         <v>315.59317171137576</v>
       </c>
     </row>
-    <row r="350" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>3</v>
       </c>
@@ -14586,6 +15088,9 @@
       </c>
       <c r="D350" s="5">
         <v>45491</v>
+      </c>
+      <c r="E350" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F350" s="1">
         <v>69.709999999999994</v>
@@ -14614,7 +15119,7 @@
         <v>229.52230669918237</v>
       </c>
     </row>
-    <row r="351" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>3</v>
       </c>
@@ -14626,6 +15131,9 @@
       </c>
       <c r="D351" s="5">
         <v>45491</v>
+      </c>
+      <c r="E351" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F351" s="1">
         <v>69.709999999999994</v>
@@ -14654,7 +15162,7 @@
         <v>57.380576674795591</v>
       </c>
     </row>
-    <row r="352" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>3</v>
       </c>
@@ -14666,6 +15174,9 @@
       </c>
       <c r="D352" s="5">
         <v>45491</v>
+      </c>
+      <c r="E352" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F352" s="1">
         <v>69.709999999999994</v>
@@ -14691,7 +15202,7 @@
         <v>43.03543250609669</v>
       </c>
     </row>
-    <row r="353" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>3</v>
       </c>
@@ -14703,6 +15214,9 @@
       </c>
       <c r="D353" s="5">
         <v>45491</v>
+      </c>
+      <c r="E353" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F353" s="1">
         <v>69.709999999999994</v>
@@ -14731,7 +15245,7 @@
         <v>372.97374838617134</v>
       </c>
     </row>
-    <row r="354" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>3</v>
       </c>
@@ -14743,6 +15257,9 @@
       </c>
       <c r="D354" s="5">
         <v>45491</v>
+      </c>
+      <c r="E354" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F354" s="1">
         <v>69.709999999999994</v>
@@ -14768,7 +15285,7 @@
         <v>100.41600918089227</v>
       </c>
     </row>
-    <row r="355" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>3</v>
       </c>
@@ -14780,6 +15297,9 @@
       </c>
       <c r="D355" s="5">
         <v>45491</v>
+      </c>
+      <c r="E355" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F355" s="1">
         <v>69.709999999999994</v>
@@ -14808,7 +15328,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="356" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>3</v>
       </c>
@@ -14820,6 +15340,9 @@
       </c>
       <c r="D356" s="5">
         <v>45491</v>
+      </c>
+      <c r="E356" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F356" s="1">
         <v>69.709999999999994</v>
@@ -14845,7 +15368,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="357" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>3</v>
       </c>
@@ -14857,6 +15380,9 @@
       </c>
       <c r="D357" s="5">
         <v>45491</v>
+      </c>
+      <c r="E357" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F357" s="1">
         <v>69.709999999999994</v>
@@ -14885,7 +15411,7 @@
         <v>28.690288337397796</v>
       </c>
     </row>
-    <row r="358" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>3</v>
       </c>
@@ -14897,6 +15423,9 @@
       </c>
       <c r="D358" s="5">
         <v>45491</v>
+      </c>
+      <c r="E358" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F358" s="1">
         <v>69.709999999999994</v>
@@ -14922,7 +15451,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="359" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>3</v>
       </c>
@@ -14934,6 +15463,9 @@
       </c>
       <c r="D359" s="5">
         <v>45491</v>
+      </c>
+      <c r="E359" s="7">
+        <v>0.71250000000000002</v>
       </c>
       <c r="F359" s="1">
         <v>69.709999999999994</v>
@@ -14962,7 +15494,7 @@
         <v>14.345144168698898</v>
       </c>
     </row>
-    <row r="360" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>1</v>
       </c>
@@ -14974,6 +15506,9 @@
       </c>
       <c r="D360" s="5">
         <v>45491</v>
+      </c>
+      <c r="E360" s="7">
+        <v>0.68680555555555556</v>
       </c>
       <c r="F360" s="1">
         <v>113.57</v>
@@ -15002,7 +15537,7 @@
         <v>88.051422030465801</v>
       </c>
     </row>
-    <row r="361" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>1</v>
       </c>
@@ -15014,6 +15549,9 @@
       </c>
       <c r="D361" s="5">
         <v>45491</v>
+      </c>
+      <c r="E361" s="7">
+        <v>0.68680555555555556</v>
       </c>
       <c r="F361" s="1">
         <v>113.57</v>
@@ -15039,7 +15577,7 @@
         <v>26.41542660913974</v>
       </c>
     </row>
-    <row r="362" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>1</v>
       </c>
@@ -15051,6 +15589,9 @@
       </c>
       <c r="D362" s="5">
         <v>45491</v>
+      </c>
+      <c r="E362" s="7">
+        <v>0.68680555555555556</v>
       </c>
       <c r="F362" s="1">
         <v>113.57</v>
@@ -15079,7 +15620,7 @@
         <v>52.830853218279479</v>
       </c>
     </row>
-    <row r="363" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>1</v>
       </c>
@@ -15091,6 +15632,9 @@
       </c>
       <c r="D363" s="5">
         <v>45491</v>
+      </c>
+      <c r="E363" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F363" s="1">
         <v>113.57</v>
@@ -15119,7 +15663,7 @@
         <v>61.635995421326058</v>
       </c>
     </row>
-    <row r="364" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>1</v>
       </c>
@@ -15131,6 +15675,9 @@
       </c>
       <c r="D364" s="5">
         <v>45491</v>
+      </c>
+      <c r="E364" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F364" s="1">
         <v>113.57</v>
@@ -15156,7 +15703,7 @@
         <v>17.610284406093161</v>
       </c>
     </row>
-    <row r="365" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>1</v>
       </c>
@@ -15168,6 +15715,9 @@
       </c>
       <c r="D365" s="5">
         <v>45491</v>
+      </c>
+      <c r="E365" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F365" s="1">
         <v>113.57</v>
@@ -15193,7 +15743,7 @@
         <v>17.610284406093161</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>1</v>
       </c>
@@ -15205,6 +15755,9 @@
       </c>
       <c r="D366" s="5">
         <v>45491</v>
+      </c>
+      <c r="E366" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F366" s="1">
         <v>113.57</v>
@@ -15230,7 +15783,7 @@
         <v>8.8051422030465805</v>
       </c>
     </row>
-    <row r="367" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>2</v>
       </c>
@@ -15242,6 +15795,9 @@
       </c>
       <c r="D367" s="5">
         <v>45491</v>
+      </c>
+      <c r="E367" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F367" s="1">
         <v>113.57</v>
@@ -15270,7 +15826,7 @@
         <v>79.246279827419215</v>
       </c>
     </row>
-    <row r="368" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>2</v>
       </c>
@@ -15282,6 +15838,9 @@
       </c>
       <c r="D368" s="5">
         <v>45491</v>
+      </c>
+      <c r="E368" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F368" s="1">
         <v>113.57</v>
@@ -15310,7 +15869,7 @@
         <v>61.635995421326058</v>
       </c>
     </row>
-    <row r="369" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>2</v>
       </c>
@@ -15322,6 +15881,9 @@
       </c>
       <c r="D369" s="5">
         <v>45491</v>
+      </c>
+      <c r="E369" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F369" s="1">
         <v>113.57</v>
@@ -15347,7 +15909,7 @@
         <v>44.025711015232901</v>
       </c>
     </row>
-    <row r="370" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>2</v>
       </c>
@@ -15359,6 +15921,9 @@
       </c>
       <c r="D370" s="5">
         <v>45491</v>
+      </c>
+      <c r="E370" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F370" s="1">
         <v>113.57</v>
@@ -15387,7 +15952,7 @@
         <v>52.830853218279479</v>
       </c>
     </row>
-    <row r="371" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>2</v>
       </c>
@@ -15399,6 +15964,9 @@
       </c>
       <c r="D371" s="5">
         <v>45491</v>
+      </c>
+      <c r="E371" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F371" s="1">
         <v>113.57</v>
@@ -15424,7 +15992,7 @@
         <v>8.8051422030465805</v>
       </c>
     </row>
-    <row r="372" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>2</v>
       </c>
@@ -15436,6 +16004,9 @@
       </c>
       <c r="D372" s="5">
         <v>45491</v>
+      </c>
+      <c r="E372" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F372" s="1">
         <v>113.57</v>
@@ -15464,7 +16035,7 @@
         <v>8.8051422030465805</v>
       </c>
     </row>
-    <row r="373" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>2</v>
       </c>
@@ -15476,6 +16047,9 @@
       </c>
       <c r="D373" s="5">
         <v>45491</v>
+      </c>
+      <c r="E373" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F373" s="1">
         <v>113.57</v>
@@ -15501,7 +16075,7 @@
         <v>17.610284406093161</v>
       </c>
     </row>
-    <row r="374" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>3</v>
       </c>
@@ -15513,6 +16087,9 @@
       </c>
       <c r="D374" s="5">
         <v>45491</v>
+      </c>
+      <c r="E374" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F374" s="1">
         <v>113.57</v>
@@ -15538,7 +16115,7 @@
         <v>52.830853218279479</v>
       </c>
     </row>
-    <row r="375" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>3</v>
       </c>
@@ -15550,6 +16127,9 @@
       </c>
       <c r="D375" s="5">
         <v>45491</v>
+      </c>
+      <c r="E375" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F375" s="1">
         <v>113.57</v>
@@ -15578,7 +16158,7 @@
         <v>79.246279827419215</v>
       </c>
     </row>
-    <row r="376" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>3</v>
       </c>
@@ -15590,6 +16170,9 @@
       </c>
       <c r="D376" s="5">
         <v>45491</v>
+      </c>
+      <c r="E376" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F376" s="1">
         <v>113.57</v>
@@ -15615,7 +16198,7 @@
         <v>8.8051422030465805</v>
       </c>
     </row>
-    <row r="377" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>3</v>
       </c>
@@ -15627,6 +16210,9 @@
       </c>
       <c r="D377" s="5">
         <v>45491</v>
+      </c>
+      <c r="E377" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F377" s="1">
         <v>113.57</v>
@@ -15655,7 +16241,7 @@
         <v>79.246279827419215</v>
       </c>
     </row>
-    <row r="378" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>3</v>
       </c>
@@ -15667,6 +16253,9 @@
       </c>
       <c r="D378" s="5">
         <v>45491</v>
+      </c>
+      <c r="E378" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F378" s="1">
         <v>113.57</v>
@@ -15692,7 +16281,7 @@
         <v>8.8051422030465805</v>
       </c>
     </row>
-    <row r="379" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>3</v>
       </c>
@@ -15704,6 +16293,9 @@
       </c>
       <c r="D379" s="5">
         <v>45491</v>
+      </c>
+      <c r="E379" s="7">
+        <v>0.686805555555556</v>
       </c>
       <c r="F379" s="1">
         <v>113.57</v>
@@ -15732,627 +16324,627 @@
         <v>61.635995421326058</v>
       </c>
     </row>
-    <row r="380" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
